--- a/InputData/bldgs/BDEQ/China-BAU Distributed Electricity Quantities.xlsx
+++ b/InputData/bldgs/BDEQ/China-BAU Distributed Electricity Quantities.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24052" windowHeight="11805" firstSheet="10" activeTab="11"/>
+    <workbookView windowWidth="22368" windowHeight="9300" firstSheet="12" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="18" r:id="rId1"/>
@@ -26,20 +26,7 @@
   <externalReferences>
     <externalReference r:id="rId16"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -610,14 +597,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="9">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
     <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
@@ -676,11 +663,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -720,21 +743,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -785,28 +793,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -820,14 +807,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color rgb="FF3B3B3B"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -858,13 +845,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -882,19 +911,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -918,18 +959,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -942,31 +971,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -984,19 +989,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1015,12 +1008,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1066,6 +1053,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -1078,16 +1080,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1121,21 +1123,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1194,148 +1181,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -1355,7 +1342,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1373,7 +1360,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1394,56 +1381,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="49" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1451,7 +1438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1461,52 +1448,52 @@
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 2" xfId="49"/>
@@ -1706,7 +1693,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1715,7 +1702,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -2303,11 +2290,6 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
-        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{781d64bb-2cb1-4ebd-a4a7-58e35c37ebb1}"/>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2918,8 +2900,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="26982420" y="1733550"/>
-        <a:ext cx="4291965" cy="2600325"/>
+        <a:off x="25805765" y="1847850"/>
+        <a:ext cx="4091940" cy="2771775"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2963,7 +2945,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7620" y="7620"/>
-          <a:ext cx="5690235" cy="8376285"/>
+          <a:ext cx="5438775" cy="8924925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3392,14 +3374,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="9.13274336283186" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9.12962962962963" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="10.7964601769912" customWidth="1"/>
-    <col min="2" max="2" width="102.132743362832" customWidth="1"/>
-    <col min="3" max="16384" width="9.13274336283186" style="34"/>
+    <col min="1" max="1" width="10.7962962962963" customWidth="1"/>
+    <col min="2" max="2" width="102.12962962963" customWidth="1"/>
+    <col min="3" max="16384" width="9.12962962962963" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3412,27 +3394,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="2:2">
       <c r="B4" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="2:2">
       <c r="B5" s="37">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="2:2">
       <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="2:2">
       <c r="B7" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="54" spans="1:2">
+    <row r="10" ht="57.6" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
@@ -3440,16 +3422,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="2:2">
       <c r="B11" s="40"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="2:2">
       <c r="B12" s="40"/>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="2:2">
       <c r="B13" s="40"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="2:2">
       <c r="B14" s="40"/>
     </row>
     <row r="15" spans="1:2">
@@ -3471,18 +3453,18 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ17"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="29.7964601769912" customWidth="1"/>
-    <col min="2" max="4" width="7.53097345132743" customWidth="1"/>
-    <col min="5" max="8" width="8.53097345132743" customWidth="1"/>
-    <col min="9" max="13" width="12.7964601769912" customWidth="1"/>
-    <col min="14" max="14" width="11.7964601769912" customWidth="1"/>
-    <col min="15" max="15" width="9.53097345132743" customWidth="1"/>
-    <col min="16" max="16" width="11.7964601769912" customWidth="1"/>
-    <col min="17" max="34" width="12.7964601769912" customWidth="1"/>
-    <col min="35" max="37" width="11.7964601769912" customWidth="1"/>
-    <col min="38" max="43" width="12.7964601769912" customWidth="1"/>
+    <col min="1" max="1" width="29.7962962962963" customWidth="1"/>
+    <col min="2" max="4" width="7.52777777777778" customWidth="1"/>
+    <col min="5" max="8" width="8.52777777777778" customWidth="1"/>
+    <col min="9" max="13" width="12.7962962962963" customWidth="1"/>
+    <col min="14" max="14" width="11.7962962962963" customWidth="1"/>
+    <col min="15" max="15" width="9.52777777777778" customWidth="1"/>
+    <col min="16" max="16" width="11.7962962962963" customWidth="1"/>
+    <col min="17" max="34" width="12.7962962962963" customWidth="1"/>
+    <col min="35" max="37" width="11.7962962962963" customWidth="1"/>
+    <col min="38" max="43" width="12.7962962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
@@ -4277,171 +4259,171 @@
       </c>
       <c r="B7" s="1">
         <f>中国光伏数据!B$21</f>
-        <v>3781.90453336</v>
+        <v>13054.3</v>
       </c>
       <c r="C7" s="1">
         <f>中国光伏数据!C$21</f>
-        <v>7123.60778776</v>
+        <v>21656.3</v>
       </c>
       <c r="D7" s="1">
         <f>中国光伏数据!D$21</f>
-        <v>16929.1221368</v>
+        <v>40007.8</v>
       </c>
       <c r="E7" s="1">
         <f>中国光伏数据!E$21</f>
-        <v>38457.7773368</v>
+        <v>61466.9</v>
       </c>
       <c r="F7" s="1">
         <f>中国光伏数据!F$21</f>
-        <v>92637.6</v>
+        <v>98427.45</v>
       </c>
       <c r="G7" s="1">
         <f>中国光伏数据!G$21</f>
-        <v>116120</v>
+        <v>123377.5</v>
       </c>
       <c r="H7" s="1">
         <f>中国光伏数据!H$21</f>
-        <v>129817.779549427</v>
+        <v>174957.2</v>
       </c>
       <c r="I7" s="1">
         <f>中国光伏数据!I$21</f>
-        <v>153810.954097134</v>
+        <v>209195.609090909</v>
       </c>
       <c r="J7" s="1">
         <f>中国光伏数据!J$21</f>
-        <v>177804.12864484</v>
+        <v>243434.018181818</v>
       </c>
       <c r="K7" s="1">
         <f>中国光伏数据!K$21</f>
-        <v>201797.303192546</v>
+        <v>277672.427272727</v>
       </c>
       <c r="L7" s="1">
         <f>中国光伏数据!L$21</f>
-        <v>225790.477740253</v>
+        <v>311910.836363636</v>
       </c>
       <c r="M7" s="1">
         <f>中国光伏数据!M$21</f>
-        <v>249783.652287959</v>
+        <v>346149.245454545</v>
       </c>
       <c r="N7" s="1">
         <f>中国光伏数据!N$21</f>
-        <v>273776.826835665</v>
+        <v>380387.654545454</v>
       </c>
       <c r="O7" s="1">
         <f>中国光伏数据!O$21</f>
-        <v>297770.001383371</v>
+        <v>414626.063636363</v>
       </c>
       <c r="P7" s="1">
         <f>中国光伏数据!P$21</f>
-        <v>321763.175931078</v>
+        <v>448864.472727273</v>
       </c>
       <c r="Q7" s="1">
         <f>中国光伏数据!Q$21</f>
-        <v>345756.350478784</v>
+        <v>483102.881818182</v>
       </c>
       <c r="R7" s="1">
         <f>中国光伏数据!R$21</f>
-        <v>369749.52502649</v>
+        <v>500000</v>
       </c>
       <c r="S7" s="1">
         <f>中国光伏数据!S$21</f>
-        <v>387564.900925449</v>
+        <v>506666.666666667</v>
       </c>
       <c r="T7" s="1">
         <f>中国光伏数据!T$21</f>
-        <v>381936.959873876</v>
+        <v>513333.333333333</v>
       </c>
       <c r="U7" s="1">
         <f>中国光伏数据!U$21</f>
-        <v>376312.717079023</v>
+        <v>520000</v>
       </c>
       <c r="V7" s="1">
         <f>中国光伏数据!V$21</f>
-        <v>370695.146212259</v>
+        <v>526666.666666667</v>
       </c>
       <c r="W7" s="1">
         <f>中国光伏数据!W$21</f>
-        <v>365082.064821948</v>
+        <v>533333.333333333</v>
       </c>
       <c r="X7" s="1">
         <f>中国光伏数据!X$21</f>
-        <v>360401.541228615</v>
+        <v>540000</v>
       </c>
       <c r="Y7" s="1">
         <f>中国光伏数据!Y$21</f>
-        <v>355733.610578035</v>
+        <v>546666.666666667</v>
       </c>
       <c r="Z7" s="1">
         <f>中国光伏数据!Z$21</f>
-        <v>351073.887490935</v>
+        <v>553333.333333333</v>
       </c>
       <c r="AA7" s="1">
         <f>中国光伏数据!AA$21</f>
-        <v>346424.23632272</v>
+        <v>560000</v>
       </c>
       <c r="AB7" s="1">
         <f>中国光伏数据!AB$21</f>
-        <v>341789.650346639</v>
+        <v>566666.666666667</v>
       </c>
       <c r="AC7" s="1">
         <f>中国光伏数据!AC$21</f>
-        <v>336584.789705864</v>
+        <v>573333.333333333</v>
       </c>
       <c r="AD7" s="1">
         <f>中国光伏数据!AD$21</f>
-        <v>331402.82600937</v>
+        <v>580000</v>
       </c>
       <c r="AE7" s="1">
         <f>中国光伏数据!AE$21</f>
-        <v>326242.224130198</v>
+        <v>586666.666666666</v>
       </c>
       <c r="AF7" s="1">
         <f>中国光伏数据!AF$21</f>
-        <v>321104.720109455</v>
+        <v>593333.333333333</v>
       </c>
       <c r="AG7" s="1">
         <f>中国光伏数据!AG$21</f>
-        <v>315987.115082194</v>
+        <v>600000</v>
       </c>
       <c r="AH7" s="1">
         <f>中国光伏数据!AH$21</f>
-        <v>310345.307426459</v>
+        <v>610000</v>
       </c>
       <c r="AI7" s="1">
         <f>中国光伏数据!AI$21</f>
-        <v>304743.610741489</v>
+        <v>620000</v>
       </c>
       <c r="AJ7" s="1">
         <f>中国光伏数据!AJ$21</f>
-        <v>299170.005981055</v>
+        <v>630000</v>
       </c>
       <c r="AK7" s="1">
         <f>中国光伏数据!AK$21</f>
-        <v>293632.943970788</v>
+        <v>640000</v>
       </c>
       <c r="AL7" s="1">
         <f>中国光伏数据!AL$21</f>
-        <v>288135.732901266</v>
+        <v>650000</v>
       </c>
       <c r="AM7" s="1">
         <f>中国光伏数据!AM$21</f>
-        <v>282230.159816052</v>
+        <v>660000</v>
       </c>
       <c r="AN7" s="1">
         <f>中国光伏数据!AN$21</f>
-        <v>276373.575230968</v>
+        <v>670000</v>
       </c>
       <c r="AO7" s="1">
         <f>中国光伏数据!AO$21</f>
-        <v>270562.360565884</v>
+        <v>680000</v>
       </c>
       <c r="AP7" s="1">
         <f>中国光伏数据!AP$21</f>
-        <v>264798.937944029</v>
+        <v>690000</v>
       </c>
       <c r="AQ7" s="1">
         <f>中国光伏数据!AQ$21</f>
-        <v>259086.072613856</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -5766,18 +5748,18 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ17"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="29.7964601769912" customWidth="1"/>
-    <col min="2" max="4" width="7.53097345132743" customWidth="1"/>
-    <col min="5" max="8" width="8.53097345132743" customWidth="1"/>
-    <col min="9" max="13" width="12.7964601769912" customWidth="1"/>
-    <col min="14" max="14" width="11.7964601769912" customWidth="1"/>
-    <col min="15" max="15" width="9.53097345132743" customWidth="1"/>
-    <col min="16" max="16" width="11.7964601769912" customWidth="1"/>
-    <col min="17" max="34" width="12.7964601769912" customWidth="1"/>
-    <col min="35" max="37" width="11.7964601769912" customWidth="1"/>
-    <col min="38" max="43" width="12.7964601769912" customWidth="1"/>
+    <col min="1" max="1" width="29.7962962962963" customWidth="1"/>
+    <col min="2" max="4" width="7.52777777777778" customWidth="1"/>
+    <col min="5" max="8" width="8.52777777777778" customWidth="1"/>
+    <col min="9" max="13" width="12.7962962962963" customWidth="1"/>
+    <col min="14" max="14" width="11.7962962962963" customWidth="1"/>
+    <col min="15" max="15" width="9.52777777777778" customWidth="1"/>
+    <col min="16" max="16" width="11.7962962962963" customWidth="1"/>
+    <col min="17" max="34" width="12.7962962962963" customWidth="1"/>
+    <col min="35" max="37" width="11.7962962962963" customWidth="1"/>
+    <col min="38" max="43" width="12.7962962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
@@ -6572,19 +6554,19 @@
       </c>
       <c r="B7" s="1">
         <f>中国光伏数据!B$18</f>
-        <v>57902.6193333</v>
+        <v>47272</v>
       </c>
       <c r="C7" s="1">
         <f>中国光伏数据!C$18</f>
-        <v>69324.4902653</v>
+        <v>52751</v>
       </c>
       <c r="D7" s="1">
         <f>中国光伏数据!D$18</f>
-        <v>86346.597329</v>
+        <v>60440</v>
       </c>
       <c r="E7" s="1">
         <f>中国光伏数据!E$18</f>
-        <v>109547.778329</v>
+        <v>85306</v>
       </c>
       <c r="F7" s="1">
         <f>中国光伏数据!F$18</f>
@@ -6596,147 +6578,147 @@
       </c>
       <c r="H7" s="1">
         <f>中国光伏数据!H$18</f>
-        <v>224210.842229882</v>
+        <v>327168</v>
       </c>
       <c r="I7" s="1">
         <f>中国光伏数据!I$18</f>
-        <v>244910.07892934</v>
+        <v>347201.636363636</v>
       </c>
       <c r="J7" s="1">
         <f>中国光伏数据!J$18</f>
-        <v>247430.707609845</v>
+        <v>367235.272727273</v>
       </c>
       <c r="K7" s="1">
         <f>中国光伏数据!K$18</f>
-        <v>249960.561025928</v>
+        <v>387268.909090909</v>
       </c>
       <c r="L7" s="1">
         <f>中国光伏数据!L$18</f>
-        <v>252498.538961338</v>
+        <v>407302.545454545</v>
       </c>
       <c r="M7" s="1">
         <f>中国光伏数据!M$18</f>
-        <v>254883.726485301</v>
+        <v>427336.181818182</v>
       </c>
       <c r="N7" s="1">
         <f>中国光伏数据!N$18</f>
-        <v>257272.318984883</v>
+        <v>447369.818181818</v>
       </c>
       <c r="O7" s="1">
         <f>中国光伏数据!O$18</f>
-        <v>259665.453926246</v>
+        <v>467403.454545454</v>
       </c>
       <c r="P7" s="1">
         <f>中国光伏数据!P$18</f>
-        <v>262062.974482612</v>
+        <v>487437.090909091</v>
       </c>
       <c r="Q7" s="1">
         <f>中国光伏数据!Q$18</f>
-        <v>264463.879226501</v>
+        <v>507470.727272727</v>
       </c>
       <c r="R7" s="1">
         <f>中国光伏数据!R$18</f>
-        <v>265631.411603458</v>
+        <v>450000</v>
       </c>
       <c r="S7" s="1">
         <f>中国光伏数据!S$18</f>
-        <v>266794.659190862</v>
+        <v>456666.666666667</v>
       </c>
       <c r="T7" s="1">
         <f>中国光伏数据!T$18</f>
-        <v>267954.855680568</v>
+        <v>463333.333333333</v>
       </c>
       <c r="U7" s="1">
         <f>中国光伏数据!U$18</f>
-        <v>269111.286531409</v>
+        <v>470000</v>
       </c>
       <c r="V7" s="1">
         <f>中国光伏数据!V$18</f>
-        <v>270264.469609319</v>
+        <v>476666.666666667</v>
       </c>
       <c r="W7" s="1">
         <f>中国光伏数据!W$18</f>
-        <v>270857.05313173</v>
+        <v>483333.333333333</v>
       </c>
       <c r="X7" s="1">
         <f>中国光伏数据!X$18</f>
-        <v>271443.089542668</v>
+        <v>490000</v>
       </c>
       <c r="Y7" s="1">
         <f>中国光伏数据!Y$18</f>
-        <v>272023.607404707</v>
+        <v>496666.666666667</v>
       </c>
       <c r="Z7" s="1">
         <f>中国光伏数据!Z$18</f>
-        <v>272598.160578447</v>
+        <v>503333.333333333</v>
       </c>
       <c r="AA7" s="1">
         <f>中国光伏数据!AA$18</f>
-        <v>273165.534507682</v>
+        <v>510000</v>
       </c>
       <c r="AB7" s="1">
         <f>中国光伏数据!AB$18</f>
-        <v>273311.612917102</v>
+        <v>516666.666666667</v>
       </c>
       <c r="AC7" s="1">
         <f>中国光伏数据!AC$18</f>
-        <v>273446.40812347</v>
+        <v>523333.333333334</v>
       </c>
       <c r="AD7" s="1">
         <f>中国光伏数据!AD$18</f>
-        <v>273570.247923253</v>
+        <v>530000</v>
       </c>
       <c r="AE7" s="1">
         <f>中国光伏数据!AE$18</f>
-        <v>273682.724166801</v>
+        <v>536666.666666667</v>
       </c>
       <c r="AF7" s="1">
         <f>中国光伏数据!AF$18</f>
-        <v>273784.562403588</v>
+        <v>543333.333333333</v>
       </c>
       <c r="AG7" s="1">
         <f>中国光伏数据!AG$18</f>
-        <v>273368.72012959</v>
+        <v>550000</v>
       </c>
       <c r="AH7" s="1">
         <f>中国光伏数据!AH$18</f>
-        <v>272934.812255703</v>
+        <v>555000</v>
       </c>
       <c r="AI7" s="1">
         <f>中国光伏数据!AI$18</f>
-        <v>272485.719528671</v>
+        <v>560000</v>
       </c>
       <c r="AJ7" s="1">
         <f>中国光伏数据!AJ$18</f>
-        <v>272019.356726679</v>
+        <v>565000</v>
       </c>
       <c r="AK7" s="1">
         <f>中国光伏数据!AK$18</f>
-        <v>271534.938828024</v>
+        <v>570000</v>
       </c>
       <c r="AL7" s="1">
         <f>中国光伏数据!AL$18</f>
-        <v>270645.21366965</v>
+        <v>575000</v>
       </c>
       <c r="AM7" s="1">
         <f>中国光伏数据!AM$18</f>
-        <v>269733.199793622</v>
+        <v>580000</v>
       </c>
       <c r="AN7" s="1">
         <f>中国光伏数据!AN$18</f>
-        <v>268799.735648496</v>
+        <v>585000</v>
       </c>
       <c r="AO7" s="1">
         <f>中国光伏数据!AO$18</f>
-        <v>267844.200839324</v>
+        <v>590000</v>
       </c>
       <c r="AP7" s="1">
         <f>中国光伏数据!AP$18</f>
-        <v>266865.906863427</v>
+        <v>595000</v>
       </c>
       <c r="AQ7" s="1">
         <f>中国光伏数据!AQ$18</f>
-        <v>329487.719458785</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -8061,11 +8043,11 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.1327433628319" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5309734513274" style="1" customWidth="1"/>
-    <col min="3" max="43" width="12.7964601769912" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5277777777778" style="1" customWidth="1"/>
+    <col min="3" max="43" width="12.7962962962963" style="1" customWidth="1"/>
     <col min="44" max="44" width="7" style="1" customWidth="1"/>
     <col min="45" max="16384" width="9" style="1"/>
   </cols>
@@ -8862,171 +8844,171 @@
       </c>
       <c r="B7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!B$7*分布式年运行时间!B$6</f>
-        <v>823543.049648913</v>
+        <v>2529221.29221733</v>
       </c>
       <c r="C7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!C$7*分布式年运行时间!C$6</f>
-        <v>1544950.0727894</v>
+        <v>3935344.17889257</v>
       </c>
       <c r="D7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!D$7*分布式年运行时间!D$6</f>
-        <v>3641458.76970551</v>
+        <v>7519663.18830542</v>
       </c>
       <c r="E7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!E$7*分布式年运行时间!E$6</f>
-        <v>8765357.51062391</v>
+        <v>11830986.5319865</v>
       </c>
       <c r="F7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!F$7*分布式年运行时间!F$6</f>
-        <v>18713032.483409</v>
+        <v>16664462.3906668</v>
       </c>
       <c r="G7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!G$7*分布式年运行时间!G$6</f>
-        <v>26816228.1872032</v>
+        <v>20504518.8442779</v>
       </c>
       <c r="H7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!H$7*分布式年运行时间!H$6</f>
-        <v>31401036.1978944</v>
+        <v>30059594.0851939</v>
       </c>
       <c r="I7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!I$7*分布式年运行时间!I$6</f>
-        <v>38888866.7390277</v>
+        <v>40929576.4767273</v>
       </c>
       <c r="J7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!J$7*分布式年运行时间!J$6</f>
-        <v>46902147.8027558</v>
+        <v>50567465.0530909</v>
       </c>
       <c r="K7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!K$7*分布式年运行时间!K$6</f>
-        <v>55440879.3890787</v>
+        <v>60828328.9930909</v>
       </c>
       <c r="L7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!L$7*分布式年运行时间!L$6</f>
-        <v>64505061.4979962</v>
+        <v>71712168.2967272</v>
       </c>
       <c r="M7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!M$7*分布式年运行时间!M$6</f>
-        <v>74094694.1295087</v>
+        <v>83218982.9639999</v>
       </c>
       <c r="N7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!N$7*分布式年运行时间!N$6</f>
-        <v>84209777.2836159</v>
+        <v>95348772.9949092</v>
       </c>
       <c r="O7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!O$7*分布式年运行时间!O$6</f>
-        <v>94850310.9603178</v>
+        <v>108101538.389455</v>
       </c>
       <c r="P7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!P$7*分布式年运行时间!P$6</f>
-        <v>106016295.159614</v>
+        <v>121477279.147636</v>
       </c>
       <c r="Q7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!Q$7*分布式年运行时间!Q$6</f>
-        <v>117707729.881506</v>
+        <v>135475995.269455</v>
       </c>
       <c r="R7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!R$7*分布式年运行时间!R$6</f>
-        <v>129924615.125992</v>
+        <v>147168000</v>
       </c>
       <c r="S7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!S$7*分布式年运行时间!S$6</f>
-        <v>142666950.893073</v>
+        <v>157609920</v>
       </c>
       <c r="T7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!T$7*分布式年运行时间!T$6</f>
-        <v>155934737.182749</v>
+        <v>168402240</v>
       </c>
       <c r="U7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!U$7*分布式年运行时间!U$6</f>
-        <v>165648393.251103</v>
+        <v>179544960</v>
       </c>
       <c r="V7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!V$7*分布式年运行时间!V$6</f>
-        <v>174645833.706493</v>
+        <v>191038080</v>
       </c>
       <c r="W7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!W$7*分布式年运行时间!W$6</f>
-        <v>183643274.161883</v>
+        <v>202881600</v>
       </c>
       <c r="X7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!X$7*分布式年运行时间!X$6</f>
-        <v>192640714.617273</v>
+        <v>215075520</v>
       </c>
       <c r="Y7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!Y$7*分布式年运行时间!Y$6</f>
-        <v>201638155.072664</v>
+        <v>227619840</v>
       </c>
       <c r="Z7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!Z$7*分布式年运行时间!Z$6</f>
-        <v>210635595.528053</v>
+        <v>237045600</v>
       </c>
       <c r="AA7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AA$7*分布式年运行时间!AA$6</f>
-        <v>219633035.983443</v>
+        <v>244228800</v>
       </c>
       <c r="AB7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AB$7*分布式年运行时间!AB$6</f>
-        <v>228630476.438832</v>
+        <v>251412000</v>
       </c>
       <c r="AC7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AC$7*分布式年运行时间!AC$6</f>
-        <v>237627916.894222</v>
+        <v>258595200</v>
       </c>
       <c r="AD7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AD$7*分布式年运行时间!AD$6</f>
-        <v>246625357.349611</v>
+        <v>265778400</v>
       </c>
       <c r="AE7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AE$7*分布式年运行时间!AE$6</f>
-        <v>255622797.805002</v>
+        <v>272961600</v>
       </c>
       <c r="AF7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AF$7*分布式年运行时间!AF$6</f>
-        <v>264620238.260393</v>
+        <v>280144800</v>
       </c>
       <c r="AG7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AG$7*分布式年运行时间!AG$6</f>
-        <v>273617678.715782</v>
+        <v>287328000</v>
       </c>
       <c r="AH7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AH$7*分布式年运行时间!AH$6</f>
-        <v>282615119.171172</v>
+        <v>294511200</v>
       </c>
       <c r="AI7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AI$7*分布式年运行时间!AI$6</f>
-        <v>291612559.626561</v>
+        <v>301694400</v>
       </c>
       <c r="AJ7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AJ$7*分布式年运行时间!AJ$6</f>
-        <v>300610000.081951</v>
+        <v>308877600</v>
       </c>
       <c r="AK7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AK$7*分布式年运行时间!AK$6</f>
-        <v>309607440.53734</v>
+        <v>316060800</v>
       </c>
       <c r="AL7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AL$7*分布式年运行时间!AL$6</f>
-        <v>318604880.992731</v>
+        <v>323244000</v>
       </c>
       <c r="AM7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AM$7*分布式年运行时间!AM$6</f>
-        <v>327602321.448121</v>
+        <v>330427200</v>
       </c>
       <c r="AN7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AN$7*分布式年运行时间!AN$6</f>
-        <v>336599761.903511</v>
+        <v>337610400</v>
       </c>
       <c r="AO7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AO$7*分布式年运行时间!AO$6</f>
-        <v>345597202.358901</v>
+        <v>344793600</v>
       </c>
       <c r="AP7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AP$7*分布式年运行时间!AP$6</f>
-        <v>354594642.81429</v>
+        <v>351976800</v>
       </c>
       <c r="AQ7" s="1">
         <f>'BDEQ-BDESC-urban-residential'!AQ$7*分布式年运行时间!AQ$6</f>
-        <v>363592083.269681</v>
+        <v>359160000</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -10351,23 +10333,23 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.1327433628319" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="7" max="10" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="12" max="15" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="17" max="20" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5309734513274" style="1" customWidth="1"/>
-    <col min="22" max="25" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="27" max="43" width="12.7964601769912" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="7" max="10" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="12" max="15" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="17" max="20" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5277777777778" style="1" customWidth="1"/>
+    <col min="22" max="25" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="27" max="43" width="12.7962962962963" style="1" customWidth="1"/>
     <col min="44" max="44" width="7" style="1" customWidth="1"/>
     <col min="45" max="16384" width="9" style="1"/>
   </cols>
@@ -11164,171 +11146,171 @@
       </c>
       <c r="B7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!B$7*分布式年运行时间!B$6</f>
-        <v>3294172.19859565</v>
+        <v>14332253.9892315</v>
       </c>
       <c r="C7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!C$7*分布式年运行时间!C$6</f>
-        <v>6179800.29115758</v>
+        <v>22300283.6803912</v>
       </c>
       <c r="D7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!D$7*分布式年运行时间!D$6</f>
-        <v>14565835.078822</v>
+        <v>42611424.7337307</v>
       </c>
       <c r="E7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!E$7*分布式年运行时间!E$6</f>
-        <v>35061430.0424957</v>
+        <v>67042257.0145901</v>
       </c>
       <c r="F7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!F$7*分布式年运行时间!F$6</f>
-        <v>74852129.9336361</v>
+        <v>94431953.5471117</v>
       </c>
       <c r="G7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!G$7*分布式年运行时间!G$6</f>
-        <v>107264912.748813</v>
+        <v>116192273.450908</v>
       </c>
       <c r="H7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!H$7*分布式年运行时间!H$6</f>
-        <v>125604144.791577</v>
+        <v>170337699.816099</v>
       </c>
       <c r="I7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!I$7*分布式年运行时间!I$6</f>
-        <v>155555466.956111</v>
+        <v>225404084.883273</v>
       </c>
       <c r="J7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!J$7*分布式年运行时间!J$6</f>
-        <v>187608591.211023</v>
+        <v>272957695.906909</v>
       </c>
       <c r="K7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!K$7*分布式年运行时间!K$6</f>
-        <v>221763517.556314</v>
+        <v>323510591.566909</v>
       </c>
       <c r="L7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!L$7*分布式年运行时间!L$6</f>
-        <v>258020245.991986</v>
+        <v>377062771.863273</v>
       </c>
       <c r="M7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!M$7*分布式年运行时间!M$6</f>
-        <v>296378776.518035</v>
+        <v>433614236.796</v>
       </c>
       <c r="N7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!N$7*分布式年运行时间!N$6</f>
-        <v>336839109.134463</v>
+        <v>493164986.365091</v>
       </c>
       <c r="O7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!O$7*分布式年运行时间!O$6</f>
-        <v>379401243.841271</v>
+        <v>555715020.570545</v>
       </c>
       <c r="P7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!P$7*分布式年运行时间!P$6</f>
-        <v>424065180.638458</v>
+        <v>621264339.412363</v>
       </c>
       <c r="Q7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!Q$7*分布式年运行时间!Q$6</f>
-        <v>470830919.526024</v>
+        <v>689812942.890545</v>
       </c>
       <c r="R7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!R$7*分布式年运行时间!R$6</f>
-        <v>519698460.503968</v>
+        <v>735840000</v>
       </c>
       <c r="S7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!S$7*分布式年运行时间!S$6</f>
-        <v>561714060.964226</v>
+        <v>767843200</v>
       </c>
       <c r="T7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!T$7*分布式年运行时间!T$6</f>
-        <v>570286088.868979</v>
+        <v>800430400</v>
       </c>
       <c r="U7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!U$7*分布式年运行时间!U$6</f>
-        <v>564469075.618535</v>
+        <v>833601600</v>
       </c>
       <c r="V7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!V$7*分布式年运行时间!V$6</f>
-        <v>556042719.318389</v>
+        <v>867356800</v>
       </c>
       <c r="W7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!W$7*分布式年运行时间!W$6</f>
-        <v>547623097.232922</v>
+        <v>901696000</v>
       </c>
       <c r="X7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!X$7*分布式年运行时间!X$6</f>
-        <v>540602311.842922</v>
+        <v>936619200</v>
       </c>
       <c r="Y7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!Y$7*分布式年运行时间!Y$6</f>
-        <v>533600415.867052</v>
+        <v>972126400</v>
       </c>
       <c r="Z7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!Z$7*分布式年运行时间!Z$6</f>
-        <v>526610831.236402</v>
+        <v>993676000</v>
       </c>
       <c r="AA7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AA$7*分布式年运行时间!AA$6</f>
-        <v>519636354.48408</v>
+        <v>1005648000</v>
       </c>
       <c r="AB7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AB$7*分布式年运行时间!AB$6</f>
-        <v>512684475.519958</v>
+        <v>1017620000</v>
       </c>
       <c r="AC7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AC$7*分布式年运行时间!AC$6</f>
-        <v>504877184.558796</v>
+        <v>1029592000</v>
       </c>
       <c r="AD7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AD$7*分布式年运行时间!AD$6</f>
-        <v>497104239.014055</v>
+        <v>1041564000</v>
       </c>
       <c r="AE7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AE$7*分布式年运行时间!AE$6</f>
-        <v>489363336.195297</v>
+        <v>1053536000</v>
       </c>
       <c r="AF7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AF$7*分布式年运行时间!AF$6</f>
-        <v>481657080.164182</v>
+        <v>1065508000</v>
       </c>
       <c r="AG7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AG$7*分布式年运行时间!AG$6</f>
-        <v>473980672.623291</v>
+        <v>1077480000</v>
       </c>
       <c r="AH7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AH$7*分布式年运行时间!AH$6</f>
-        <v>465517961.139688</v>
+        <v>1095438000</v>
       </c>
       <c r="AI7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AI$7*分布式年运行时间!AI$6</f>
-        <v>457115416.112233</v>
+        <v>1113396000</v>
       </c>
       <c r="AJ7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AJ$7*分布式年运行时间!AJ$6</f>
-        <v>448755008.971582</v>
+        <v>1131354000</v>
       </c>
       <c r="AK7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AK$7*分布式年运行时间!AK$6</f>
-        <v>440449415.956182</v>
+        <v>1149312000</v>
       </c>
       <c r="AL7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AL$7*分布式年运行时间!AL$6</f>
-        <v>432203599.351899</v>
+        <v>1167270000</v>
       </c>
       <c r="AM7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AM$7*分布式年运行时间!AM$6</f>
-        <v>423345239.724078</v>
+        <v>1185228000</v>
       </c>
       <c r="AN7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AN$7*分布式年运行时间!AN$6</f>
-        <v>414560362.846452</v>
+        <v>1203186000</v>
       </c>
       <c r="AO7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AO$7*分布式年运行时间!AO$6</f>
-        <v>405843540.848826</v>
+        <v>1221144000</v>
       </c>
       <c r="AP7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AP$7*分布式年运行时间!AP$6</f>
-        <v>397198406.916043</v>
+        <v>1239102000</v>
       </c>
       <c r="AQ7" s="1">
         <f>'BDEQ-BDESC-rural-residential'!AQ$7*分布式年运行时间!AQ$6</f>
-        <v>388629108.920784</v>
+        <v>1257060000</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -12653,13 +12635,13 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.1327433628319" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7964601769912" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.7964601769912" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5309734513274" style="1" customWidth="1"/>
-    <col min="6" max="43" width="12.7964601769912" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1296296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7962962962963" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.7962962962963" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5277777777778" style="1" customWidth="1"/>
+    <col min="6" max="43" width="12.7962962962963" style="1" customWidth="1"/>
     <col min="44" max="44" width="7" style="1" customWidth="1"/>
     <col min="45" max="16384" width="9" style="1"/>
   </cols>
@@ -13456,171 +13438,171 @@
       </c>
       <c r="B7" s="1">
         <f>'BDEQ-BDESC-commercial'!B$7*分布式年运行时间!B$6</f>
-        <v>50435223.0869672</v>
+        <v>51899704.3563388</v>
       </c>
       <c r="C7" s="1">
         <f>'BDEQ-BDESC-commercial'!C$7*分布式年运行时间!C$6</f>
-        <v>60139681.7300865</v>
+        <v>54319632.8285218</v>
       </c>
       <c r="D7" s="1">
         <f>'BDEQ-BDESC-commercial'!D$7*分布式年运行时间!D$6</f>
-        <v>74292706.1514724</v>
+        <v>64373309.9772215</v>
       </c>
       <c r="E7" s="1">
         <f>'BDEQ-BDESC-commercial'!E$7*分布式年运行时间!E$6</f>
-        <v>99873212.4468805</v>
+        <v>93043683.2976224</v>
       </c>
       <c r="F7" s="1">
         <f>'BDEQ-BDESC-commercial'!F$7*分布式年运行时间!F$6</f>
-        <v>112023348.468972</v>
+        <v>133013102.25679</v>
       </c>
       <c r="G7" s="1">
         <f>'BDEQ-BDESC-commercial'!G$7*分布式年运行时间!G$6</f>
-        <v>212118859.063984</v>
+        <v>216256868.169091</v>
       </c>
       <c r="H7" s="1">
         <f>'BDEQ-BDESC-commercial'!H$7*分布式年运行时间!H$6</f>
-        <v>216933390.703707</v>
+        <v>318529586.512778</v>
       </c>
       <c r="I7" s="1">
         <f>'BDEQ-BDESC-commercial'!I$7*分布式年运行时间!I$6</f>
-        <v>247687831.557514</v>
+        <v>374102819.149091</v>
       </c>
       <c r="J7" s="1">
         <f>'BDEQ-BDESC-commercial'!J$7*分布式年运行时间!J$6</f>
-        <v>261074514.021847</v>
+        <v>411773566.603637</v>
       </c>
       <c r="K7" s="1">
         <f>'BDEQ-BDESC-commercial'!K$7*分布式年运行时间!K$6</f>
-        <v>274692141.007299</v>
+        <v>451199260.603636</v>
       </c>
       <c r="L7" s="1">
         <f>'BDEQ-BDESC-commercial'!L$7*分布式年运行时间!L$6</f>
-        <v>288540667.380885</v>
+        <v>492379901.14909</v>
       </c>
       <c r="M7" s="1">
         <f>'BDEQ-BDESC-commercial'!M$7*分布式年运行时间!M$6</f>
-        <v>302430228.392143</v>
+        <v>535315488.24</v>
       </c>
       <c r="N7" s="1">
         <f>'BDEQ-BDESC-commercial'!N$7*分布式年运行时间!N$6</f>
-        <v>316532921.114769</v>
+        <v>580006021.876363</v>
       </c>
       <c r="O7" s="1">
         <f>'BDEQ-BDESC-commercial'!O$7*分布式年运行时间!O$6</f>
-        <v>330850642.255891</v>
+        <v>626451502.058181</v>
       </c>
       <c r="P7" s="1">
         <f>'BDEQ-BDESC-commercial'!P$7*分布式年运行时间!P$6</f>
-        <v>345383782.003771</v>
+        <v>674651928.785455</v>
       </c>
       <c r="Q7" s="1">
         <f>'BDEQ-BDESC-commercial'!Q$7*分布式年运行时间!Q$6</f>
-        <v>360131552.942433</v>
+        <v>724607302.058182</v>
       </c>
       <c r="R7" s="1">
         <f>'BDEQ-BDESC-commercial'!R$7*分布式年运行时间!R$6</f>
-        <v>373356086.561363</v>
+        <v>662256000</v>
       </c>
       <c r="S7" s="1">
         <f>'BDEQ-BDESC-commercial'!S$7*分布式年运行时间!S$6</f>
-        <v>386676685.89136</v>
+        <v>692069200</v>
       </c>
       <c r="T7" s="1">
         <f>'BDEQ-BDESC-commercial'!T$7*分布式年运行时间!T$6</f>
-        <v>400094629.988112</v>
+        <v>722466400</v>
       </c>
       <c r="U7" s="1">
         <f>'BDEQ-BDESC-commercial'!U$7*分布式年运行时间!U$6</f>
-        <v>403666929.797114</v>
+        <v>753447600</v>
       </c>
       <c r="V7" s="1">
         <f>'BDEQ-BDESC-commercial'!V$7*分布式年运行时间!V$6</f>
-        <v>405396704.413979</v>
+        <v>785012800.000001</v>
       </c>
       <c r="W7" s="1">
         <f>'BDEQ-BDESC-commercial'!W$7*分布式年运行时间!W$6</f>
-        <v>406285579.697595</v>
+        <v>817162000</v>
       </c>
       <c r="X7" s="1">
         <f>'BDEQ-BDESC-commercial'!X$7*分布式年运行时间!X$6</f>
-        <v>407164634.314002</v>
+        <v>849895200</v>
       </c>
       <c r="Y7" s="1">
         <f>'BDEQ-BDESC-commercial'!Y$7*分布式年运行时间!Y$6</f>
-        <v>408035411.10706</v>
+        <v>883212400.000001</v>
       </c>
       <c r="Z7" s="1">
         <f>'BDEQ-BDESC-commercial'!Z$7*分布式年运行时间!Z$6</f>
-        <v>408897240.86767</v>
+        <v>903885999.999999</v>
       </c>
       <c r="AA7" s="1">
         <f>'BDEQ-BDESC-commercial'!AA$7*分布式年运行时间!AA$6</f>
-        <v>409748301.761523</v>
+        <v>915858000</v>
       </c>
       <c r="AB7" s="1">
         <f>'BDEQ-BDESC-commercial'!AB$7*分布式年运行时间!AB$6</f>
-        <v>409967419.375653</v>
+        <v>927830000</v>
       </c>
       <c r="AC7" s="1">
         <f>'BDEQ-BDESC-commercial'!AC$7*分布式年运行时间!AC$6</f>
-        <v>410169612.185205</v>
+        <v>939802000.000001</v>
       </c>
       <c r="AD7" s="1">
         <f>'BDEQ-BDESC-commercial'!AD$7*分布式年运行时间!AD$6</f>
-        <v>410355371.884879</v>
+        <v>951774000</v>
       </c>
       <c r="AE7" s="1">
         <f>'BDEQ-BDESC-commercial'!AE$7*分布式年运行时间!AE$6</f>
-        <v>410524086.250202</v>
+        <v>963746000</v>
       </c>
       <c r="AF7" s="1">
         <f>'BDEQ-BDESC-commercial'!AF$7*分布式年运行时间!AF$6</f>
-        <v>410676843.605382</v>
+        <v>975717999.999999</v>
       </c>
       <c r="AG7" s="1">
         <f>'BDEQ-BDESC-commercial'!AG$7*分布式年运行时间!AG$6</f>
-        <v>410053080.194385</v>
+        <v>987690000</v>
       </c>
       <c r="AH7" s="1">
         <f>'BDEQ-BDESC-commercial'!AH$7*分布式年运行时间!AH$6</f>
-        <v>409402218.383554</v>
+        <v>996669000</v>
       </c>
       <c r="AI7" s="1">
         <f>'BDEQ-BDESC-commercial'!AI$7*分布式年运行时间!AI$6</f>
-        <v>408728579.293006</v>
+        <v>1005648000</v>
       </c>
       <c r="AJ7" s="1">
         <f>'BDEQ-BDESC-commercial'!AJ$7*分布式年运行时间!AJ$6</f>
-        <v>408029035.090019</v>
+        <v>1014627000</v>
       </c>
       <c r="AK7" s="1">
         <f>'BDEQ-BDESC-commercial'!AK$7*分布式年运行时间!AK$6</f>
-        <v>407302408.242036</v>
+        <v>1023606000</v>
       </c>
       <c r="AL7" s="1">
         <f>'BDEQ-BDESC-commercial'!AL$7*分布式年运行时间!AL$6</f>
-        <v>405967820.504475</v>
+        <v>1032585000</v>
       </c>
       <c r="AM7" s="1">
         <f>'BDEQ-BDESC-commercial'!AM$7*分布式年运行时间!AM$6</f>
-        <v>404599799.690433</v>
+        <v>1041564000</v>
       </c>
       <c r="AN7" s="1">
         <f>'BDEQ-BDESC-commercial'!AN$7*分布式年运行时间!AN$6</f>
-        <v>403199603.472744</v>
+        <v>1050543000</v>
       </c>
       <c r="AO7" s="1">
         <f>'BDEQ-BDESC-commercial'!AO$7*分布式年运行时间!AO$6</f>
-        <v>401766301.258986</v>
+        <v>1059522000</v>
       </c>
       <c r="AP7" s="1">
         <f>'BDEQ-BDESC-commercial'!AP$7*分布式年运行时间!AP$6</f>
-        <v>400298860.295141</v>
+        <v>1068501000</v>
       </c>
       <c r="AQ7" s="1">
         <f>'BDEQ-BDESC-commercial'!AQ$7*分布式年运行时间!AQ$6</f>
-        <v>494231579.188178</v>
+        <v>1077480000</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -14943,7 +14925,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="K2"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <sheetData>
     <row r="2" spans="11:11">
       <c r="K2" t="s">
@@ -14961,13 +14943,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AZ34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="6" width="9.46902654867257" customWidth="1"/>
+    <col min="5" max="6" width="9.47222222222222" customWidth="1"/>
     <col min="8" max="12" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="2:52">
       <c r="B1">
         <v>2017</v>
       </c>
@@ -15003,52 +14985,52 @@
       </c>
       <c r="O1" s="16"/>
       <c r="P1" s="16"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="19" t="s">
+      <c r="Q1" s="21"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="X1" s="21" t="s">
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="X1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AC1" s="22" t="s">
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AC1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AH1" s="22" t="s">
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AH1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AM1" s="22" t="s">
+      <c r="AI1" s="26"/>
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="26"/>
+      <c r="AM1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
-      <c r="AR1" s="22" t="s">
+      <c r="AN1" s="26"/>
+      <c r="AO1" s="26"/>
+      <c r="AP1" s="26"/>
+      <c r="AR1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="AS1" s="22"/>
-      <c r="AT1" s="22"/>
-      <c r="AU1" s="22"/>
-      <c r="AW1" s="22" t="s">
+      <c r="AS1" s="26"/>
+      <c r="AT1" s="26"/>
+      <c r="AU1" s="26"/>
+      <c r="AW1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AX1" s="22"/>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="22"/>
+      <c r="AX1" s="26"/>
+      <c r="AY1" s="26"/>
+      <c r="AZ1" s="26"/>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="2:52">
       <c r="B2" t="s">
         <v>16</v>
       </c>
@@ -15079,100 +15061,100 @@
       <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="Q2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="23" t="s">
+      <c r="S2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="23" t="s">
+      <c r="T2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="23" t="s">
+      <c r="U2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="V2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="23" t="s">
+      <c r="X2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="23" t="s">
+      <c r="Y2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="23" t="s">
+      <c r="Z2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="23" t="s">
+      <c r="AA2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AC2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" s="23" t="s">
+      <c r="AD2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AE2" s="23" t="s">
+      <c r="AE2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AF2" s="23" t="s">
+      <c r="AF2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AH2" s="23" t="s">
+      <c r="AH2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AI2" s="23" t="s">
+      <c r="AI2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AJ2" s="23" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AK2" s="23" t="s">
+      <c r="AK2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AM2" s="23" t="s">
+      <c r="AM2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AN2" s="23" t="s">
+      <c r="AN2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AO2" s="23" t="s">
+      <c r="AO2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AP2" s="23" t="s">
+      <c r="AP2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AR2" s="23" t="s">
+      <c r="AR2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AS2" s="23" t="s">
+      <c r="AS2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AT2" s="23" t="s">
+      <c r="AT2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AU2" s="23" t="s">
+      <c r="AU2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AW2" s="23" t="s">
+      <c r="AW2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AX2" s="23" t="s">
+      <c r="AX2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AY2" s="23" t="s">
+      <c r="AY2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AZ2" s="23" t="s">
+      <c r="AZ2" s="17" t="s">
         <v>21</v>
       </c>
     </row>
@@ -15210,111 +15192,111 @@
       <c r="L3">
         <v>10750.8</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>154</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="18">
         <v>388</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="18">
         <v>538</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="18">
         <v>679</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="26">
         <v>1178</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="26">
         <v>1769</v>
       </c>
-      <c r="U3" s="22">
+      <c r="U3" s="26">
         <v>2240</v>
       </c>
-      <c r="V3" s="22">
+      <c r="V3" s="26">
         <v>2611</v>
       </c>
-      <c r="X3" s="25">
+      <c r="X3" s="27">
         <v>10277</v>
       </c>
-      <c r="Y3" s="25">
+      <c r="Y3" s="27">
         <v>12885</v>
       </c>
-      <c r="Z3" s="25">
+      <c r="Z3" s="27">
         <v>14709</v>
       </c>
-      <c r="AA3" s="25">
+      <c r="AA3" s="27">
         <v>18134</v>
       </c>
-      <c r="AC3" s="22">
+      <c r="AC3" s="26">
         <v>1029</v>
       </c>
-      <c r="AD3" s="22">
+      <c r="AD3" s="26">
         <v>1412</v>
       </c>
-      <c r="AE3" s="25">
+      <c r="AE3" s="27">
         <v>1738</v>
       </c>
-      <c r="AF3" s="25">
+      <c r="AF3" s="27">
         <v>1982</v>
       </c>
-      <c r="AH3" s="25">
+      <c r="AH3" s="27">
         <v>1205</v>
       </c>
-      <c r="AI3" s="25">
+      <c r="AI3" s="27">
         <v>1230</v>
       </c>
-      <c r="AJ3" s="25">
+      <c r="AJ3" s="27">
         <v>1281</v>
       </c>
-      <c r="AK3" s="26">
+      <c r="AK3" s="31">
         <v>1291</v>
       </c>
-      <c r="AM3" s="27">
+      <c r="AM3" s="32">
         <f t="shared" ref="AM3:AP3" si="0">AC3*10000/X3</f>
         <v>1001.26496059161</v>
       </c>
-      <c r="AN3" s="27">
+      <c r="AN3" s="32">
         <f t="shared" si="0"/>
         <v>1095.84788513776</v>
       </c>
-      <c r="AO3" s="27">
+      <c r="AO3" s="32">
         <f t="shared" si="0"/>
         <v>1181.58950302536</v>
       </c>
-      <c r="AP3" s="27">
+      <c r="AP3" s="32">
         <f t="shared" si="0"/>
         <v>1092.97452299548</v>
       </c>
-      <c r="AR3" s="27">
+      <c r="AR3" s="32">
         <f t="shared" ref="AR3:AR11" si="1">(S3-N3)*10000/B3</f>
         <v>1091.21909633419</v>
       </c>
-      <c r="AS3" s="27">
+      <c r="AS3" s="32">
         <f t="shared" ref="AS3:AS24" si="2">(T3-O3)*10000/C3</f>
         <v>1113.17104626793</v>
       </c>
-      <c r="AT3" s="27">
+      <c r="AT3" s="32">
         <f t="shared" ref="AT3:AT24" si="3">(U3-P3)*10000/D3</f>
         <v>1201.3834968589</v>
       </c>
-      <c r="AU3" s="27">
+      <c r="AU3" s="32">
         <f t="shared" ref="AU3:AU34" si="4">(V3-Q3)*10000/E3</f>
         <v>1117.54658034796</v>
       </c>
-      <c r="AW3" s="27">
+      <c r="AW3" s="32">
         <f t="shared" ref="AW3:AZ3" si="5">N3*10000/H3</f>
         <v>420.995079278294</v>
       </c>
-      <c r="AX3" s="27">
+      <c r="AX3" s="32">
         <f t="shared" si="5"/>
         <v>771.832106624229</v>
       </c>
-      <c r="AY3" s="27">
+      <c r="AY3" s="32">
         <f t="shared" si="5"/>
         <v>859.013252434935</v>
       </c>
-      <c r="AZ3" s="27">
+      <c r="AZ3" s="32">
         <f t="shared" si="5"/>
         <v>867.964565570313</v>
       </c>
@@ -15353,96 +15335,96 @@
       <c r="L4">
         <v>75</v>
       </c>
-      <c r="N4" s="24">
+      <c r="N4" s="18">
         <v>1</v>
       </c>
-      <c r="O4" s="24">
+      <c r="O4" s="18">
         <v>2</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="18">
         <v>4</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="Q4" s="18">
         <v>5</v>
       </c>
-      <c r="S4" s="22">
+      <c r="S4" s="26">
         <v>2</v>
       </c>
-      <c r="T4" s="22">
+      <c r="T4" s="26">
         <v>3</v>
       </c>
-      <c r="U4" s="22">
+      <c r="U4" s="26">
         <v>5</v>
       </c>
-      <c r="V4" s="22">
+      <c r="V4" s="26">
         <v>6</v>
       </c>
-      <c r="X4" s="25">
+      <c r="X4" s="27">
         <v>5</v>
       </c>
-      <c r="Y4" s="25">
+      <c r="Y4" s="27">
         <v>8</v>
       </c>
-      <c r="Z4" s="25">
+      <c r="Z4" s="27">
         <v>8</v>
       </c>
-      <c r="AA4" s="25">
+      <c r="AA4" s="27">
         <v>8</v>
       </c>
-      <c r="AC4" s="22">
+      <c r="AC4" s="26">
         <v>1</v>
       </c>
-      <c r="AD4" s="22">
+      <c r="AD4" s="26">
         <v>0.8</v>
       </c>
-      <c r="AE4" s="25">
+      <c r="AE4" s="27">
         <v>1</v>
       </c>
-      <c r="AF4" s="25">
+      <c r="AF4" s="27">
         <v>1</v>
       </c>
-      <c r="AH4" s="25">
+      <c r="AH4" s="27">
         <v>1551</v>
       </c>
-      <c r="AI4" s="25">
+      <c r="AI4" s="27">
         <v>1261</v>
       </c>
-      <c r="AJ4" s="25">
+      <c r="AJ4" s="27">
         <v>1242</v>
       </c>
-      <c r="AK4" s="26">
+      <c r="AK4" s="31">
         <v>1323</v>
       </c>
-      <c r="AM4" s="27"/>
-      <c r="AN4" s="27">
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32">
         <f t="shared" ref="AN4:AP4" si="6">AD4*10000/Y4</f>
         <v>1000</v>
       </c>
-      <c r="AO4" s="27">
+      <c r="AO4" s="32">
         <f t="shared" si="6"/>
         <v>1250</v>
       </c>
-      <c r="AP4" s="27">
+      <c r="AP4" s="32">
         <f t="shared" si="6"/>
         <v>1250</v>
       </c>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AW4" s="27">
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="32"/>
+      <c r="AW4" s="32">
         <f t="shared" ref="AW4:AZ4" si="7">N4*10000/H4</f>
         <v>454.545454545455</v>
       </c>
-      <c r="AX4" s="27">
+      <c r="AX4" s="32">
         <f t="shared" si="7"/>
         <v>571.428571428571</v>
       </c>
-      <c r="AY4" s="27">
+      <c r="AY4" s="32">
         <f t="shared" si="7"/>
         <v>869.565217391304</v>
       </c>
-      <c r="AZ4" s="27">
+      <c r="AZ4" s="32">
         <f t="shared" si="7"/>
         <v>886.524822695035</v>
       </c>
@@ -15481,111 +15463,111 @@
       <c r="L5">
         <v>58.9</v>
       </c>
-      <c r="N5" s="24">
+      <c r="N5" s="18">
         <v>1</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="18">
         <v>2</v>
       </c>
-      <c r="P5" s="24">
+      <c r="P5" s="18">
         <v>3</v>
       </c>
-      <c r="Q5" s="24">
+      <c r="Q5" s="18">
         <v>4</v>
       </c>
-      <c r="S5" s="22">
+      <c r="S5" s="26">
         <v>6.2</v>
       </c>
-      <c r="T5" s="22">
+      <c r="T5" s="26">
         <v>8</v>
       </c>
       <c r="U5" s="28">
         <v>15</v>
       </c>
-      <c r="V5" s="22">
+      <c r="V5" s="26">
         <v>19</v>
       </c>
-      <c r="X5" s="25">
+      <c r="X5" s="27">
         <v>55</v>
       </c>
-      <c r="Y5" s="25">
+      <c r="Y5" s="27">
         <v>108</v>
       </c>
-      <c r="Z5" s="25">
+      <c r="Z5" s="27">
         <v>119</v>
       </c>
-      <c r="AA5" s="25">
+      <c r="AA5" s="27">
         <v>134</v>
       </c>
-      <c r="AC5" s="22">
+      <c r="AC5" s="26">
         <v>6</v>
       </c>
-      <c r="AD5" s="22">
+      <c r="AD5" s="26">
         <v>7</v>
       </c>
-      <c r="AE5" s="25">
+      <c r="AE5" s="27">
         <v>13</v>
       </c>
-      <c r="AF5" s="25">
+      <c r="AF5" s="27">
         <v>16</v>
       </c>
-      <c r="AH5" s="25">
+      <c r="AH5" s="27">
         <v>1027</v>
       </c>
-      <c r="AI5" s="25">
+      <c r="AI5" s="27">
         <v>864</v>
       </c>
-      <c r="AJ5" s="25">
+      <c r="AJ5" s="27">
         <v>1265</v>
       </c>
-      <c r="AK5" s="26">
+      <c r="AK5" s="31">
         <v>1144</v>
       </c>
-      <c r="AM5" s="27">
+      <c r="AM5" s="32">
         <f t="shared" ref="AM5:AP5" si="8">AC5*10000/X5</f>
         <v>1090.90909090909</v>
       </c>
-      <c r="AN5" s="27">
+      <c r="AN5" s="32">
         <f t="shared" si="8"/>
         <v>648.148148148148</v>
       </c>
-      <c r="AO5" s="27">
+      <c r="AO5" s="32">
         <f t="shared" si="8"/>
         <v>1092.43697478992</v>
       </c>
-      <c r="AP5" s="27">
+      <c r="AP5" s="32">
         <f t="shared" si="8"/>
         <v>1194.02985074627</v>
       </c>
-      <c r="AR5" s="27">
+      <c r="AR5" s="32">
         <f t="shared" si="1"/>
         <v>981.132075471698</v>
       </c>
-      <c r="AS5" s="27">
+      <c r="AS5" s="32">
         <f t="shared" si="2"/>
         <v>618.556701030928</v>
       </c>
-      <c r="AT5" s="27">
+      <c r="AT5" s="32">
         <f t="shared" si="3"/>
         <v>1153.84615384615</v>
       </c>
-      <c r="AU5" s="27">
+      <c r="AU5" s="32">
         <f t="shared" si="4"/>
         <v>1262.20127903063</v>
       </c>
-      <c r="AW5" s="27">
+      <c r="AW5" s="32">
         <f t="shared" ref="AW5:AZ5" si="9">N5*10000/H5</f>
         <v>666.666666666667</v>
       </c>
-      <c r="AX5" s="27">
+      <c r="AX5" s="32">
         <f t="shared" si="9"/>
         <v>645.161290322581</v>
       </c>
-      <c r="AY5" s="27">
+      <c r="AY5" s="32">
         <f t="shared" si="9"/>
         <v>789.473684210526</v>
       </c>
-      <c r="AZ5" s="27">
+      <c r="AZ5" s="32">
         <f t="shared" si="9"/>
         <v>894.854586129754</v>
       </c>
@@ -15624,111 +15606,111 @@
       <c r="L6">
         <v>1262.5</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="18">
         <v>11</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="18">
         <v>32</v>
       </c>
-      <c r="P6" s="24">
+      <c r="P6" s="18">
         <v>53</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="Q6" s="18">
         <v>70</v>
       </c>
-      <c r="S6" s="22">
+      <c r="S6" s="26">
         <v>77</v>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="26">
         <v>126</v>
       </c>
-      <c r="U6" s="22">
+      <c r="U6" s="26">
         <v>176</v>
       </c>
-      <c r="V6" s="22">
+      <c r="V6" s="26">
         <v>211</v>
       </c>
-      <c r="X6" s="25">
+      <c r="X6" s="27">
         <v>662</v>
       </c>
-      <c r="Y6" s="25">
+      <c r="Y6" s="27">
         <v>859</v>
       </c>
-      <c r="Z6" s="25">
+      <c r="Z6" s="27">
         <v>965</v>
       </c>
-      <c r="AA6" s="25">
+      <c r="AA6" s="27">
         <v>1447</v>
       </c>
-      <c r="AC6" s="22">
+      <c r="AC6" s="26">
         <v>67</v>
       </c>
-      <c r="AD6" s="22">
+      <c r="AD6" s="26">
         <v>95</v>
       </c>
-      <c r="AE6" s="25">
+      <c r="AE6" s="27">
         <v>124</v>
       </c>
-      <c r="AF6" s="25">
+      <c r="AF6" s="27">
         <v>141</v>
       </c>
-      <c r="AH6" s="25">
+      <c r="AH6" s="27">
         <v>1303</v>
       </c>
-      <c r="AI6" s="25">
+      <c r="AI6" s="27">
         <v>1275</v>
       </c>
-      <c r="AJ6" s="25">
+      <c r="AJ6" s="27">
         <v>1336</v>
       </c>
-      <c r="AK6" s="26">
+      <c r="AK6" s="31">
         <v>1379</v>
       </c>
-      <c r="AM6" s="27">
+      <c r="AM6" s="32">
         <f t="shared" ref="AM6:AP6" si="10">AC6*10000/X6</f>
         <v>1012.08459214502</v>
       </c>
-      <c r="AN6" s="27">
+      <c r="AN6" s="32">
         <f t="shared" si="10"/>
         <v>1105.93713620489</v>
       </c>
-      <c r="AO6" s="27">
+      <c r="AO6" s="32">
         <f t="shared" si="10"/>
         <v>1284.97409326425</v>
       </c>
-      <c r="AP6" s="27">
+      <c r="AP6" s="32">
         <f t="shared" si="10"/>
         <v>974.429854872149</v>
       </c>
-      <c r="AR6" s="27">
+      <c r="AR6" s="32">
         <f t="shared" si="1"/>
         <v>1276.59574468085</v>
       </c>
-      <c r="AS6" s="27">
+      <c r="AS6" s="32">
         <f t="shared" si="2"/>
         <v>1098.1308411215</v>
       </c>
-      <c r="AT6" s="27">
+      <c r="AT6" s="32">
         <f t="shared" si="3"/>
         <v>1278.58627858628</v>
       </c>
-      <c r="AU6" s="27">
+      <c r="AU6" s="32">
         <f t="shared" si="4"/>
         <v>975.427527810061</v>
       </c>
-      <c r="AW6" s="27">
+      <c r="AW6" s="32">
         <f t="shared" ref="AW6:AZ6" si="11">N6*10000/H6</f>
         <v>313.390313390313</v>
       </c>
-      <c r="AX6" s="27">
+      <c r="AX6" s="32">
         <f t="shared" si="11"/>
         <v>846.560846560847</v>
       </c>
-      <c r="AY6" s="27">
+      <c r="AY6" s="32">
         <f t="shared" si="11"/>
         <v>1035.15625</v>
       </c>
-      <c r="AZ6" s="27">
+      <c r="AZ6" s="32">
         <f t="shared" si="11"/>
         <v>938.589434164655</v>
       </c>
@@ -15767,111 +15749,111 @@
       <c r="L7">
         <v>355.9</v>
       </c>
-      <c r="N7" s="24">
+      <c r="N7" s="18">
         <v>5</v>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="18">
         <v>14</v>
       </c>
-      <c r="P7" s="24">
+      <c r="P7" s="18">
         <v>25</v>
       </c>
-      <c r="Q7" s="24">
+      <c r="Q7" s="18">
         <v>31</v>
       </c>
-      <c r="S7" s="22">
+      <c r="S7" s="26">
         <v>56</v>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="26">
         <v>94</v>
       </c>
-      <c r="U7" s="22">
+      <c r="U7" s="26">
         <v>128</v>
       </c>
-      <c r="V7" s="22">
+      <c r="V7" s="26">
         <v>159</v>
       </c>
-      <c r="X7" s="25">
+      <c r="X7" s="27">
         <v>534</v>
       </c>
-      <c r="Y7" s="25">
+      <c r="Y7" s="27">
         <v>686</v>
       </c>
-      <c r="Z7" s="25">
+      <c r="Z7" s="27">
         <v>862</v>
       </c>
-      <c r="AA7" s="25">
+      <c r="AA7" s="27">
         <v>1033</v>
       </c>
-      <c r="AC7" s="22">
+      <c r="AC7" s="26">
         <v>51</v>
       </c>
-      <c r="AD7" s="22">
+      <c r="AD7" s="26">
         <v>80</v>
       </c>
-      <c r="AE7" s="25">
+      <c r="AE7" s="27">
         <v>103</v>
       </c>
-      <c r="AF7" s="25">
+      <c r="AF7" s="27">
         <v>129</v>
       </c>
-      <c r="AH7" s="25">
+      <c r="AH7" s="27">
         <v>1374</v>
       </c>
-      <c r="AI7" s="25">
+      <c r="AI7" s="27">
         <v>1265</v>
       </c>
-      <c r="AJ7" s="25">
+      <c r="AJ7" s="27">
         <v>1277</v>
       </c>
-      <c r="AK7" s="26">
+      <c r="AK7" s="31">
         <v>1307</v>
       </c>
-      <c r="AM7" s="27">
+      <c r="AM7" s="32">
         <f t="shared" ref="AM7:AP7" si="12">AC7*10000/X7</f>
         <v>955.056179775281</v>
       </c>
-      <c r="AN7" s="27">
+      <c r="AN7" s="32">
         <f t="shared" si="12"/>
         <v>1166.18075801749</v>
       </c>
-      <c r="AO7" s="27">
+      <c r="AO7" s="32">
         <f t="shared" si="12"/>
         <v>1194.89559164733</v>
       </c>
-      <c r="AP7" s="27">
+      <c r="AP7" s="32">
         <f t="shared" si="12"/>
         <v>1248.78993223621</v>
       </c>
-      <c r="AR7" s="27">
+      <c r="AR7" s="32">
         <f t="shared" si="1"/>
         <v>962.264150943396</v>
       </c>
-      <c r="AS7" s="27">
+      <c r="AS7" s="32">
         <f t="shared" si="2"/>
         <v>1174.74302496329</v>
       </c>
-      <c r="AT7" s="27">
+      <c r="AT7" s="32">
         <f t="shared" si="3"/>
         <v>1201.86697782964</v>
       </c>
-      <c r="AU7" s="27">
+      <c r="AU7" s="32">
         <f t="shared" si="4"/>
         <v>1244.74871635289</v>
       </c>
-      <c r="AW7" s="27">
+      <c r="AW7" s="32">
         <f t="shared" ref="AW7:AZ7" si="13">N7*10000/H7</f>
         <v>833.333333333333</v>
       </c>
-      <c r="AX7" s="27">
+      <c r="AX7" s="32">
         <f t="shared" si="13"/>
         <v>765.027322404372</v>
       </c>
-      <c r="AY7" s="27">
+      <c r="AY7" s="32">
         <f t="shared" si="13"/>
         <v>1082.25108225108</v>
       </c>
-      <c r="AZ7" s="27">
+      <c r="AZ7" s="32">
         <f t="shared" si="13"/>
         <v>1106.35260528194</v>
       </c>
@@ -15910,111 +15892,111 @@
       <c r="L8">
         <v>102.5</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="18">
         <v>0.3</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="18">
         <v>1</v>
       </c>
-      <c r="P8" s="24">
+      <c r="P8" s="18">
         <v>3</v>
       </c>
-      <c r="Q8" s="24">
+      <c r="Q8" s="18">
         <v>13</v>
       </c>
-      <c r="S8" s="22">
+      <c r="S8" s="26">
         <v>113</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="26">
         <v>130</v>
       </c>
-      <c r="U8" s="22">
+      <c r="U8" s="26">
         <v>163</v>
       </c>
-      <c r="V8" s="22">
+      <c r="V8" s="26">
         <v>188</v>
       </c>
-      <c r="X8" s="25">
+      <c r="X8" s="27">
         <v>740</v>
       </c>
-      <c r="Y8" s="25">
+      <c r="Y8" s="27">
         <v>933</v>
       </c>
-      <c r="Z8" s="25">
+      <c r="Z8" s="27">
         <v>962</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AA8" s="27">
         <v>1176</v>
       </c>
-      <c r="AC8" s="22">
+      <c r="AC8" s="26">
         <v>112</v>
       </c>
-      <c r="AD8" s="22">
+      <c r="AD8" s="26">
         <v>129</v>
       </c>
-      <c r="AE8" s="25">
+      <c r="AE8" s="27">
         <v>160</v>
       </c>
-      <c r="AF8" s="25">
+      <c r="AF8" s="27">
         <v>180</v>
       </c>
-      <c r="AH8" s="25">
+      <c r="AH8" s="27">
         <v>1524</v>
       </c>
-      <c r="AI8" s="25">
+      <c r="AI8" s="27">
         <v>1632</v>
       </c>
-      <c r="AJ8" s="25">
+      <c r="AJ8" s="27">
         <v>1654</v>
       </c>
-      <c r="AK8" s="26">
+      <c r="AK8" s="31">
         <v>1663</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="32">
         <f t="shared" ref="AM8:AP8" si="14">AC8*10000/X8</f>
         <v>1513.51351351351</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="32">
         <f t="shared" si="14"/>
         <v>1382.63665594855</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="32">
         <f t="shared" si="14"/>
         <v>1663.20166320166</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="32">
         <f t="shared" si="14"/>
         <v>1530.61224489796</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="32">
         <f t="shared" si="1"/>
         <v>1520.91767881242</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="32">
         <f t="shared" si="2"/>
         <v>1382.63665594855</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="32">
         <f t="shared" si="3"/>
         <v>1598.4015984016</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="32">
         <f t="shared" si="4"/>
         <v>1537.7855887522</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="32">
         <f t="shared" ref="AW8:AZ8" si="15">N8*10000/H8</f>
         <v>1500</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="32">
         <f t="shared" si="15"/>
         <v>769.230769230769</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="32">
         <f t="shared" si="15"/>
         <v>375</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="32">
         <f t="shared" si="15"/>
         <v>1442.84128745838</v>
       </c>
@@ -16053,111 +16035,111 @@
       <c r="L9">
         <v>160</v>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="18">
         <v>3</v>
       </c>
-      <c r="O9" s="24">
+      <c r="O9" s="18">
         <v>7</v>
       </c>
-      <c r="P9" s="24">
+      <c r="P9" s="18">
         <v>10</v>
       </c>
-      <c r="Q9" s="24">
+      <c r="Q9" s="18">
         <v>12</v>
       </c>
-      <c r="S9" s="22">
+      <c r="S9" s="26">
         <v>12</v>
       </c>
-      <c r="T9" s="22">
+      <c r="T9" s="26">
         <v>32</v>
       </c>
-      <c r="U9" s="22">
+      <c r="U9" s="26">
         <v>42</v>
       </c>
-      <c r="V9" s="22">
+      <c r="V9" s="26">
         <v>51</v>
       </c>
-      <c r="X9" s="25">
+      <c r="X9" s="27">
         <v>200</v>
       </c>
-      <c r="Y9" s="25">
+      <c r="Y9" s="27">
         <v>248</v>
       </c>
-      <c r="Z9" s="25">
+      <c r="Z9" s="27">
         <v>276</v>
       </c>
-      <c r="AA9" s="25">
+      <c r="AA9" s="27">
         <v>313</v>
       </c>
-      <c r="AC9" s="22">
+      <c r="AC9" s="26">
         <v>10</v>
       </c>
-      <c r="AD9" s="22">
+      <c r="AD9" s="26">
         <v>27</v>
       </c>
-      <c r="AE9" s="25">
+      <c r="AE9" s="27">
         <v>35</v>
       </c>
-      <c r="AF9" s="25">
+      <c r="AF9" s="27">
         <v>43</v>
       </c>
-      <c r="AH9" s="25">
+      <c r="AH9" s="27">
         <v>1072</v>
       </c>
-      <c r="AI9" s="25">
+      <c r="AI9" s="27">
         <v>1235</v>
       </c>
-      <c r="AJ9" s="25">
+      <c r="AJ9" s="27">
         <v>1453</v>
       </c>
-      <c r="AK9" s="26">
+      <c r="AK9" s="31">
         <v>1396</v>
       </c>
-      <c r="AM9" s="27">
+      <c r="AM9" s="32">
         <f t="shared" ref="AM9:AP9" si="16">AC9*10000/X9</f>
         <v>500</v>
       </c>
-      <c r="AN9" s="27">
+      <c r="AN9" s="32">
         <f t="shared" si="16"/>
         <v>1088.70967741935</v>
       </c>
-      <c r="AO9" s="27">
+      <c r="AO9" s="32">
         <f t="shared" si="16"/>
         <v>1268.11594202899</v>
       </c>
-      <c r="AP9" s="27">
+      <c r="AP9" s="32">
         <f t="shared" si="16"/>
         <v>1373.80191693291</v>
       </c>
-      <c r="AR9" s="27">
+      <c r="AR9" s="32">
         <f t="shared" si="1"/>
         <v>486.486486486487</v>
       </c>
-      <c r="AS9" s="27">
+      <c r="AS9" s="32">
         <f t="shared" si="2"/>
         <v>1141.55251141553</v>
       </c>
-      <c r="AT9" s="27">
+      <c r="AT9" s="32">
         <f t="shared" si="3"/>
         <v>1300.81300813008</v>
       </c>
-      <c r="AU9" s="27">
+      <c r="AU9" s="32">
         <f t="shared" si="4"/>
         <v>1383.51839369967</v>
       </c>
-      <c r="AW9" s="27">
+      <c r="AW9" s="32">
         <f t="shared" ref="AW9:AZ9" si="17">N9*10000/H9</f>
         <v>789.473684210526</v>
       </c>
-      <c r="AX9" s="27">
+      <c r="AX9" s="32">
         <f t="shared" si="17"/>
         <v>843.373493975904</v>
       </c>
-      <c r="AY9" s="27">
+      <c r="AY9" s="32">
         <f t="shared" si="17"/>
         <v>1030.92783505155</v>
       </c>
-      <c r="AZ9" s="27">
+      <c r="AZ9" s="32">
         <f t="shared" si="17"/>
         <v>1017.81170483461</v>
       </c>
@@ -16196,111 +16178,111 @@
       <c r="L10">
         <v>80.1</v>
       </c>
-      <c r="N10" s="24">
+      <c r="N10" s="18">
         <v>2</v>
       </c>
-      <c r="O10" s="24">
+      <c r="O10" s="18">
         <v>7</v>
       </c>
-      <c r="P10" s="24">
+      <c r="P10" s="18">
         <v>9</v>
       </c>
-      <c r="Q10" s="24">
+      <c r="Q10" s="18">
         <v>9</v>
       </c>
-      <c r="S10" s="22">
+      <c r="S10" s="26">
         <v>13</v>
       </c>
-      <c r="T10" s="22">
+      <c r="T10" s="26">
         <v>24</v>
       </c>
-      <c r="U10" s="22">
+      <c r="U10" s="26">
         <v>40</v>
       </c>
-      <c r="V10" s="22">
+      <c r="V10" s="26">
         <v>45</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X10" s="27">
         <v>130</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y10" s="27">
         <v>226</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z10" s="27">
         <v>228</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA10" s="27">
         <v>285</v>
       </c>
-      <c r="AC10" s="22">
+      <c r="AC10" s="26">
         <v>12</v>
       </c>
-      <c r="AD10" s="22">
+      <c r="AD10" s="26">
         <v>20</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE10" s="27">
         <v>34</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF10" s="27">
         <v>39</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH10" s="27">
         <v>1251</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI10" s="27">
         <v>1332</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ10" s="27">
         <v>1531</v>
       </c>
-      <c r="AK10" s="26">
+      <c r="AK10" s="31">
         <v>1504</v>
       </c>
-      <c r="AM10" s="27">
+      <c r="AM10" s="32">
         <f t="shared" ref="AM10:AP10" si="18">AC10*10000/X10</f>
         <v>923.076923076923</v>
       </c>
-      <c r="AN10" s="27">
+      <c r="AN10" s="32">
         <f t="shared" si="18"/>
         <v>884.955752212389</v>
       </c>
-      <c r="AO10" s="27">
+      <c r="AO10" s="32">
         <f t="shared" si="18"/>
         <v>1491.22807017544</v>
       </c>
-      <c r="AP10" s="27">
+      <c r="AP10" s="32">
         <f t="shared" si="18"/>
         <v>1368.42105263158</v>
       </c>
-      <c r="AR10" s="27">
+      <c r="AR10" s="32">
         <f t="shared" si="1"/>
         <v>1028.03738317757</v>
       </c>
-      <c r="AS10" s="27">
+      <c r="AS10" s="32">
         <f t="shared" si="2"/>
         <v>837.43842364532</v>
       </c>
-      <c r="AT10" s="27">
+      <c r="AT10" s="32">
         <f t="shared" si="3"/>
         <v>1512.19512195122</v>
       </c>
-      <c r="AU10" s="27">
+      <c r="AU10" s="32">
         <f t="shared" si="4"/>
         <v>1379.78613314936</v>
       </c>
-      <c r="AW10" s="27">
+      <c r="AW10" s="32">
         <f t="shared" ref="AW10:AZ10" si="19">N10*10000/H10</f>
         <v>384.615384615385</v>
       </c>
-      <c r="AX10" s="27">
+      <c r="AX10" s="32">
         <f t="shared" si="19"/>
         <v>1129.03225806452</v>
       </c>
-      <c r="AY10" s="27">
+      <c r="AY10" s="32">
         <f t="shared" si="19"/>
         <v>1304.34782608696</v>
       </c>
-      <c r="AZ10" s="27">
+      <c r="AZ10" s="32">
         <f t="shared" si="19"/>
         <v>1184.21052631579</v>
       </c>
@@ -16339,111 +16321,111 @@
       <c r="L11">
         <v>89.8</v>
       </c>
-      <c r="N11" s="24">
+      <c r="N11" s="18">
         <v>1</v>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="18">
         <v>5</v>
       </c>
-      <c r="P11" s="24">
+      <c r="P11" s="18">
         <v>9</v>
       </c>
-      <c r="Q11" s="24">
+      <c r="Q11" s="18">
         <v>10</v>
       </c>
-      <c r="S11" s="22">
+      <c r="S11" s="26">
         <v>6</v>
       </c>
-      <c r="T11" s="22">
+      <c r="T11" s="26">
         <v>20</v>
       </c>
       <c r="U11" s="28">
         <v>32</v>
       </c>
-      <c r="V11" s="22">
+      <c r="V11" s="26">
         <v>43</v>
       </c>
-      <c r="X11" s="25">
+      <c r="X11" s="27">
         <v>73</v>
       </c>
-      <c r="Y11" s="25">
+      <c r="Y11" s="27">
         <v>144</v>
       </c>
-      <c r="Z11" s="25">
+      <c r="Z11" s="27">
         <v>198</v>
       </c>
-      <c r="AA11" s="25">
+      <c r="AA11" s="27">
         <v>238</v>
       </c>
-      <c r="AC11" s="22">
+      <c r="AC11" s="26">
         <v>5</v>
       </c>
-      <c r="AD11" s="22">
+      <c r="AD11" s="26">
         <v>16</v>
       </c>
-      <c r="AE11" s="25">
+      <c r="AE11" s="27">
         <v>23</v>
       </c>
-      <c r="AF11" s="25">
+      <c r="AF11" s="27">
         <v>33</v>
       </c>
-      <c r="AH11" s="25">
+      <c r="AH11" s="27">
         <v>1249</v>
       </c>
-      <c r="AI11" s="25">
+      <c r="AI11" s="27">
         <v>1447</v>
       </c>
-      <c r="AJ11" s="25">
+      <c r="AJ11" s="27">
         <v>1604</v>
       </c>
-      <c r="AK11" s="26">
+      <c r="AK11" s="31">
         <v>1566</v>
       </c>
-      <c r="AM11" s="27">
+      <c r="AM11" s="32">
         <f t="shared" ref="AM11:AP11" si="20">AC11*10000/X11</f>
         <v>684.931506849315</v>
       </c>
-      <c r="AN11" s="27">
+      <c r="AN11" s="32">
         <f t="shared" si="20"/>
         <v>1111.11111111111</v>
       </c>
-      <c r="AO11" s="27">
+      <c r="AO11" s="32">
         <f t="shared" si="20"/>
         <v>1161.61616161616</v>
       </c>
-      <c r="AP11" s="27">
+      <c r="AP11" s="32">
         <f t="shared" si="20"/>
         <v>1386.55462184874</v>
       </c>
-      <c r="AR11" s="27">
+      <c r="AR11" s="32">
         <f t="shared" si="1"/>
         <v>781.25</v>
       </c>
-      <c r="AS11" s="27">
+      <c r="AS11" s="32">
         <f t="shared" si="2"/>
         <v>1063.82978723404</v>
       </c>
-      <c r="AT11" s="27">
+      <c r="AT11" s="32">
         <f t="shared" si="3"/>
         <v>1179.48717948718</v>
       </c>
-      <c r="AU11" s="27">
+      <c r="AU11" s="32">
         <f t="shared" si="4"/>
         <v>1404.31507723733</v>
       </c>
-      <c r="AW11" s="27">
+      <c r="AW11" s="32">
         <f t="shared" ref="AW11:AZ11" si="21">N11*10000/H11</f>
         <v>333.333333333333</v>
       </c>
-      <c r="AX11" s="27">
+      <c r="AX11" s="32">
         <f t="shared" si="21"/>
         <v>675.675675675676</v>
       </c>
-      <c r="AY11" s="27">
+      <c r="AY11" s="32">
         <f t="shared" si="21"/>
         <v>1125</v>
       </c>
-      <c r="AZ11" s="27">
+      <c r="AZ11" s="32">
         <f t="shared" si="21"/>
         <v>1209.18984280532</v>
       </c>
@@ -16479,22 +16461,22 @@
       <c r="L12">
         <v>144.2</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="18">
         <v>2</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="18">
         <v>5</v>
       </c>
-      <c r="P12" s="24">
+      <c r="P12" s="18">
         <v>7</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="Q12" s="18">
         <v>9</v>
       </c>
-      <c r="S12" s="22">
+      <c r="S12" s="26">
         <v>3</v>
       </c>
-      <c r="T12" s="22">
+      <c r="T12" s="26">
         <v>6</v>
       </c>
       <c r="U12" s="28">
@@ -16503,84 +16485,84 @@
       <c r="V12" s="28">
         <v>10</v>
       </c>
-      <c r="X12" s="25">
+      <c r="X12" s="27">
         <v>7</v>
       </c>
-      <c r="Y12" s="25">
+      <c r="Y12" s="27">
         <v>13</v>
       </c>
-      <c r="Z12" s="25">
+      <c r="Z12" s="27">
         <v>15</v>
       </c>
-      <c r="AA12" s="25">
+      <c r="AA12" s="27">
         <v>28</v>
       </c>
-      <c r="AC12" s="22">
+      <c r="AC12" s="26">
         <v>1</v>
       </c>
-      <c r="AD12" s="22">
+      <c r="AD12" s="26">
         <v>1</v>
       </c>
-      <c r="AE12" s="25">
+      <c r="AE12" s="27">
         <v>1</v>
       </c>
-      <c r="AF12" s="25">
+      <c r="AF12" s="27">
         <v>2</v>
       </c>
-      <c r="AH12" s="25">
+      <c r="AH12" s="27">
         <v>893</v>
       </c>
-      <c r="AI12" s="25">
+      <c r="AI12" s="27">
         <v>946</v>
       </c>
-      <c r="AJ12" s="25">
+      <c r="AJ12" s="27">
         <v>861</v>
       </c>
-      <c r="AK12" s="26">
+      <c r="AK12" s="31">
         <v>867</v>
       </c>
-      <c r="AM12" s="27">
+      <c r="AM12" s="32">
         <f t="shared" ref="AM12:AP12" si="22">AC12*10000/X12</f>
         <v>1428.57142857143</v>
       </c>
-      <c r="AN12" s="27">
+      <c r="AN12" s="32">
         <f t="shared" si="22"/>
         <v>769.230769230769</v>
       </c>
-      <c r="AO12" s="27">
+      <c r="AO12" s="32">
         <f t="shared" si="22"/>
         <v>666.666666666667</v>
       </c>
-      <c r="AP12" s="27">
+      <c r="AP12" s="32">
         <f t="shared" si="22"/>
         <v>714.285714285714</v>
       </c>
-      <c r="AR12" s="27"/>
-      <c r="AS12" s="27">
+      <c r="AR12" s="32"/>
+      <c r="AS12" s="32">
         <f t="shared" si="2"/>
         <v>1428.57142857143</v>
       </c>
-      <c r="AT12" s="27">
+      <c r="AT12" s="32">
         <f t="shared" si="3"/>
         <v>1666.66666666667</v>
       </c>
-      <c r="AU12" s="27">
+      <c r="AU12" s="32">
         <f t="shared" si="4"/>
         <v>507.61421319797</v>
       </c>
-      <c r="AW12" s="27">
+      <c r="AW12" s="32">
         <f t="shared" ref="AW12:AZ12" si="23">N12*10000/H12</f>
         <v>338.983050847458</v>
       </c>
-      <c r="AX12" s="27">
+      <c r="AX12" s="32">
         <f t="shared" si="23"/>
         <v>609.756097560976</v>
       </c>
-      <c r="AY12" s="27">
+      <c r="AY12" s="32">
         <f t="shared" si="23"/>
         <v>679.611650485437</v>
       </c>
-      <c r="AZ12" s="27">
+      <c r="AZ12" s="32">
         <f t="shared" si="23"/>
         <v>769.88879384089</v>
       </c>
@@ -16619,111 +16601,111 @@
       <c r="L13">
         <v>974.9</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13" s="18">
         <v>19</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="18">
         <v>40</v>
       </c>
-      <c r="P13" s="24">
+      <c r="P13" s="18">
         <v>53</v>
       </c>
-      <c r="Q13" s="24">
+      <c r="Q13" s="18">
         <v>61</v>
       </c>
-      <c r="S13" s="22">
+      <c r="S13" s="26">
         <v>81</v>
       </c>
-      <c r="T13" s="22">
+      <c r="T13" s="26">
         <v>120</v>
       </c>
-      <c r="U13" s="22">
+      <c r="U13" s="26">
         <v>154</v>
       </c>
-      <c r="V13" s="22">
+      <c r="V13" s="26">
         <v>167</v>
       </c>
-      <c r="X13" s="25">
+      <c r="X13" s="27">
         <v>571</v>
       </c>
-      <c r="Y13" s="25">
+      <c r="Y13" s="27">
         <v>776</v>
       </c>
-      <c r="Z13" s="25">
+      <c r="Z13" s="27">
         <v>815</v>
       </c>
-      <c r="AA13" s="25">
+      <c r="AA13" s="27">
         <v>898</v>
       </c>
-      <c r="AC13" s="22">
+      <c r="AC13" s="26">
         <v>60</v>
       </c>
-      <c r="AD13" s="22">
+      <c r="AD13" s="26">
         <v>75</v>
       </c>
-      <c r="AE13" s="25">
+      <c r="AE13" s="27">
         <v>95</v>
       </c>
-      <c r="AF13" s="25">
+      <c r="AF13" s="27">
         <v>100</v>
       </c>
-      <c r="AH13" s="25">
+      <c r="AH13" s="27">
         <v>1188</v>
       </c>
-      <c r="AI13" s="25">
+      <c r="AI13" s="27">
         <v>1059</v>
       </c>
-      <c r="AJ13" s="25">
+      <c r="AJ13" s="27">
         <v>1165</v>
       </c>
-      <c r="AK13" s="26">
+      <c r="AK13" s="31">
         <v>1192</v>
       </c>
-      <c r="AM13" s="27">
+      <c r="AM13" s="32">
         <f t="shared" ref="AM13:AP13" si="24">AC13*10000/X13</f>
         <v>1050.7880910683</v>
       </c>
-      <c r="AN13" s="27">
+      <c r="AN13" s="32">
         <f t="shared" si="24"/>
         <v>966.494845360825</v>
       </c>
-      <c r="AO13" s="27">
+      <c r="AO13" s="32">
         <f t="shared" si="24"/>
         <v>1165.64417177914</v>
       </c>
-      <c r="AP13" s="27">
+      <c r="AP13" s="32">
         <f t="shared" si="24"/>
         <v>1113.58574610245</v>
       </c>
-      <c r="AR13" s="27">
+      <c r="AR13" s="32">
         <f t="shared" ref="AR13:AR15" si="25">(S13-N13)*10000/B13</f>
         <v>1068.96551724138</v>
       </c>
-      <c r="AS13" s="27">
+      <c r="AS13" s="32">
         <f t="shared" si="2"/>
         <v>1010.10101010101</v>
       </c>
-      <c r="AT13" s="27">
+      <c r="AT13" s="32">
         <f t="shared" si="3"/>
         <v>1230.20706455542</v>
       </c>
-      <c r="AU13" s="27">
+      <c r="AU13" s="32">
         <f t="shared" si="4"/>
         <v>1183.15455793551</v>
       </c>
-      <c r="AW13" s="27">
+      <c r="AW13" s="32">
         <f t="shared" ref="AW13:AZ13" si="26">N13*10000/H13</f>
         <v>581.039755351682</v>
       </c>
-      <c r="AX13" s="27">
+      <c r="AX13" s="32">
         <f t="shared" si="26"/>
         <v>740.740740740741</v>
       </c>
-      <c r="AY13" s="27">
+      <c r="AY13" s="32">
         <f t="shared" si="26"/>
         <v>796.992481203008</v>
       </c>
-      <c r="AZ13" s="27">
+      <c r="AZ13" s="32">
         <f t="shared" si="26"/>
         <v>774.013450069788</v>
       </c>
@@ -16762,111 +16744,111 @@
       <c r="L14">
         <v>1264.8</v>
       </c>
-      <c r="N14" s="24">
+      <c r="N14" s="18">
         <v>31</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="18">
         <v>63</v>
       </c>
-      <c r="P14" s="24">
+      <c r="P14" s="18">
         <v>75</v>
       </c>
-      <c r="Q14" s="24">
+      <c r="Q14" s="18">
         <v>88</v>
       </c>
-      <c r="S14" s="22">
+      <c r="S14" s="26">
         <v>56</v>
       </c>
-      <c r="T14" s="22">
+      <c r="T14" s="26">
         <v>100</v>
       </c>
-      <c r="U14" s="22">
+      <c r="U14" s="26">
         <v>119</v>
       </c>
-      <c r="V14" s="22">
+      <c r="V14" s="26">
         <v>131</v>
       </c>
-      <c r="X14" s="25">
+      <c r="X14" s="27">
         <v>328</v>
       </c>
-      <c r="Y14" s="25">
+      <c r="Y14" s="27">
         <v>376</v>
       </c>
-      <c r="Z14" s="25">
+      <c r="Z14" s="27">
         <v>428</v>
       </c>
-      <c r="AA14" s="25">
+      <c r="AA14" s="27">
         <v>462</v>
       </c>
-      <c r="AC14" s="22">
+      <c r="AC14" s="26">
         <v>27</v>
       </c>
-      <c r="AD14" s="22">
+      <c r="AD14" s="26">
         <v>38</v>
       </c>
-      <c r="AE14" s="25">
+      <c r="AE14" s="27">
         <v>45</v>
       </c>
-      <c r="AF14" s="25">
+      <c r="AF14" s="27">
         <v>44</v>
       </c>
-      <c r="AH14" s="25">
+      <c r="AH14" s="27">
         <v>1044</v>
       </c>
-      <c r="AI14" s="25">
+      <c r="AI14" s="27">
         <v>1085</v>
       </c>
-      <c r="AJ14" s="25">
+      <c r="AJ14" s="27">
         <v>998</v>
       </c>
-      <c r="AK14" s="26">
+      <c r="AK14" s="31">
         <v>1104</v>
       </c>
-      <c r="AM14" s="27">
+      <c r="AM14" s="32">
         <f t="shared" ref="AM14:AP14" si="27">AC14*10000/X14</f>
         <v>823.170731707317</v>
       </c>
-      <c r="AN14" s="27">
+      <c r="AN14" s="32">
         <f t="shared" si="27"/>
         <v>1010.63829787234</v>
       </c>
-      <c r="AO14" s="27">
+      <c r="AO14" s="32">
         <f t="shared" si="27"/>
         <v>1051.40186915888</v>
       </c>
-      <c r="AP14" s="27">
+      <c r="AP14" s="32">
         <f t="shared" si="27"/>
         <v>952.380952380952</v>
       </c>
-      <c r="AR14" s="27">
+      <c r="AR14" s="32">
         <f t="shared" si="25"/>
         <v>793.650793650794</v>
       </c>
-      <c r="AS14" s="27">
+      <c r="AS14" s="32">
         <f t="shared" si="2"/>
         <v>1024.93074792244</v>
       </c>
-      <c r="AT14" s="27">
+      <c r="AT14" s="32">
         <f t="shared" si="3"/>
         <v>1062.80193236715</v>
       </c>
-      <c r="AU14" s="27">
+      <c r="AU14" s="32">
         <f t="shared" si="4"/>
         <v>1043.25884950385</v>
       </c>
-      <c r="AW14" s="27">
+      <c r="AW14" s="32">
         <f t="shared" ref="AW14:AZ14" si="28">N14*10000/H14</f>
         <v>621.24248496994</v>
       </c>
-      <c r="AX14" s="27">
+      <c r="AX14" s="32">
         <f t="shared" si="28"/>
         <v>810.810810810811</v>
       </c>
-      <c r="AY14" s="27">
+      <c r="AY14" s="32">
         <f t="shared" si="28"/>
         <v>810.810810810811</v>
       </c>
-      <c r="AZ14" s="27">
+      <c r="AZ14" s="32">
         <f t="shared" si="28"/>
         <v>824.587706146927</v>
       </c>
@@ -16905,111 +16887,111 @@
       <c r="L15">
         <v>759.8</v>
       </c>
-      <c r="N15" s="24">
+      <c r="N15" s="18">
         <v>18</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="18">
         <v>36</v>
       </c>
-      <c r="P15" s="24">
+      <c r="P15" s="18">
         <v>46</v>
       </c>
-      <c r="Q15" s="24">
+      <c r="Q15" s="18">
         <v>45</v>
       </c>
-      <c r="S15" s="22">
+      <c r="S15" s="26">
         <v>62</v>
       </c>
-      <c r="T15" s="22">
+      <c r="T15" s="26">
         <v>104</v>
       </c>
-      <c r="U15" s="22">
+      <c r="U15" s="26">
         <v>125</v>
       </c>
-      <c r="V15" s="22">
+      <c r="V15" s="26">
         <v>130</v>
       </c>
-      <c r="X15" s="25">
+      <c r="X15" s="27">
         <v>608</v>
       </c>
-      <c r="Y15" s="25">
+      <c r="Y15" s="27">
         <v>743</v>
       </c>
-      <c r="Z15" s="25">
+      <c r="Z15" s="27">
         <v>859</v>
       </c>
-      <c r="AA15" s="25">
+      <c r="AA15" s="27">
         <v>887</v>
       </c>
-      <c r="AC15" s="22">
+      <c r="AC15" s="26">
         <v>48</v>
       </c>
-      <c r="AD15" s="22">
+      <c r="AD15" s="26">
         <v>73</v>
       </c>
-      <c r="AE15" s="25">
+      <c r="AE15" s="27">
         <v>86</v>
       </c>
-      <c r="AF15" s="25">
+      <c r="AF15" s="27">
         <v>89</v>
       </c>
-      <c r="AH15" s="25">
+      <c r="AH15" s="27">
         <v>992</v>
       </c>
-      <c r="AI15" s="25">
+      <c r="AI15" s="27">
         <v>1065</v>
       </c>
-      <c r="AJ15" s="25">
+      <c r="AJ15" s="27">
         <v>1071</v>
       </c>
-      <c r="AK15" s="26">
+      <c r="AK15" s="31">
         <v>1102</v>
       </c>
-      <c r="AM15" s="27">
+      <c r="AM15" s="32">
         <f t="shared" ref="AM15:AP15" si="29">AC15*10000/X15</f>
         <v>789.473684210526</v>
       </c>
-      <c r="AN15" s="27">
+      <c r="AN15" s="32">
         <f t="shared" si="29"/>
         <v>982.50336473755</v>
       </c>
-      <c r="AO15" s="27">
+      <c r="AO15" s="32">
         <f t="shared" si="29"/>
         <v>1001.1641443539</v>
       </c>
-      <c r="AP15" s="27">
+      <c r="AP15" s="32">
         <f t="shared" si="29"/>
         <v>1003.38218714769</v>
       </c>
-      <c r="AR15" s="27">
+      <c r="AR15" s="32">
         <f t="shared" si="25"/>
         <v>778.761061946903</v>
       </c>
-      <c r="AS15" s="27">
+      <c r="AS15" s="32">
         <f t="shared" si="2"/>
         <v>1004.43131462334</v>
       </c>
-      <c r="AT15" s="27">
+      <c r="AT15" s="32">
         <f t="shared" si="3"/>
         <v>1021.99223803364</v>
       </c>
-      <c r="AU15" s="27">
+      <c r="AU15" s="32">
         <f t="shared" si="4"/>
         <v>1029.60414748777</v>
       </c>
-      <c r="AW15" s="27">
+      <c r="AW15" s="32">
         <f t="shared" ref="AW15:AZ15" si="30">N15*10000/H15</f>
         <v>557.275541795666</v>
       </c>
-      <c r="AX15" s="27">
+      <c r="AX15" s="32">
         <f t="shared" si="30"/>
         <v>816.326530612245</v>
       </c>
-      <c r="AY15" s="27">
+      <c r="AY15" s="32">
         <f t="shared" si="30"/>
         <v>958.333333333333</v>
       </c>
-      <c r="AZ15" s="27">
+      <c r="AZ15" s="32">
         <f t="shared" si="30"/>
         <v>827.053850395148</v>
       </c>
@@ -17045,108 +17027,108 @@
       <c r="L16">
         <v>237.9</v>
       </c>
-      <c r="N16" s="24">
+      <c r="N16" s="18">
         <v>3</v>
       </c>
-      <c r="O16" s="24">
+      <c r="O16" s="18">
         <v>9</v>
       </c>
-      <c r="P16" s="23">
+      <c r="P16" s="17">
         <v>11</v>
       </c>
-      <c r="Q16" s="23">
+      <c r="Q16" s="17">
         <v>15</v>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="26">
         <v>6</v>
       </c>
-      <c r="T16" s="22">
+      <c r="T16" s="26">
         <v>14</v>
       </c>
-      <c r="U16" s="22">
+      <c r="U16" s="26">
         <v>16</v>
       </c>
-      <c r="V16" s="22">
+      <c r="V16" s="26">
         <v>19</v>
       </c>
-      <c r="X16" s="25">
+      <c r="X16" s="27">
         <v>60</v>
       </c>
-      <c r="Y16" s="25">
+      <c r="Y16" s="27">
         <v>67</v>
       </c>
-      <c r="Z16" s="25">
+      <c r="Z16" s="27">
         <v>72</v>
       </c>
-      <c r="AA16" s="25">
+      <c r="AA16" s="27">
         <v>72</v>
       </c>
-      <c r="AC16" s="22">
+      <c r="AC16" s="26">
         <v>4</v>
       </c>
-      <c r="AD16" s="22">
+      <c r="AD16" s="26">
         <v>7</v>
       </c>
-      <c r="AE16" s="25">
+      <c r="AE16" s="27">
         <v>7</v>
       </c>
-      <c r="AF16" s="25">
+      <c r="AF16" s="27">
         <v>8</v>
       </c>
-      <c r="AH16" s="25">
+      <c r="AH16" s="27">
         <v>843</v>
       </c>
-      <c r="AI16" s="25">
+      <c r="AI16" s="27">
         <v>1099</v>
       </c>
-      <c r="AJ16" s="25">
+      <c r="AJ16" s="27">
         <v>1063</v>
       </c>
-      <c r="AK16" s="26">
+      <c r="AK16" s="31">
         <v>1040</v>
       </c>
-      <c r="AM16" s="27">
+      <c r="AM16" s="32">
         <f t="shared" ref="AM16:AP16" si="31">AC16*10000/X16</f>
         <v>666.666666666667</v>
       </c>
-      <c r="AN16" s="27">
+      <c r="AN16" s="32">
         <f t="shared" si="31"/>
         <v>1044.77611940299</v>
       </c>
-      <c r="AO16" s="27">
+      <c r="AO16" s="32">
         <f t="shared" si="31"/>
         <v>972.222222222222</v>
       </c>
-      <c r="AP16" s="27">
+      <c r="AP16" s="32">
         <f t="shared" si="31"/>
         <v>1111.11111111111</v>
       </c>
-      <c r="AR16" s="27"/>
-      <c r="AS16" s="27">
+      <c r="AR16" s="32"/>
+      <c r="AS16" s="32">
         <f t="shared" si="2"/>
         <v>1351.35135135135</v>
       </c>
-      <c r="AT16" s="27">
+      <c r="AT16" s="32">
         <f t="shared" si="3"/>
         <v>1315.78947368421</v>
       </c>
-      <c r="AU16" s="27">
+      <c r="AU16" s="32">
         <f t="shared" si="4"/>
         <v>1058.20105820106</v>
       </c>
-      <c r="AW16" s="27">
+      <c r="AW16" s="32">
         <f t="shared" ref="AW16:AZ16" si="32">N16*10000/H16</f>
         <v>275.229357798165</v>
       </c>
-      <c r="AX16" s="27">
+      <c r="AX16" s="32">
         <f t="shared" si="32"/>
         <v>810.810810810811</v>
       </c>
-      <c r="AY16" s="27">
+      <c r="AY16" s="32">
         <f t="shared" si="32"/>
         <v>839.69465648855</v>
       </c>
-      <c r="AZ16" s="27">
+      <c r="AZ16" s="32">
         <f t="shared" si="32"/>
         <v>912.964090079123</v>
       </c>
@@ -17185,111 +17167,111 @@
       <c r="L17">
         <v>359.2</v>
       </c>
-      <c r="N17" s="24">
+      <c r="N17" s="18">
         <v>8</v>
       </c>
-      <c r="O17" s="24">
+      <c r="O17" s="18">
         <v>21</v>
       </c>
-      <c r="P17" s="24">
+      <c r="P17" s="18">
         <v>24</v>
       </c>
-      <c r="Q17" s="24">
+      <c r="Q17" s="18">
         <v>26</v>
       </c>
-      <c r="S17" s="22">
+      <c r="S17" s="26">
         <v>30</v>
       </c>
-      <c r="T17" s="22">
+      <c r="T17" s="26">
         <v>52</v>
       </c>
-      <c r="U17" s="22">
+      <c r="U17" s="26">
         <v>56</v>
       </c>
-      <c r="V17" s="22">
+      <c r="V17" s="26">
         <v>62</v>
       </c>
-      <c r="X17" s="25">
+      <c r="X17" s="27">
         <v>287</v>
       </c>
-      <c r="Y17" s="25">
+      <c r="Y17" s="27">
         <v>309</v>
       </c>
-      <c r="Z17" s="25">
+      <c r="Z17" s="27">
         <v>383</v>
       </c>
-      <c r="AA17" s="25">
+      <c r="AA17" s="27">
         <v>500</v>
       </c>
-      <c r="AC17" s="22">
+      <c r="AC17" s="26">
         <v>23</v>
       </c>
-      <c r="AD17" s="22">
+      <c r="AD17" s="26">
         <v>32</v>
       </c>
-      <c r="AE17" s="25">
+      <c r="AE17" s="27">
         <v>33</v>
       </c>
-      <c r="AF17" s="25">
+      <c r="AF17" s="27">
         <v>38</v>
       </c>
-      <c r="AH17" s="25">
+      <c r="AH17" s="27">
         <v>891</v>
       </c>
-      <c r="AI17" s="25">
+      <c r="AI17" s="27">
         <v>1064</v>
       </c>
-      <c r="AJ17" s="25">
+      <c r="AJ17" s="27">
         <v>917</v>
       </c>
-      <c r="AK17" s="26">
+      <c r="AK17" s="31">
         <v>1004</v>
       </c>
-      <c r="AM17" s="27">
+      <c r="AM17" s="32">
         <f t="shared" ref="AM17:AP17" si="33">AC17*10000/X17</f>
         <v>801.393728222997</v>
       </c>
-      <c r="AN17" s="27">
+      <c r="AN17" s="32">
         <f t="shared" si="33"/>
         <v>1035.59870550162</v>
       </c>
-      <c r="AO17" s="27">
+      <c r="AO17" s="32">
         <f t="shared" si="33"/>
         <v>861.618798955614</v>
       </c>
-      <c r="AP17" s="27">
+      <c r="AP17" s="32">
         <f t="shared" si="33"/>
         <v>760</v>
       </c>
-      <c r="AR17" s="27">
+      <c r="AR17" s="32">
         <f t="shared" ref="AR17:AR22" si="34">(S17-N17)*10000/B17</f>
         <v>794.223826714801</v>
       </c>
-      <c r="AS17" s="27">
+      <c r="AS17" s="32">
         <f t="shared" si="2"/>
         <v>1054.42176870748</v>
       </c>
-      <c r="AT17" s="27">
+      <c r="AT17" s="32">
         <f t="shared" si="3"/>
         <v>871.934604904632</v>
       </c>
-      <c r="AU17" s="27">
+      <c r="AU17" s="32">
         <f t="shared" si="4"/>
         <v>755.255318256199</v>
       </c>
-      <c r="AW17" s="27">
+      <c r="AW17" s="32">
         <f t="shared" ref="AW17:AZ17" si="35">N17*10000/H17</f>
         <v>465.116279069767</v>
       </c>
-      <c r="AX17" s="27">
+      <c r="AX17" s="32">
         <f t="shared" si="35"/>
         <v>867.768595041322</v>
       </c>
-      <c r="AY17" s="27">
+      <c r="AY17" s="32">
         <f t="shared" si="35"/>
         <v>912.54752851711</v>
       </c>
-      <c r="AZ17" s="27">
+      <c r="AZ17" s="32">
         <f t="shared" si="35"/>
         <v>868.983957219251</v>
       </c>
@@ -17328,28 +17310,28 @@
       <c r="L18">
         <v>2334.4</v>
       </c>
-      <c r="N18" s="24">
+      <c r="N18" s="18">
         <v>20</v>
       </c>
-      <c r="O18" s="24">
+      <c r="O18" s="18">
         <v>60</v>
       </c>
-      <c r="P18" s="24">
+      <c r="P18" s="18">
         <v>80</v>
       </c>
-      <c r="Q18" s="24">
+      <c r="Q18" s="18">
         <v>117</v>
       </c>
-      <c r="S18" s="22">
+      <c r="S18" s="26">
         <v>73</v>
       </c>
-      <c r="T18" s="22">
+      <c r="T18" s="26">
         <v>137</v>
       </c>
-      <c r="U18" s="22">
+      <c r="U18" s="26">
         <v>167</v>
       </c>
-      <c r="V18" s="22">
+      <c r="V18" s="26">
         <v>206</v>
       </c>
       <c r="X18" s="29">
@@ -17364,10 +17346,10 @@
       <c r="AA18" s="29">
         <v>905</v>
       </c>
-      <c r="AC18" s="22">
+      <c r="AC18" s="26">
         <v>56</v>
       </c>
-      <c r="AD18" s="22">
+      <c r="AD18" s="26">
         <v>82</v>
       </c>
       <c r="AE18" s="29">
@@ -17376,63 +17358,63 @@
       <c r="AF18" s="29">
         <v>99</v>
       </c>
-      <c r="AH18" s="25">
+      <c r="AH18" s="27">
         <v>1154</v>
       </c>
-      <c r="AI18" s="25">
+      <c r="AI18" s="27">
         <v>1227</v>
       </c>
-      <c r="AJ18" s="25">
+      <c r="AJ18" s="27">
         <v>1225</v>
       </c>
-      <c r="AK18" s="26">
+      <c r="AK18" s="31">
         <v>1284</v>
       </c>
-      <c r="AM18" s="27">
+      <c r="AM18" s="32">
         <f t="shared" ref="AM18:AP18" si="36">AC18*10000/X18</f>
         <v>875</v>
       </c>
-      <c r="AN18" s="27">
+      <c r="AN18" s="32">
         <f t="shared" si="36"/>
         <v>1158.19209039548</v>
       </c>
-      <c r="AO18" s="27">
+      <c r="AO18" s="32">
         <f t="shared" si="36"/>
         <v>1238.34886817577</v>
       </c>
-      <c r="AP18" s="27">
+      <c r="AP18" s="32">
         <f t="shared" si="36"/>
         <v>1093.9226519337</v>
       </c>
-      <c r="AR18" s="27">
+      <c r="AR18" s="32">
         <f t="shared" si="34"/>
         <v>916.955017301038</v>
       </c>
-      <c r="AS18" s="27">
+      <c r="AS18" s="32">
         <f t="shared" si="2"/>
         <v>1188.27160493827</v>
       </c>
-      <c r="AT18" s="27">
+      <c r="AT18" s="32">
         <f t="shared" si="3"/>
         <v>1285.08124076809</v>
       </c>
-      <c r="AU18" s="27">
+      <c r="AU18" s="32">
         <f t="shared" si="4"/>
         <v>1105.56259471814</v>
       </c>
-      <c r="AW18" s="27">
+      <c r="AW18" s="32">
         <f t="shared" ref="AW18:AZ18" si="37">N18*10000/H18</f>
         <v>421.940928270042</v>
       </c>
-      <c r="AX18" s="27">
+      <c r="AX18" s="32">
         <f t="shared" si="37"/>
         <v>841.514726507714</v>
       </c>
-      <c r="AY18" s="27">
+      <c r="AY18" s="32">
         <f t="shared" si="37"/>
         <v>848.356309650053</v>
       </c>
-      <c r="AZ18" s="27">
+      <c r="AZ18" s="32">
         <f t="shared" si="37"/>
         <v>797.328608423061</v>
       </c>
@@ -17471,111 +17453,111 @@
       <c r="L19">
         <v>929.8</v>
       </c>
-      <c r="N19" s="24">
+      <c r="N19" s="18">
         <v>4</v>
       </c>
-      <c r="O19" s="24">
+      <c r="O19" s="18">
         <v>27</v>
       </c>
-      <c r="P19" s="24">
+      <c r="P19" s="18">
         <v>38</v>
       </c>
-      <c r="Q19" s="24">
+      <c r="Q19" s="18">
         <v>49</v>
       </c>
-      <c r="S19" s="22">
+      <c r="S19" s="26">
         <v>44</v>
       </c>
-      <c r="T19" s="22">
+      <c r="T19" s="26">
         <v>84</v>
       </c>
-      <c r="U19" s="22">
+      <c r="U19" s="26">
         <v>102</v>
       </c>
-      <c r="V19" s="22">
+      <c r="V19" s="26">
         <v>112</v>
       </c>
-      <c r="X19" s="25">
+      <c r="X19" s="27">
         <v>532</v>
       </c>
-      <c r="Y19" s="25">
+      <c r="Y19" s="27">
         <v>602</v>
       </c>
-      <c r="Z19" s="25">
+      <c r="Z19" s="27">
         <v>602</v>
       </c>
-      <c r="AA19" s="25">
+      <c r="AA19" s="27">
         <v>604</v>
       </c>
-      <c r="AC19" s="22">
+      <c r="AC19" s="26">
         <v>40</v>
       </c>
-      <c r="AD19" s="22">
+      <c r="AD19" s="26">
         <v>57</v>
       </c>
-      <c r="AE19" s="25">
+      <c r="AE19" s="27">
         <v>64</v>
       </c>
-      <c r="AF19" s="25">
+      <c r="AF19" s="27">
         <v>63</v>
       </c>
-      <c r="AH19" s="25">
+      <c r="AH19" s="27">
         <v>934</v>
       </c>
-      <c r="AI19" s="25">
+      <c r="AI19" s="27">
         <v>998</v>
       </c>
-      <c r="AJ19" s="25">
+      <c r="AJ19" s="27">
         <v>1055</v>
       </c>
-      <c r="AK19" s="26">
+      <c r="AK19" s="31">
         <v>1061</v>
       </c>
-      <c r="AM19" s="27">
+      <c r="AM19" s="32">
         <f t="shared" ref="AM19:AP19" si="38">AC19*10000/X19</f>
         <v>751.87969924812</v>
       </c>
-      <c r="AN19" s="27">
+      <c r="AN19" s="32">
         <f t="shared" si="38"/>
         <v>946.843853820598</v>
       </c>
-      <c r="AO19" s="27">
+      <c r="AO19" s="32">
         <f t="shared" si="38"/>
         <v>1063.12292358804</v>
       </c>
-      <c r="AP19" s="27">
+      <c r="AP19" s="32">
         <f t="shared" si="38"/>
         <v>1043.04635761589</v>
       </c>
-      <c r="AR19" s="27">
+      <c r="AR19" s="32">
         <f t="shared" si="34"/>
         <v>813.008130081301</v>
       </c>
-      <c r="AS19" s="27">
+      <c r="AS19" s="32">
         <f t="shared" si="2"/>
         <v>950</v>
       </c>
-      <c r="AT19" s="27">
+      <c r="AT19" s="32">
         <f t="shared" si="3"/>
         <v>1066.66666666667</v>
       </c>
-      <c r="AU19" s="27">
+      <c r="AU19" s="32">
         <f t="shared" si="4"/>
         <v>1043.30545665314</v>
       </c>
-      <c r="AW19" s="27">
+      <c r="AW19" s="32">
         <f t="shared" ref="AW19:AZ19" si="39">N19*10000/H19</f>
         <v>189.57345971564</v>
       </c>
-      <c r="AX19" s="27">
+      <c r="AX19" s="32">
         <f t="shared" si="39"/>
         <v>690.537084398977</v>
       </c>
-      <c r="AY19" s="27">
+      <c r="AY19" s="32">
         <f t="shared" si="39"/>
         <v>837.004405286344</v>
       </c>
-      <c r="AZ19" s="27">
+      <c r="AZ19" s="32">
         <f t="shared" si="39"/>
         <v>858.444288717589</v>
       </c>
@@ -17614,111 +17596,111 @@
       <c r="L20">
         <v>239.6</v>
       </c>
-      <c r="N20" s="24">
+      <c r="N20" s="18">
         <v>5</v>
       </c>
-      <c r="O20" s="24">
+      <c r="O20" s="18">
         <v>13</v>
       </c>
-      <c r="P20" s="24">
+      <c r="P20" s="18">
         <v>17</v>
       </c>
-      <c r="Q20" s="24">
+      <c r="Q20" s="18">
         <v>19</v>
       </c>
-      <c r="S20" s="22">
+      <c r="S20" s="26">
         <v>28</v>
       </c>
-      <c r="T20" s="22">
+      <c r="T20" s="26">
         <v>49</v>
       </c>
-      <c r="U20" s="22">
+      <c r="U20" s="26">
         <v>57</v>
       </c>
-      <c r="V20" s="22">
+      <c r="V20" s="26">
         <v>65</v>
       </c>
-      <c r="X20" s="25">
+      <c r="X20" s="27">
         <v>301</v>
       </c>
-      <c r="Y20" s="25">
+      <c r="Y20" s="27">
         <v>338</v>
       </c>
-      <c r="Z20" s="25">
+      <c r="Z20" s="27">
         <v>425</v>
       </c>
-      <c r="AA20" s="25">
+      <c r="AA20" s="27">
         <v>491</v>
       </c>
-      <c r="AC20" s="22">
+      <c r="AC20" s="26">
         <v>23</v>
       </c>
-      <c r="AD20" s="22">
+      <c r="AD20" s="26">
         <v>36</v>
       </c>
-      <c r="AE20" s="25">
+      <c r="AE20" s="27">
         <v>40</v>
       </c>
-      <c r="AF20" s="25">
+      <c r="AF20" s="27">
         <v>46</v>
       </c>
-      <c r="AH20" s="25">
+      <c r="AH20" s="27">
         <v>987</v>
       </c>
-      <c r="AI20" s="25">
+      <c r="AI20" s="27">
         <v>1115</v>
       </c>
-      <c r="AJ20" s="25">
+      <c r="AJ20" s="27">
         <v>1013</v>
       </c>
-      <c r="AK20" s="26">
+      <c r="AK20" s="31">
         <v>1103</v>
       </c>
-      <c r="AM20" s="27">
+      <c r="AM20" s="32">
         <f t="shared" ref="AM20:AP20" si="40">AC20*10000/X20</f>
         <v>764.119601328904</v>
       </c>
-      <c r="AN20" s="27">
+      <c r="AN20" s="32">
         <f t="shared" si="40"/>
         <v>1065.08875739645</v>
       </c>
-      <c r="AO20" s="27">
+      <c r="AO20" s="32">
         <f t="shared" si="40"/>
         <v>941.176470588235</v>
       </c>
-      <c r="AP20" s="27">
+      <c r="AP20" s="32">
         <f t="shared" si="40"/>
         <v>936.863543788187</v>
       </c>
-      <c r="AR20" s="27">
+      <c r="AR20" s="32">
         <f t="shared" si="34"/>
         <v>974.576271186441</v>
       </c>
-      <c r="AS20" s="27">
+      <c r="AS20" s="32">
         <f t="shared" si="2"/>
         <v>1074.62686567164</v>
       </c>
-      <c r="AT20" s="27">
+      <c r="AT20" s="32">
         <f t="shared" si="3"/>
         <v>952.380952380952</v>
       </c>
-      <c r="AU20" s="27">
+      <c r="AU20" s="32">
         <f t="shared" si="4"/>
         <v>947.164683111642</v>
       </c>
-      <c r="AW20" s="27">
+      <c r="AW20" s="32">
         <f t="shared" ref="AW20:AZ20" si="41">N20*10000/H20</f>
         <v>282.485875706215</v>
       </c>
-      <c r="AX20" s="27">
+      <c r="AX20" s="32">
         <f t="shared" si="41"/>
         <v>742.857142857143</v>
       </c>
-      <c r="AY20" s="27">
+      <c r="AY20" s="32">
         <f t="shared" si="41"/>
         <v>845.771144278607</v>
       </c>
-      <c r="AZ20" s="27">
+      <c r="AZ20" s="32">
         <f t="shared" si="41"/>
         <v>896.649362907032</v>
       </c>
@@ -17757,22 +17739,22 @@
       <c r="L21">
         <v>231</v>
       </c>
-      <c r="N21" s="24">
+      <c r="N21" s="18">
         <v>4</v>
       </c>
-      <c r="O21" s="24">
+      <c r="O21" s="18">
         <v>10</v>
       </c>
-      <c r="P21" s="24">
+      <c r="P21" s="18">
         <v>13</v>
       </c>
-      <c r="Q21" s="24">
+      <c r="Q21" s="18">
         <v>14</v>
       </c>
-      <c r="S21" s="22">
+      <c r="S21" s="26">
         <v>6</v>
       </c>
-      <c r="T21" s="22">
+      <c r="T21" s="26">
         <v>20</v>
       </c>
       <c r="U21" s="28">
@@ -17781,87 +17763,87 @@
       <c r="V21" s="28">
         <v>30</v>
       </c>
-      <c r="X21" s="25">
+      <c r="X21" s="27">
         <v>113</v>
       </c>
-      <c r="Y21" s="25">
+      <c r="Y21" s="27">
         <v>160</v>
       </c>
-      <c r="Z21" s="25">
+      <c r="Z21" s="27">
         <v>188</v>
       </c>
-      <c r="AA21" s="25">
+      <c r="AA21" s="27">
         <v>242</v>
       </c>
-      <c r="AC21" s="22">
+      <c r="AC21" s="26">
         <v>3</v>
       </c>
-      <c r="AD21" s="22">
+      <c r="AD21" s="26">
         <v>12</v>
       </c>
-      <c r="AE21" s="25">
+      <c r="AE21" s="27">
         <v>16</v>
       </c>
-      <c r="AF21" s="25">
+      <c r="AF21" s="27">
         <v>20</v>
       </c>
-      <c r="AH21" s="25">
+      <c r="AH21" s="27">
         <v>512</v>
       </c>
-      <c r="AI21" s="25">
+      <c r="AI21" s="27">
         <v>933</v>
       </c>
-      <c r="AJ21" s="25">
+      <c r="AJ21" s="27">
         <v>902</v>
       </c>
-      <c r="AK21" s="26">
+      <c r="AK21" s="31">
         <v>905</v>
       </c>
-      <c r="AM21" s="27">
+      <c r="AM21" s="32">
         <f t="shared" ref="AM21:AP21" si="42">AC21*10000/X21</f>
         <v>265.486725663717</v>
       </c>
-      <c r="AN21" s="27">
+      <c r="AN21" s="32">
         <f t="shared" si="42"/>
         <v>750</v>
       </c>
-      <c r="AO21" s="27">
+      <c r="AO21" s="32">
         <f t="shared" si="42"/>
         <v>851.063829787234</v>
       </c>
-      <c r="AP21" s="27">
+      <c r="AP21" s="32">
         <f t="shared" si="42"/>
         <v>826.446280991736</v>
       </c>
-      <c r="AR21" s="27">
+      <c r="AR21" s="32">
         <f t="shared" si="34"/>
         <v>232.558139534884</v>
       </c>
-      <c r="AS21" s="27">
+      <c r="AS21" s="32">
         <f t="shared" si="2"/>
         <v>793.650793650794</v>
       </c>
-      <c r="AT21" s="27">
+      <c r="AT21" s="32">
         <f t="shared" si="3"/>
         <v>838.709677419355</v>
       </c>
-      <c r="AU21" s="27">
+      <c r="AU21" s="32">
         <f t="shared" si="4"/>
         <v>839.366278459763</v>
       </c>
-      <c r="AW21" s="27">
+      <c r="AW21" s="32">
         <f t="shared" ref="AW21:AZ21" si="43">N21*10000/H21</f>
         <v>444.444444444444</v>
       </c>
-      <c r="AX21" s="27">
+      <c r="AX21" s="32">
         <f t="shared" si="43"/>
         <v>602.409638554217</v>
       </c>
-      <c r="AY21" s="27">
+      <c r="AY21" s="32">
         <f t="shared" si="43"/>
         <v>687.830687830688</v>
       </c>
-      <c r="AZ21" s="27">
+      <c r="AZ21" s="32">
         <f t="shared" si="43"/>
         <v>699.650174912544</v>
       </c>
@@ -17900,111 +17882,111 @@
       <c r="L22">
         <v>511.9</v>
       </c>
-      <c r="N22" s="24">
+      <c r="N22" s="18">
         <v>8</v>
       </c>
-      <c r="O22" s="24">
+      <c r="O22" s="18">
         <v>15</v>
       </c>
-      <c r="P22" s="24">
+      <c r="P22" s="18">
         <v>22</v>
       </c>
-      <c r="Q22" s="24">
+      <c r="Q22" s="18">
         <v>32</v>
       </c>
-      <c r="S22" s="22">
+      <c r="S22" s="26">
         <v>20</v>
       </c>
-      <c r="T22" s="22">
+      <c r="T22" s="26">
         <v>38</v>
       </c>
-      <c r="U22" s="22">
+      <c r="U22" s="26">
         <v>53</v>
       </c>
-      <c r="V22" s="22">
+      <c r="V22" s="26">
         <v>74</v>
       </c>
-      <c r="X22" s="25">
+      <c r="X22" s="27">
         <v>229</v>
       </c>
-      <c r="Y22" s="25">
+      <c r="Y22" s="27">
         <v>370</v>
       </c>
-      <c r="Z22" s="25">
+      <c r="Z22" s="27">
         <v>382</v>
       </c>
-      <c r="AA22" s="25">
+      <c r="AA22" s="27">
         <v>495</v>
       </c>
-      <c r="AC22" s="22">
+      <c r="AC22" s="26">
         <v>12</v>
       </c>
-      <c r="AD22" s="22">
+      <c r="AD22" s="26">
         <v>25</v>
       </c>
-      <c r="AE22" s="25">
+      <c r="AE22" s="27">
         <v>34</v>
       </c>
-      <c r="AF22" s="25">
+      <c r="AF22" s="27">
         <v>47</v>
       </c>
-      <c r="AH22" s="25">
+      <c r="AH22" s="27">
         <v>843</v>
       </c>
-      <c r="AI22" s="25">
+      <c r="AI22" s="27">
         <v>884</v>
       </c>
-      <c r="AJ22" s="25">
+      <c r="AJ22" s="27">
         <v>1020</v>
       </c>
-      <c r="AK22" s="26">
+      <c r="AK22" s="31">
         <v>915</v>
       </c>
-      <c r="AM22" s="27">
+      <c r="AM22" s="32">
         <f t="shared" ref="AM22:AP22" si="44">AC22*10000/X22</f>
         <v>524.017467248908</v>
       </c>
-      <c r="AN22" s="27">
+      <c r="AN22" s="32">
         <f t="shared" si="44"/>
         <v>675.675675675676</v>
       </c>
-      <c r="AO22" s="27">
+      <c r="AO22" s="32">
         <f t="shared" si="44"/>
         <v>890.052356020942</v>
       </c>
-      <c r="AP22" s="27">
+      <c r="AP22" s="32">
         <f t="shared" si="44"/>
         <v>949.49494949495</v>
       </c>
-      <c r="AR22" s="27">
+      <c r="AR22" s="32">
         <f t="shared" si="34"/>
         <v>571.428571428571</v>
       </c>
-      <c r="AS22" s="27">
+      <c r="AS22" s="32">
         <f t="shared" si="2"/>
         <v>723.270440251572</v>
       </c>
-      <c r="AT22" s="27">
+      <c r="AT22" s="32">
         <f t="shared" si="3"/>
         <v>1026.49006622517</v>
       </c>
-      <c r="AU22" s="27">
+      <c r="AU22" s="32">
         <f t="shared" si="4"/>
         <v>1027.34699867913</v>
       </c>
-      <c r="AW22" s="27">
+      <c r="AW22" s="32">
         <f t="shared" ref="AW22:AZ22" si="45">N22*10000/H22</f>
         <v>655.737704918033</v>
       </c>
-      <c r="AX22" s="27">
+      <c r="AX22" s="32">
         <f t="shared" si="45"/>
         <v>717.703349282297</v>
       </c>
-      <c r="AY22" s="27">
+      <c r="AY22" s="32">
         <f t="shared" si="45"/>
         <v>714.285714285714</v>
       </c>
-      <c r="AZ22" s="27">
+      <c r="AZ22" s="32">
         <f t="shared" si="45"/>
         <v>831.384775266303</v>
       </c>
@@ -18040,28 +18022,28 @@
       <c r="L23">
         <v>52.6</v>
       </c>
-      <c r="N23" s="24">
+      <c r="N23" s="18">
         <v>1</v>
       </c>
-      <c r="O23" s="24">
+      <c r="O23" s="18">
         <v>1</v>
       </c>
-      <c r="P23" s="24">
+      <c r="P23" s="18">
         <v>2</v>
       </c>
-      <c r="Q23" s="24">
+      <c r="Q23" s="18">
         <v>3</v>
       </c>
-      <c r="S23" s="22">
+      <c r="S23" s="26">
         <v>4</v>
       </c>
-      <c r="T23" s="22">
+      <c r="T23" s="26">
         <v>9</v>
       </c>
-      <c r="U23" s="22">
+      <c r="U23" s="26">
         <v>14</v>
       </c>
-      <c r="V23" s="22">
+      <c r="V23" s="26">
         <v>19</v>
       </c>
       <c r="X23" s="29">
@@ -18076,10 +18058,10 @@
       <c r="AA23" s="29">
         <v>170</v>
       </c>
-      <c r="AC23" s="22">
+      <c r="AC23" s="26">
         <v>4</v>
       </c>
-      <c r="AD23" s="22">
+      <c r="AD23" s="26">
         <v>8</v>
       </c>
       <c r="AE23" s="29">
@@ -18088,60 +18070,60 @@
       <c r="AF23" s="29">
         <v>15</v>
       </c>
-      <c r="AH23" s="25">
+      <c r="AH23" s="27">
         <v>919</v>
       </c>
-      <c r="AI23" s="25">
+      <c r="AI23" s="27">
         <v>1006</v>
       </c>
-      <c r="AJ23" s="25">
+      <c r="AJ23" s="27">
         <v>1085</v>
       </c>
-      <c r="AK23" s="26">
+      <c r="AK23" s="31">
         <v>1097</v>
       </c>
-      <c r="AM23" s="27">
+      <c r="AM23" s="32">
         <f t="shared" ref="AM23:AP23" si="46">AC23*10000/X23</f>
         <v>579.710144927536</v>
       </c>
-      <c r="AN23" s="27">
+      <c r="AN23" s="32">
         <f t="shared" si="46"/>
         <v>808.080808080808</v>
       </c>
-      <c r="AO23" s="27">
+      <c r="AO23" s="32">
         <f t="shared" si="46"/>
         <v>1090.90909090909</v>
       </c>
-      <c r="AP23" s="27">
+      <c r="AP23" s="32">
         <f t="shared" si="46"/>
         <v>882.352941176471</v>
       </c>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="27">
+      <c r="AR23" s="32"/>
+      <c r="AS23" s="32">
         <f t="shared" si="2"/>
         <v>842.105263157895</v>
       </c>
-      <c r="AT23" s="27">
+      <c r="AT23" s="32">
         <f t="shared" si="3"/>
         <v>1142.85714285714</v>
       </c>
-      <c r="AU23" s="27">
+      <c r="AU23" s="32">
         <f t="shared" si="4"/>
         <v>984.857811153515</v>
       </c>
-      <c r="AW23" s="27">
+      <c r="AW23" s="32">
         <f t="shared" ref="AW23:AZ23" si="47">N23*10000/H23</f>
         <v>26.8096514745308</v>
       </c>
-      <c r="AX23" s="27">
+      <c r="AX23" s="32">
         <f t="shared" si="47"/>
         <v>344.827586206897</v>
       </c>
-      <c r="AY23" s="27">
+      <c r="AY23" s="32">
         <f t="shared" si="47"/>
         <v>666.666666666667</v>
       </c>
-      <c r="AZ23" s="27">
+      <c r="AZ23" s="32">
         <f t="shared" si="47"/>
         <v>702.576112412178</v>
       </c>
@@ -18180,111 +18162,111 @@
       <c r="L24">
         <v>19.4</v>
       </c>
-      <c r="N24" s="24">
+      <c r="N24" s="18">
         <v>0.2</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="18">
         <v>1</v>
       </c>
-      <c r="P24" s="24">
+      <c r="P24" s="18">
         <v>1</v>
       </c>
-      <c r="Q24" s="24">
+      <c r="Q24" s="18">
         <v>1</v>
       </c>
-      <c r="S24" s="22">
+      <c r="S24" s="26">
         <v>3</v>
       </c>
-      <c r="T24" s="22">
+      <c r="T24" s="26">
         <v>6</v>
       </c>
-      <c r="U24" s="22">
+      <c r="U24" s="26">
         <v>14</v>
       </c>
-      <c r="V24" s="22">
+      <c r="V24" s="26">
         <v>15</v>
       </c>
-      <c r="X24" s="25">
+      <c r="X24" s="27">
         <v>33</v>
       </c>
-      <c r="Y24" s="25">
+      <c r="Y24" s="27">
         <v>125</v>
       </c>
-      <c r="Z24" s="25">
+      <c r="Z24" s="27">
         <v>129</v>
       </c>
-      <c r="AA24" s="25">
+      <c r="AA24" s="27">
         <v>129</v>
       </c>
-      <c r="AC24" s="22">
+      <c r="AC24" s="26">
         <v>3</v>
       </c>
-      <c r="AD24" s="22">
+      <c r="AD24" s="26">
         <v>6</v>
       </c>
-      <c r="AE24" s="25">
+      <c r="AE24" s="27">
         <v>13</v>
       </c>
-      <c r="AF24" s="25">
+      <c r="AF24" s="27">
         <v>14</v>
       </c>
-      <c r="AH24" s="25">
+      <c r="AH24" s="27">
         <v>1113</v>
       </c>
-      <c r="AI24" s="25">
+      <c r="AI24" s="27">
         <v>752</v>
       </c>
-      <c r="AJ24" s="25">
+      <c r="AJ24" s="27">
         <v>1061</v>
       </c>
-      <c r="AK24" s="26">
+      <c r="AK24" s="31">
         <v>1023</v>
       </c>
-      <c r="AM24" s="27">
+      <c r="AM24" s="32">
         <f t="shared" ref="AM24:AP24" si="48">AC24*10000/X24</f>
         <v>909.090909090909</v>
       </c>
-      <c r="AN24" s="27">
+      <c r="AN24" s="32">
         <f t="shared" si="48"/>
         <v>480</v>
       </c>
-      <c r="AO24" s="27">
+      <c r="AO24" s="32">
         <f t="shared" si="48"/>
         <v>1007.7519379845</v>
       </c>
-      <c r="AP24" s="27">
+      <c r="AP24" s="32">
         <f t="shared" si="48"/>
         <v>1085.27131782946</v>
       </c>
-      <c r="AR24" s="27">
+      <c r="AR24" s="32">
         <f t="shared" ref="AR24:AR34" si="49">(S24-N24)*10000/B24</f>
         <v>875</v>
       </c>
-      <c r="AS24" s="27">
+      <c r="AS24" s="32">
         <f t="shared" si="2"/>
         <v>406.50406504065</v>
       </c>
-      <c r="AT24" s="27">
+      <c r="AT24" s="32">
         <f t="shared" si="3"/>
         <v>1023.62204724409</v>
       </c>
-      <c r="AU24" s="27">
+      <c r="AU24" s="32">
         <f t="shared" si="4"/>
         <v>1296.17627997408</v>
       </c>
-      <c r="AW24" s="27">
+      <c r="AW24" s="32">
         <f t="shared" ref="AW24:AZ24" si="50">N24*10000/H24</f>
         <v>181.818181818182</v>
       </c>
-      <c r="AX24" s="27">
+      <c r="AX24" s="32">
         <f t="shared" si="50"/>
         <v>769.230769230769</v>
       </c>
-      <c r="AY24" s="27">
+      <c r="AY24" s="32">
         <f t="shared" si="50"/>
         <v>769.230769230769</v>
       </c>
-      <c r="AZ24" s="27">
+      <c r="AZ24" s="32">
         <f t="shared" si="50"/>
         <v>793.650793650794</v>
       </c>
@@ -18317,52 +18299,52 @@
       <c r="L25">
         <v>9.2</v>
       </c>
-      <c r="N25" s="24">
+      <c r="N25" s="18">
         <v>0.2</v>
       </c>
-      <c r="O25" s="24">
+      <c r="O25" s="18">
         <v>2</v>
       </c>
-      <c r="P25" s="24">
+      <c r="P25" s="18">
         <v>3</v>
       </c>
-      <c r="Q25" s="24">
+      <c r="Q25" s="18">
         <v>0.4</v>
       </c>
-      <c r="S25" s="22">
+      <c r="S25" s="26">
         <v>0.2</v>
       </c>
-      <c r="T25" s="22">
+      <c r="T25" s="26">
         <v>2</v>
       </c>
       <c r="U25" s="28">
         <v>3</v>
       </c>
-      <c r="V25" s="22">
+      <c r="V25" s="26">
         <v>4</v>
       </c>
-      <c r="X25" s="25">
+      <c r="X25" s="27">
         <v>10</v>
       </c>
-      <c r="Y25" s="25">
+      <c r="Y25" s="27">
         <v>38</v>
       </c>
-      <c r="Z25" s="25">
+      <c r="Z25" s="27">
         <v>58</v>
       </c>
-      <c r="AA25" s="25">
+      <c r="AA25" s="27">
         <v>60</v>
       </c>
-      <c r="AC25" s="22">
+      <c r="AC25" s="26">
         <v>0.2</v>
       </c>
-      <c r="AD25" s="22">
+      <c r="AD25" s="26">
         <v>2</v>
       </c>
-      <c r="AE25" s="25">
+      <c r="AE25" s="27">
         <v>3</v>
       </c>
-      <c r="AF25" s="25">
+      <c r="AF25" s="27">
         <v>4</v>
       </c>
       <c r="AH25" s="29">
@@ -18374,45 +18356,45 @@
       <c r="AJ25" s="29">
         <v>655</v>
       </c>
-      <c r="AK25" s="30">
+      <c r="AK25" s="33">
         <v>606</v>
       </c>
-      <c r="AM25" s="27">
+      <c r="AM25" s="32">
         <f t="shared" ref="AM25:AP25" si="51">AC25*10000/X25</f>
         <v>200</v>
       </c>
-      <c r="AN25" s="27">
+      <c r="AN25" s="32">
         <f t="shared" si="51"/>
         <v>526.315789473684</v>
       </c>
-      <c r="AO25" s="27">
+      <c r="AO25" s="32">
         <f t="shared" si="51"/>
         <v>517.241379310345</v>
       </c>
-      <c r="AP25" s="27">
+      <c r="AP25" s="32">
         <f t="shared" si="51"/>
         <v>666.666666666667</v>
       </c>
-      <c r="AR25" s="27"/>
-      <c r="AS25" s="27"/>
-      <c r="AT25" s="27"/>
-      <c r="AU25" s="27">
+      <c r="AR25" s="32"/>
+      <c r="AS25" s="32"/>
+      <c r="AT25" s="32"/>
+      <c r="AU25" s="32">
         <f t="shared" si="4"/>
         <v>732.15375228798</v>
       </c>
-      <c r="AW25" s="27">
+      <c r="AW25" s="32">
         <f t="shared" ref="AW25:AZ25" si="52">N25*10000/H25</f>
         <v>166.666666666667</v>
       </c>
-      <c r="AX25" s="27">
+      <c r="AX25" s="32">
         <f t="shared" si="52"/>
         <v>465.116279069767</v>
       </c>
-      <c r="AY25" s="27">
+      <c r="AY25" s="32">
         <f t="shared" si="52"/>
         <v>4285.71428571429</v>
       </c>
-      <c r="AZ25" s="27">
+      <c r="AZ25" s="32">
         <f t="shared" si="52"/>
         <v>540.540540540541</v>
       </c>
@@ -18451,22 +18433,22 @@
       <c r="L26">
         <v>26.9</v>
       </c>
-      <c r="N26" s="24">
+      <c r="N26" s="18">
         <v>1</v>
       </c>
-      <c r="O26" s="24">
+      <c r="O26" s="18">
         <v>1</v>
       </c>
-      <c r="P26" s="24">
+      <c r="P26" s="18">
         <v>2</v>
       </c>
-      <c r="Q26" s="24">
+      <c r="Q26" s="18">
         <v>2</v>
       </c>
-      <c r="S26" s="22">
+      <c r="S26" s="26">
         <v>16</v>
       </c>
-      <c r="T26" s="22">
+      <c r="T26" s="26">
         <v>22</v>
       </c>
       <c r="U26" s="28">
@@ -18475,87 +18457,87 @@
       <c r="V26" s="28">
         <v>27</v>
       </c>
-      <c r="X26" s="25">
+      <c r="X26" s="27">
         <v>132</v>
       </c>
-      <c r="Y26" s="25">
+      <c r="Y26" s="27">
         <v>175</v>
       </c>
-      <c r="Z26" s="25">
+      <c r="Z26" s="27">
         <v>179</v>
       </c>
-      <c r="AA26" s="25">
+      <c r="AA26" s="27">
         <v>179</v>
       </c>
-      <c r="AC26" s="22">
+      <c r="AC26" s="26">
         <v>16</v>
       </c>
-      <c r="AD26" s="22">
+      <c r="AD26" s="26">
         <v>22</v>
       </c>
-      <c r="AE26" s="25">
+      <c r="AE26" s="27">
         <v>28</v>
       </c>
-      <c r="AF26" s="25">
+      <c r="AF26" s="27">
         <v>26</v>
       </c>
-      <c r="AH26" s="25">
+      <c r="AH26" s="27">
         <v>1492</v>
       </c>
-      <c r="AI26" s="25">
+      <c r="AI26" s="27">
         <v>1461</v>
       </c>
-      <c r="AJ26" s="25">
+      <c r="AJ26" s="27">
         <v>1466</v>
       </c>
-      <c r="AK26" s="26">
+      <c r="AK26" s="31">
         <v>1554</v>
       </c>
-      <c r="AM26" s="27">
+      <c r="AM26" s="32">
         <f t="shared" ref="AM26:AP26" si="53">AC26*10000/X26</f>
         <v>1212.12121212121</v>
       </c>
-      <c r="AN26" s="27">
+      <c r="AN26" s="32">
         <f t="shared" si="53"/>
         <v>1257.14285714286</v>
       </c>
-      <c r="AO26" s="27">
+      <c r="AO26" s="32">
         <f t="shared" si="53"/>
         <v>1564.24581005587</v>
       </c>
-      <c r="AP26" s="27">
+      <c r="AP26" s="32">
         <f t="shared" si="53"/>
         <v>1452.51396648045</v>
       </c>
-      <c r="AR26" s="27">
+      <c r="AR26" s="32">
         <f t="shared" si="49"/>
         <v>1293.10344827586</v>
       </c>
-      <c r="AS26" s="27">
+      <c r="AS26" s="32">
         <f t="shared" ref="AS26:AS34" si="54">(T26-O26)*10000/C26</f>
         <v>1250</v>
       </c>
-      <c r="AT26" s="27">
+      <c r="AT26" s="32">
         <f t="shared" ref="AT26:AT34" si="55">(U26-P26)*10000/D26</f>
         <v>1538.46153846154</v>
       </c>
-      <c r="AU26" s="27">
+      <c r="AU26" s="32">
         <f t="shared" si="4"/>
         <v>1479.20241405834</v>
       </c>
-      <c r="AW26" s="27">
+      <c r="AW26" s="32">
         <f t="shared" ref="AW26:AZ26" si="56">N26*10000/H26</f>
         <v>526.315789473684</v>
       </c>
-      <c r="AX26" s="27">
+      <c r="AX26" s="32">
         <f t="shared" si="56"/>
         <v>769.230769230769</v>
       </c>
-      <c r="AY26" s="27">
+      <c r="AY26" s="32">
         <f t="shared" si="56"/>
         <v>1052.63157894737</v>
       </c>
-      <c r="AZ26" s="27">
+      <c r="AZ26" s="32">
         <f t="shared" si="56"/>
         <v>904.977375565611</v>
       </c>
@@ -18591,20 +18573,20 @@
       <c r="L27">
         <v>19.4</v>
       </c>
-      <c r="N27" s="31"/>
-      <c r="O27" s="24">
+      <c r="N27" s="19"/>
+      <c r="O27" s="18">
         <v>1</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="19">
         <v>1</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="19">
         <v>1</v>
       </c>
-      <c r="S27" s="22">
+      <c r="S27" s="26">
         <v>6</v>
       </c>
-      <c r="T27" s="22">
+      <c r="T27" s="26">
         <v>16</v>
       </c>
       <c r="U27" s="28">
@@ -18613,84 +18595,84 @@
       <c r="V27" s="28">
         <v>45</v>
       </c>
-      <c r="X27" s="25">
+      <c r="X27" s="27">
         <v>135</v>
       </c>
-      <c r="Y27" s="25">
+      <c r="Y27" s="27">
         <v>178</v>
       </c>
-      <c r="Z27" s="25">
+      <c r="Z27" s="27">
         <v>510</v>
       </c>
-      <c r="AA27" s="25">
+      <c r="AA27" s="27">
         <v>1057</v>
       </c>
-      <c r="AC27" s="22">
+      <c r="AC27" s="26">
         <v>6</v>
       </c>
-      <c r="AD27" s="22">
+      <c r="AD27" s="26">
         <v>16</v>
       </c>
-      <c r="AE27" s="25">
+      <c r="AE27" s="27">
         <v>20</v>
       </c>
-      <c r="AF27" s="25">
+      <c r="AF27" s="27">
         <v>45</v>
       </c>
-      <c r="AH27" s="25">
+      <c r="AH27" s="27">
         <v>793</v>
       </c>
-      <c r="AI27" s="25">
+      <c r="AI27" s="27">
         <v>932</v>
       </c>
-      <c r="AJ27" s="25">
+      <c r="AJ27" s="27">
         <v>1032</v>
       </c>
-      <c r="AK27" s="26">
+      <c r="AK27" s="31">
         <v>1092</v>
       </c>
-      <c r="AM27" s="27">
+      <c r="AM27" s="32">
         <f t="shared" ref="AM27:AP27" si="57">AC27*10000/X27</f>
         <v>444.444444444444</v>
       </c>
-      <c r="AN27" s="27">
+      <c r="AN27" s="32">
         <f t="shared" si="57"/>
         <v>898.876404494382</v>
       </c>
-      <c r="AO27" s="27">
+      <c r="AO27" s="32">
         <f t="shared" si="57"/>
         <v>392.156862745098</v>
       </c>
-      <c r="AP27" s="27">
+      <c r="AP27" s="32">
         <f t="shared" si="57"/>
         <v>425.733207190161</v>
       </c>
-      <c r="AR27" s="27">
+      <c r="AR27" s="32">
         <f t="shared" si="49"/>
         <v>444.444444444444</v>
       </c>
-      <c r="AS27" s="27">
+      <c r="AS27" s="32">
         <f t="shared" si="54"/>
         <v>931.67701863354</v>
       </c>
-      <c r="AT27" s="27">
+      <c r="AT27" s="32">
         <f t="shared" si="55"/>
         <v>386.965376782077</v>
       </c>
-      <c r="AU27" s="27">
+      <c r="AU27" s="32">
         <f t="shared" si="4"/>
         <v>453.295146651282</v>
       </c>
-      <c r="AW27" s="27"/>
-      <c r="AX27" s="27">
+      <c r="AW27" s="32"/>
+      <c r="AX27" s="32">
         <f t="shared" ref="AX27:AZ27" si="58">O27*10000/I27</f>
         <v>588.235294117647</v>
       </c>
-      <c r="AY27" s="27">
+      <c r="AY27" s="32">
         <f t="shared" si="58"/>
         <v>526.315789473684</v>
       </c>
-      <c r="AZ27" s="27">
+      <c r="AZ27" s="32">
         <f t="shared" si="58"/>
         <v>526.315789473684</v>
       </c>
@@ -18729,28 +18711,28 @@
       <c r="L28">
         <v>47.2</v>
       </c>
-      <c r="N28" s="24">
+      <c r="N28" s="18">
         <v>0.3</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O28" s="18">
         <v>1</v>
       </c>
-      <c r="P28" s="24">
+      <c r="P28" s="18">
         <v>2</v>
       </c>
-      <c r="Q28" s="24">
+      <c r="Q28" s="18">
         <v>3</v>
       </c>
-      <c r="S28" s="22">
+      <c r="S28" s="26">
         <v>28</v>
       </c>
-      <c r="T28" s="22">
+      <c r="T28" s="26">
         <v>34</v>
       </c>
-      <c r="U28" s="22">
+      <c r="U28" s="26">
         <v>48</v>
       </c>
-      <c r="V28" s="22">
+      <c r="V28" s="26">
         <v>50</v>
       </c>
       <c r="X28" s="29">
@@ -18765,10 +18747,10 @@
       <c r="AA28" s="29">
         <v>350</v>
       </c>
-      <c r="AC28" s="22">
+      <c r="AC28" s="26">
         <v>28</v>
       </c>
-      <c r="AD28" s="22">
+      <c r="AD28" s="26">
         <v>34</v>
       </c>
       <c r="AE28" s="29">
@@ -18777,60 +18759,60 @@
       <c r="AF28" s="29">
         <v>47</v>
       </c>
-      <c r="AH28" s="25">
+      <c r="AH28" s="27">
         <v>1282</v>
       </c>
-      <c r="AI28" s="25">
+      <c r="AI28" s="27">
         <v>1182</v>
       </c>
-      <c r="AJ28" s="25">
+      <c r="AJ28" s="27">
         <v>1332</v>
       </c>
-      <c r="AK28" s="26">
+      <c r="AK28" s="31">
         <v>1350</v>
       </c>
-      <c r="AM28" s="27">
+      <c r="AM28" s="32">
         <f t="shared" ref="AM28:AP28" si="59">AC28*10000/X28</f>
         <v>1176.47058823529</v>
       </c>
-      <c r="AN28" s="27">
+      <c r="AN28" s="32">
         <f t="shared" si="59"/>
         <v>1042.94478527607</v>
       </c>
-      <c r="AO28" s="27">
+      <c r="AO28" s="32">
         <f t="shared" si="59"/>
         <v>1342.85714285714</v>
       </c>
-      <c r="AP28" s="27">
+      <c r="AP28" s="32">
         <f t="shared" si="59"/>
         <v>1342.85714285714</v>
       </c>
-      <c r="AR28" s="27">
+      <c r="AR28" s="32">
         <f t="shared" si="49"/>
         <v>1166.31578947368</v>
       </c>
-      <c r="AS28" s="27">
+      <c r="AS28" s="32">
         <f t="shared" si="54"/>
         <v>1057.69230769231</v>
       </c>
-      <c r="AT28" s="27">
+      <c r="AT28" s="32">
         <f t="shared" si="55"/>
         <v>1314.28571428571</v>
       </c>
-      <c r="AU28" s="27">
+      <c r="AU28" s="32">
         <f t="shared" si="4"/>
         <v>1590.90139796229</v>
       </c>
-      <c r="AW28" s="27"/>
-      <c r="AX28" s="27">
+      <c r="AW28" s="32"/>
+      <c r="AX28" s="32">
         <f t="shared" ref="AX28:AZ28" si="60">O28*10000/I28</f>
         <v>714.285714285714</v>
       </c>
-      <c r="AY28" s="27">
+      <c r="AY28" s="32">
         <f t="shared" si="60"/>
         <v>800</v>
       </c>
-      <c r="AZ28" s="27">
+      <c r="AZ28" s="32">
         <f t="shared" si="60"/>
         <v>781.25</v>
       </c>
@@ -18863,94 +18845,94 @@
       <c r="L29">
         <v>2.2</v>
       </c>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="S29" s="22">
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="S29" s="26">
         <v>6</v>
       </c>
-      <c r="T29" s="22">
+      <c r="T29" s="26">
         <v>8</v>
       </c>
       <c r="U29" s="28">
         <v>13</v>
       </c>
-      <c r="V29" s="22">
+      <c r="V29" s="26">
         <v>14</v>
       </c>
-      <c r="X29" s="25">
+      <c r="X29" s="27">
         <v>79</v>
       </c>
-      <c r="Y29" s="25">
+      <c r="Y29" s="27">
         <v>98</v>
       </c>
-      <c r="Z29" s="25">
+      <c r="Z29" s="27">
         <v>110</v>
       </c>
-      <c r="AA29" s="25">
+      <c r="AA29" s="27">
         <v>137</v>
       </c>
-      <c r="AC29" s="22">
+      <c r="AC29" s="26">
         <v>6</v>
       </c>
-      <c r="AD29" s="22">
+      <c r="AD29" s="26">
         <v>8</v>
       </c>
-      <c r="AE29" s="25">
+      <c r="AE29" s="27">
         <v>13</v>
       </c>
-      <c r="AF29" s="25">
+      <c r="AF29" s="27">
         <v>14</v>
       </c>
-      <c r="AH29" s="25">
+      <c r="AH29" s="27">
         <v>894</v>
       </c>
-      <c r="AI29" s="25">
+      <c r="AI29" s="27">
         <v>900</v>
       </c>
-      <c r="AJ29" s="25">
+      <c r="AJ29" s="27">
         <v>1116</v>
       </c>
-      <c r="AK29" s="26">
+      <c r="AK29" s="31">
         <v>1210</v>
       </c>
-      <c r="AM29" s="27">
+      <c r="AM29" s="32">
         <f t="shared" ref="AM29:AP29" si="61">AC29*10000/X29</f>
         <v>759.493670886076</v>
       </c>
-      <c r="AN29" s="27">
+      <c r="AN29" s="32">
         <f t="shared" si="61"/>
         <v>816.326530612245</v>
       </c>
-      <c r="AO29" s="27">
+      <c r="AO29" s="32">
         <f t="shared" si="61"/>
         <v>1181.81818181818</v>
       </c>
-      <c r="AP29" s="27">
+      <c r="AP29" s="32">
         <f t="shared" si="61"/>
         <v>1021.89781021898</v>
       </c>
-      <c r="AR29" s="27">
+      <c r="AR29" s="32">
         <f t="shared" si="49"/>
         <v>759.493670886076</v>
       </c>
-      <c r="AS29" s="27">
+      <c r="AS29" s="32">
         <f t="shared" si="54"/>
         <v>816.326530612245</v>
       </c>
-      <c r="AT29" s="27">
+      <c r="AT29" s="32">
         <f t="shared" si="55"/>
         <v>1181.81818181818</v>
       </c>
-      <c r="AU29" s="27">
+      <c r="AU29" s="32">
         <f t="shared" si="4"/>
         <v>1027.44752678702</v>
       </c>
-      <c r="AW29" s="27"/>
-      <c r="AX29" s="27"/>
-      <c r="AY29" s="27"/>
-      <c r="AZ29" s="27"/>
+      <c r="AW29" s="32"/>
+      <c r="AX29" s="32"/>
+      <c r="AY29" s="32"/>
+      <c r="AZ29" s="32"/>
     </row>
     <row r="30" spans="1:52">
       <c r="A30" t="s">
@@ -18986,111 +18968,111 @@
       <c r="L30">
         <v>210.9</v>
       </c>
-      <c r="N30" s="24">
+      <c r="N30" s="18">
         <v>2</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="18">
         <v>6</v>
       </c>
-      <c r="P30" s="24">
+      <c r="P30" s="18">
         <v>9</v>
       </c>
-      <c r="Q30" s="24">
+      <c r="Q30" s="18">
         <v>16</v>
       </c>
-      <c r="S30" s="22">
+      <c r="S30" s="26">
         <v>52</v>
       </c>
-      <c r="T30" s="22">
+      <c r="T30" s="26">
         <v>71</v>
       </c>
-      <c r="U30" s="22">
+      <c r="U30" s="26">
         <v>94</v>
       </c>
-      <c r="V30" s="22">
+      <c r="V30" s="26">
         <v>119</v>
       </c>
-      <c r="X30" s="25">
+      <c r="X30" s="27">
         <v>406</v>
       </c>
-      <c r="Y30" s="25">
+      <c r="Y30" s="27">
         <v>659</v>
       </c>
-      <c r="Z30" s="25">
+      <c r="Z30" s="27">
         <v>806</v>
       </c>
-      <c r="AA30" s="25">
+      <c r="AA30" s="27">
         <v>926</v>
       </c>
-      <c r="AC30" s="22">
+      <c r="AC30" s="26">
         <v>40</v>
       </c>
-      <c r="AD30" s="22">
+      <c r="AD30" s="26">
         <v>65</v>
       </c>
-      <c r="AE30" s="25">
+      <c r="AE30" s="27">
         <v>83</v>
       </c>
-      <c r="AF30" s="25">
+      <c r="AF30" s="27">
         <v>104</v>
       </c>
-      <c r="AH30" s="25">
+      <c r="AH30" s="27">
         <v>1270</v>
       </c>
-      <c r="AI30" s="25">
+      <c r="AI30" s="27">
         <v>1274</v>
       </c>
-      <c r="AJ30" s="25">
+      <c r="AJ30" s="27">
         <v>1392</v>
       </c>
-      <c r="AK30" s="26">
+      <c r="AK30" s="31">
         <v>1273</v>
       </c>
-      <c r="AM30" s="27">
+      <c r="AM30" s="32">
         <f t="shared" ref="AM30:AP30" si="62">AC30*10000/X30</f>
         <v>985.221674876847</v>
       </c>
-      <c r="AN30" s="27">
+      <c r="AN30" s="32">
         <f t="shared" si="62"/>
         <v>986.342943854325</v>
       </c>
-      <c r="AO30" s="27">
+      <c r="AO30" s="32">
         <f t="shared" si="62"/>
         <v>1029.77667493797</v>
       </c>
-      <c r="AP30" s="27">
+      <c r="AP30" s="32">
         <f t="shared" si="62"/>
         <v>1123.1101511879</v>
       </c>
-      <c r="AR30" s="27">
+      <c r="AR30" s="32">
         <f t="shared" si="49"/>
         <v>1033.05785123967</v>
       </c>
-      <c r="AS30" s="27">
+      <c r="AS30" s="32">
         <f t="shared" si="54"/>
         <v>1015.625</v>
       </c>
-      <c r="AT30" s="27">
+      <c r="AT30" s="32">
         <f t="shared" si="55"/>
         <v>1092.54498714653</v>
       </c>
-      <c r="AU30" s="27">
+      <c r="AU30" s="32">
         <f t="shared" si="4"/>
         <v>1152.87322871662</v>
       </c>
-      <c r="AW30" s="27">
+      <c r="AW30" s="32">
         <f t="shared" ref="AW30:AZ30" si="63">N30*10000/H30</f>
         <v>392.156862745098</v>
       </c>
-      <c r="AX30" s="27">
+      <c r="AX30" s="32">
         <f t="shared" si="63"/>
         <v>789.473684210526</v>
       </c>
-      <c r="AY30" s="27">
+      <c r="AY30" s="32">
         <f t="shared" si="63"/>
         <v>555.555555555556</v>
       </c>
-      <c r="AZ30" s="27">
+      <c r="AZ30" s="32">
         <f t="shared" si="63"/>
         <v>839.014158363922</v>
       </c>
@@ -19129,111 +19111,111 @@
       <c r="L31">
         <v>77.1</v>
       </c>
-      <c r="N31" s="24">
+      <c r="N31" s="18">
         <v>1</v>
       </c>
-      <c r="O31" s="24">
+      <c r="O31" s="18">
         <v>2</v>
       </c>
-      <c r="P31" s="24">
+      <c r="P31" s="18">
         <v>6</v>
       </c>
-      <c r="Q31" s="24">
+      <c r="Q31" s="18">
         <v>9</v>
       </c>
-      <c r="S31" s="22">
+      <c r="S31" s="26">
         <v>73</v>
       </c>
-      <c r="T31" s="22">
+      <c r="T31" s="26">
         <v>95</v>
       </c>
-      <c r="U31" s="22">
+      <c r="U31" s="26">
         <v>118</v>
       </c>
       <c r="V31" s="28">
         <v>133</v>
       </c>
-      <c r="X31" s="33">
+      <c r="X31" s="30">
         <v>769</v>
       </c>
-      <c r="Y31" s="33">
+      <c r="Y31" s="30">
         <v>790</v>
       </c>
-      <c r="Z31" s="33">
+      <c r="Z31" s="30">
         <v>852</v>
       </c>
-      <c r="AA31" s="33">
+      <c r="AA31" s="30">
         <v>908</v>
       </c>
-      <c r="AC31" s="22">
+      <c r="AC31" s="26">
         <v>73</v>
       </c>
-      <c r="AD31" s="22">
+      <c r="AD31" s="26">
         <v>93</v>
       </c>
-      <c r="AE31" s="33">
+      <c r="AE31" s="30">
         <v>112</v>
       </c>
-      <c r="AF31" s="33">
+      <c r="AF31" s="30">
         <v>125</v>
       </c>
-      <c r="AH31" s="25">
+      <c r="AH31" s="27">
         <v>1123</v>
       </c>
-      <c r="AI31" s="25">
+      <c r="AI31" s="27">
         <v>1336</v>
       </c>
-      <c r="AJ31" s="25">
+      <c r="AJ31" s="27">
         <v>1511</v>
       </c>
-      <c r="AK31" s="26">
+      <c r="AK31" s="31">
         <v>1422</v>
       </c>
-      <c r="AM31" s="27">
+      <c r="AM31" s="32">
         <f t="shared" ref="AM31:AP31" si="64">AC31*10000/X31</f>
         <v>949.284785435631</v>
       </c>
-      <c r="AN31" s="27">
+      <c r="AN31" s="32">
         <f t="shared" si="64"/>
         <v>1177.21518987342</v>
       </c>
-      <c r="AO31" s="27">
+      <c r="AO31" s="32">
         <f t="shared" si="64"/>
         <v>1314.55399061033</v>
       </c>
-      <c r="AP31" s="27">
+      <c r="AP31" s="32">
         <f t="shared" si="64"/>
         <v>1376.65198237885</v>
       </c>
-      <c r="AR31" s="27">
+      <c r="AR31" s="32">
         <f t="shared" si="49"/>
         <v>937.5</v>
       </c>
-      <c r="AS31" s="27">
+      <c r="AS31" s="32">
         <f t="shared" si="54"/>
         <v>1177.21518987342</v>
       </c>
-      <c r="AT31" s="27">
+      <c r="AT31" s="32">
         <f t="shared" si="55"/>
         <v>1339.71291866029</v>
       </c>
-      <c r="AU31" s="27">
+      <c r="AU31" s="32">
         <f t="shared" si="4"/>
         <v>1391.19508145223</v>
       </c>
-      <c r="AW31" s="27">
+      <c r="AW31" s="32">
         <f t="shared" ref="AW31:AZ31" si="65">N31*10000/H31</f>
         <v>555.555555555556</v>
       </c>
-      <c r="AX31" s="27">
+      <c r="AX31" s="32">
         <f t="shared" si="65"/>
         <v>408.163265306122</v>
       </c>
-      <c r="AY31" s="27">
+      <c r="AY31" s="32">
         <f t="shared" si="65"/>
         <v>845.070422535211</v>
       </c>
-      <c r="AZ31" s="27">
+      <c r="AZ31" s="32">
         <f t="shared" si="65"/>
         <v>1216.21621621622</v>
       </c>
@@ -19272,28 +19254,28 @@
       <c r="L32">
         <v>16</v>
       </c>
-      <c r="N32" s="24">
+      <c r="N32" s="18">
         <v>0.3</v>
       </c>
-      <c r="O32" s="24">
+      <c r="O32" s="18">
         <v>1</v>
       </c>
-      <c r="P32" s="24">
+      <c r="P32" s="18">
         <v>2</v>
       </c>
-      <c r="Q32" s="24">
+      <c r="Q32" s="18">
         <v>2</v>
       </c>
-      <c r="S32" s="22">
+      <c r="S32" s="26">
         <v>113</v>
       </c>
-      <c r="T32" s="22">
+      <c r="T32" s="26">
         <v>131</v>
       </c>
-      <c r="U32" s="22">
+      <c r="U32" s="26">
         <v>158</v>
       </c>
-      <c r="V32" s="22">
+      <c r="V32" s="26">
         <v>167</v>
       </c>
       <c r="X32" s="29">
@@ -19308,10 +19290,10 @@
       <c r="AA32" s="29">
         <v>1565</v>
       </c>
-      <c r="AC32" s="22">
+      <c r="AC32" s="26">
         <v>113</v>
       </c>
-      <c r="AD32" s="22">
+      <c r="AD32" s="26">
         <v>130</v>
       </c>
       <c r="AE32" s="29">
@@ -19320,63 +19302,63 @@
       <c r="AF32" s="29">
         <v>162</v>
       </c>
-      <c r="AH32" s="25">
+      <c r="AH32" s="27">
         <v>1518</v>
       </c>
-      <c r="AI32" s="25">
+      <c r="AI32" s="27">
         <v>1464</v>
       </c>
-      <c r="AJ32" s="25">
+      <c r="AJ32" s="27">
         <v>1376</v>
       </c>
-      <c r="AK32" s="26">
+      <c r="AK32" s="31">
         <v>1487</v>
       </c>
-      <c r="AM32" s="27">
+      <c r="AM32" s="32">
         <f t="shared" ref="AM32:AP32" si="66">AC32*10000/X32</f>
         <v>1439.49044585987</v>
       </c>
-      <c r="AN32" s="27">
+      <c r="AN32" s="32">
         <f t="shared" si="66"/>
         <v>1374.20718816068</v>
       </c>
-      <c r="AO32" s="27">
+      <c r="AO32" s="32">
         <f t="shared" si="66"/>
         <v>1406.5335753176</v>
       </c>
-      <c r="AP32" s="27">
+      <c r="AP32" s="32">
         <f t="shared" si="66"/>
         <v>1035.14376996805</v>
       </c>
-      <c r="AR32" s="27">
+      <c r="AR32" s="32">
         <f t="shared" si="49"/>
         <v>1433.84223918575</v>
       </c>
-      <c r="AS32" s="27">
+      <c r="AS32" s="32">
         <f t="shared" si="54"/>
         <v>1365.54621848739</v>
       </c>
-      <c r="AT32" s="27">
+      <c r="AT32" s="32">
         <f t="shared" si="55"/>
         <v>1436.46408839779</v>
       </c>
-      <c r="AU32" s="27">
+      <c r="AU32" s="32">
         <f t="shared" si="4"/>
         <v>1076.96023079584</v>
       </c>
-      <c r="AW32" s="27">
+      <c r="AW32" s="32">
         <f t="shared" ref="AW32:AZ32" si="67">N32*10000/H32</f>
         <v>600</v>
       </c>
-      <c r="AX32" s="27">
+      <c r="AX32" s="32">
         <f t="shared" si="67"/>
         <v>1000</v>
       </c>
-      <c r="AY32" s="27">
+      <c r="AY32" s="32">
         <f t="shared" si="67"/>
         <v>1333.33333333333</v>
       </c>
-      <c r="AZ32" s="27">
+      <c r="AZ32" s="32">
         <f t="shared" si="67"/>
         <v>1273.88535031847</v>
       </c>
@@ -19415,111 +19397,111 @@
       <c r="L33">
         <v>80.6</v>
       </c>
-      <c r="N33" s="24">
+      <c r="N33" s="18">
         <v>3</v>
       </c>
-      <c r="O33" s="24">
+      <c r="O33" s="18">
         <v>4</v>
       </c>
-      <c r="P33" s="24">
+      <c r="P33" s="18">
         <v>8</v>
       </c>
-      <c r="Q33" s="24">
+      <c r="Q33" s="18">
         <v>10</v>
       </c>
-      <c r="S33" s="22">
+      <c r="S33" s="26">
         <v>76</v>
       </c>
-      <c r="T33" s="22">
+      <c r="T33" s="26">
         <v>97</v>
       </c>
-      <c r="U33" s="22">
+      <c r="U33" s="26">
         <v>115</v>
       </c>
-      <c r="V33" s="22">
+      <c r="V33" s="26">
         <v>136</v>
       </c>
-      <c r="X33" s="25">
+      <c r="X33" s="27">
         <v>612</v>
       </c>
-      <c r="Y33" s="25">
+      <c r="Y33" s="27">
         <v>799</v>
       </c>
-      <c r="Z33" s="25">
+      <c r="Z33" s="27">
         <v>895</v>
       </c>
-      <c r="AA33" s="25">
+      <c r="AA33" s="27">
         <v>1173</v>
       </c>
-      <c r="AC33" s="22">
+      <c r="AC33" s="26">
         <v>75</v>
       </c>
-      <c r="AD33" s="22">
+      <c r="AD33" s="26">
         <v>96</v>
       </c>
-      <c r="AE33" s="25">
+      <c r="AE33" s="27">
         <v>112</v>
       </c>
-      <c r="AF33" s="25">
+      <c r="AF33" s="27">
         <v>133</v>
       </c>
-      <c r="AH33" s="25">
+      <c r="AH33" s="27">
         <v>1326</v>
       </c>
-      <c r="AI33" s="25">
+      <c r="AI33" s="27">
         <v>1383</v>
       </c>
-      <c r="AJ33" s="25">
+      <c r="AJ33" s="27">
         <v>1393</v>
       </c>
-      <c r="AK33" s="26">
+      <c r="AK33" s="31">
         <v>1371</v>
       </c>
-      <c r="AM33" s="27">
+      <c r="AM33" s="32">
         <f t="shared" ref="AM33:AP33" si="68">AC33*10000/X33</f>
         <v>1225.49019607843</v>
       </c>
-      <c r="AN33" s="27">
+      <c r="AN33" s="32">
         <f t="shared" si="68"/>
         <v>1201.50187734668</v>
       </c>
-      <c r="AO33" s="27">
+      <c r="AO33" s="32">
         <f t="shared" si="68"/>
         <v>1251.39664804469</v>
       </c>
-      <c r="AP33" s="27">
+      <c r="AP33" s="32">
         <f t="shared" si="68"/>
         <v>1133.84484228474</v>
       </c>
-      <c r="AR33" s="27">
+      <c r="AR33" s="32">
         <f t="shared" si="49"/>
         <v>1243.61158432709</v>
       </c>
-      <c r="AS33" s="27">
+      <c r="AS33" s="32">
         <f t="shared" si="54"/>
         <v>1222.07621550591</v>
       </c>
-      <c r="AT33" s="27">
+      <c r="AT33" s="32">
         <f t="shared" si="55"/>
         <v>1267.77251184834</v>
       </c>
-      <c r="AU33" s="27">
+      <c r="AU33" s="32">
         <f t="shared" si="4"/>
         <v>1123.03468929374</v>
       </c>
-      <c r="AW33" s="27">
+      <c r="AW33" s="32">
         <f t="shared" ref="AW33:AZ33" si="69">N33*10000/H33</f>
         <v>909.090909090909</v>
       </c>
-      <c r="AX33" s="27">
+      <c r="AX33" s="32">
         <f t="shared" si="69"/>
         <v>727.272727272727</v>
       </c>
-      <c r="AY33" s="27">
+      <c r="AY33" s="32">
         <f t="shared" si="69"/>
         <v>1081.08108108108</v>
       </c>
-      <c r="AZ33" s="27">
+      <c r="AZ33" s="32">
         <f t="shared" si="69"/>
         <v>1329.78723404255</v>
       </c>
@@ -19558,52 +19540,52 @@
       <c r="L34">
         <v>17.2</v>
       </c>
-      <c r="N34" s="23">
+      <c r="N34" s="17">
         <v>0.01</v>
       </c>
-      <c r="O34" s="31">
+      <c r="O34" s="19">
         <v>0.1</v>
       </c>
-      <c r="P34" s="24">
+      <c r="P34" s="18">
         <v>1</v>
       </c>
-      <c r="Q34" s="24">
+      <c r="Q34" s="18">
         <v>2</v>
       </c>
-      <c r="S34" s="22">
+      <c r="S34" s="26">
         <v>107</v>
       </c>
-      <c r="T34" s="22">
+      <c r="T34" s="26">
         <v>116</v>
       </c>
-      <c r="U34" s="22">
+      <c r="U34" s="26">
         <v>132</v>
       </c>
-      <c r="V34" s="22">
+      <c r="V34" s="26">
         <v>157</v>
       </c>
-      <c r="X34" s="25">
+      <c r="X34" s="27">
         <v>934</v>
       </c>
-      <c r="Y34" s="25">
+      <c r="Y34" s="27">
         <v>978</v>
       </c>
-      <c r="Z34" s="25">
+      <c r="Z34" s="27">
         <v>1072</v>
       </c>
-      <c r="AA34" s="25">
+      <c r="AA34" s="27">
         <v>1266</v>
       </c>
-      <c r="AC34" s="22">
+      <c r="AC34" s="26">
         <v>107</v>
       </c>
-      <c r="AD34" s="22">
+      <c r="AD34" s="26">
         <v>116</v>
       </c>
-      <c r="AE34" s="25">
+      <c r="AE34" s="27">
         <v>132</v>
       </c>
-      <c r="AF34" s="25">
+      <c r="AF34" s="27">
         <v>157</v>
       </c>
       <c r="AH34" s="29">
@@ -19615,54 +19597,54 @@
       <c r="AJ34" s="29">
         <v>1396</v>
       </c>
-      <c r="AK34" s="30">
+      <c r="AK34" s="33">
         <v>1284</v>
       </c>
-      <c r="AM34" s="27">
+      <c r="AM34" s="32">
         <f t="shared" ref="AM34:AP34" si="70">AC34*10000/X34</f>
         <v>1145.61027837259</v>
       </c>
-      <c r="AN34" s="27">
+      <c r="AN34" s="32">
         <f t="shared" si="70"/>
         <v>1186.09406952965</v>
       </c>
-      <c r="AO34" s="27">
+      <c r="AO34" s="32">
         <f t="shared" si="70"/>
         <v>1231.34328358209</v>
       </c>
-      <c r="AP34" s="27">
+      <c r="AP34" s="32">
         <f t="shared" si="70"/>
         <v>1240.12638230648</v>
       </c>
-      <c r="AR34" s="27">
+      <c r="AR34" s="32">
         <f t="shared" si="49"/>
         <v>1146.73097534834</v>
       </c>
-      <c r="AS34" s="27">
+      <c r="AS34" s="32">
         <f t="shared" si="54"/>
         <v>1187.5</v>
       </c>
-      <c r="AT34" s="27">
+      <c r="AT34" s="32">
         <f t="shared" si="55"/>
         <v>1275.55988315482</v>
       </c>
-      <c r="AU34" s="27">
+      <c r="AU34" s="32">
         <f t="shared" si="4"/>
         <v>1208.40739701251</v>
       </c>
-      <c r="AW34" s="27">
+      <c r="AW34" s="32">
         <f t="shared" ref="AW34:AZ34" si="71">N34*10000/H34</f>
         <v>100</v>
       </c>
-      <c r="AX34" s="27">
+      <c r="AX34" s="32">
         <f t="shared" si="71"/>
         <v>500</v>
       </c>
-      <c r="AY34" s="27">
+      <c r="AY34" s="32">
         <f t="shared" si="71"/>
         <v>714.285714285714</v>
       </c>
-      <c r="AZ34" s="27">
+      <c r="AZ34" s="32">
         <f t="shared" si="71"/>
         <v>1197.60479041916</v>
       </c>
@@ -19711,13 +19693,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.3362831858407" customWidth="1"/>
-    <col min="2" max="37" width="9.20353982300885" customWidth="1"/>
+    <col min="1" max="1" width="21.3333333333333" customWidth="1"/>
+    <col min="2" max="37" width="9.2037037037037" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="2:51">
       <c r="B1">
         <v>201901</v>
       </c>
@@ -19983,7 +19965,7 @@
       <c r="AX2" s="12"/>
       <c r="AY2" s="12"/>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:50">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -20248,7 +20230,7 @@
         <v>157.9777</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:37">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -20346,7 +20328,7 @@
         <v>109.535</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:37">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -20444,7 +20426,7 @@
         <v>13.522</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:37">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -20542,7 +20524,7 @@
         <v>22.6447</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:37">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -20640,7 +20622,7 @@
         <v>2.9517</v>
       </c>
     </row>
-    <row r="9" spans="1:51">
+    <row r="9" spans="1:37">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -20738,7 +20720,7 @@
         <v>0.281</v>
       </c>
     </row>
-    <row r="10" spans="1:51">
+    <row r="10" spans="1:37">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -20836,7 +20818,7 @@
         <v>2.6707</v>
       </c>
     </row>
-    <row r="11" spans="1:51">
+    <row r="11" spans="1:37">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -20934,7 +20916,7 @@
         <v>11.6456</v>
       </c>
     </row>
-    <row r="12" spans="1:51">
+    <row r="12" spans="1:37">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -21032,7 +21014,7 @@
         <v>2.6022</v>
       </c>
     </row>
-    <row r="13" spans="1:51">
+    <row r="13" spans="1:37">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -21130,7 +21112,7 @@
         <v>1.1844</v>
       </c>
     </row>
-    <row r="14" spans="1:51">
+    <row r="14" spans="1:37">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -21228,7 +21210,7 @@
         <v>0.4717</v>
       </c>
     </row>
-    <row r="15" spans="1:51">
+    <row r="15" spans="1:37">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -21326,7 +21308,7 @@
         <v>13.0681</v>
       </c>
     </row>
-    <row r="16" spans="1:51">
+    <row r="16" spans="1:37">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -23411,7 +23393,7 @@
         <v>634.9901</v>
       </c>
     </row>
-    <row r="38" spans="1:37">
+    <row r="38" spans="2:37">
       <c r="B38">
         <v>201901</v>
       </c>
@@ -27418,7 +27400,7 @@
         <v>2699.0448</v>
       </c>
     </row>
-    <row r="75" ht="20.25" spans="1:37">
+    <row r="75" ht="20.4" spans="1:1">
       <c r="A75" s="14" t="s">
         <v>88</v>
       </c>
@@ -27434,9 +27416,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BF33"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:58">
+    <row r="1" spans="3:58">
       <c r="C1">
         <v>2005</v>
       </c>
@@ -33248,14 +33230,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AQ11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="39.2035398230088" style="8" customWidth="1"/>
-    <col min="2" max="43" width="12.7964601769912" style="8"/>
+    <col min="1" max="1" width="39.2037037037037" style="8" customWidth="1"/>
+    <col min="2" max="43" width="12.7962962962963" style="8"/>
     <col min="44" max="16382" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:43">
+    <row r="1" s="8" customFormat="1" spans="2:43">
       <c r="B1" s="8">
         <v>2019</v>
       </c>
@@ -33388,166 +33370,130 @@
         <v>92</v>
       </c>
       <c r="B2" s="8">
-        <v>0.0994332488610206</v>
+        <v>0.125330508228342</v>
       </c>
       <c r="C2" s="8">
-        <v>0.0990308106875101</v>
+        <v>0.117549834646866</v>
       </c>
       <c r="D2" s="8">
-        <v>0.09821930210397</v>
+        <v>0.121584238372977</v>
       </c>
       <c r="E2" s="10">
-        <v>0.104073782445382</v>
+        <v>0.124509706632302</v>
       </c>
       <c r="F2" s="10">
-        <v>0.0922386125186139</v>
+        <v>0.109521311107399</v>
       </c>
       <c r="G2" s="10">
-        <v>0.105449991849099</v>
+        <v>0.107507107507417</v>
       </c>
       <c r="H2" s="10">
-        <f t="shared" ref="F2:AQ2" si="0">MIN(G2+0.005,1500/8760)</f>
-        <v>0.110449991849099</v>
+        <v>0.111141141384185</v>
       </c>
       <c r="I2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.115449991849099</v>
+        <v>0.123</v>
       </c>
       <c r="J2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.120449991849099</v>
+        <v>0.128</v>
       </c>
       <c r="K2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.125449991849099</v>
+        <v>0.133</v>
       </c>
       <c r="L2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.130449991849099</v>
+        <v>0.138</v>
       </c>
       <c r="M2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.135449991849099</v>
+        <v>0.143</v>
       </c>
       <c r="N2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.140449991849099</v>
+        <v>0.148</v>
       </c>
       <c r="O2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.145449991849099</v>
+        <v>0.153</v>
       </c>
       <c r="P2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.150449991849099</v>
+        <v>0.158</v>
       </c>
       <c r="Q2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.155449991849099</v>
+        <v>0.163</v>
       </c>
       <c r="R2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.160449991849099</v>
+        <v>0.168</v>
       </c>
       <c r="S2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.165449991849099</v>
+        <v>0.173</v>
       </c>
       <c r="T2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.170449991849099</v>
+        <v>0.178</v>
       </c>
       <c r="U2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.183</v>
       </c>
       <c r="V2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.188</v>
       </c>
       <c r="W2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.193</v>
       </c>
       <c r="X2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.198</v>
       </c>
       <c r="Y2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.203</v>
       </c>
       <c r="Z2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AA2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AB2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AC2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AD2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AE2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AF2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AG2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AH2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AI2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AJ2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AK2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AL2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AM2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AN2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AO2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AP2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
       <c r="AQ2" s="10">
-        <f t="shared" si="0"/>
-        <v>0.171232876712329</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="6" spans="1:43">
@@ -33556,174 +33502,174 @@
       </c>
       <c r="B6" s="8">
         <f>B2*8760</f>
-        <v>871.035260022541</v>
+        <v>1097.89525208028</v>
       </c>
       <c r="C6" s="8">
-        <f t="shared" ref="C6:AQ6" si="1">C2*8760</f>
-        <v>867.509901622588</v>
+        <f t="shared" ref="C6:AQ6" si="0">C2*8760</f>
+        <v>1029.73655150655</v>
       </c>
       <c r="D6" s="8">
-        <f t="shared" si="1"/>
-        <v>860.401086430777</v>
+        <f t="shared" si="0"/>
+        <v>1065.07792814728</v>
       </c>
       <c r="E6" s="8">
-        <f t="shared" si="1"/>
-        <v>911.686334221546</v>
+        <f t="shared" si="0"/>
+        <v>1090.70503009897</v>
       </c>
       <c r="F6" s="8">
-        <f t="shared" si="1"/>
-        <v>808.010245663058</v>
+        <f t="shared" si="0"/>
+        <v>959.406685300815</v>
       </c>
       <c r="G6" s="8">
-        <f t="shared" si="1"/>
-        <v>923.741928598111</v>
+        <f t="shared" si="0"/>
+        <v>941.762261764973</v>
       </c>
       <c r="H6" s="8">
-        <f t="shared" si="1"/>
-        <v>967.541928598111</v>
+        <f t="shared" si="0"/>
+        <v>973.596398525461</v>
       </c>
       <c r="I6" s="8">
-        <f t="shared" si="1"/>
-        <v>1011.34192859811</v>
+        <f t="shared" si="0"/>
+        <v>1077.48</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" si="1"/>
-        <v>1055.14192859811</v>
+        <f t="shared" si="0"/>
+        <v>1121.28</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="1"/>
-        <v>1098.94192859811</v>
+        <f t="shared" si="0"/>
+        <v>1165.08</v>
       </c>
       <c r="L6" s="8">
-        <f t="shared" si="1"/>
-        <v>1142.74192859811</v>
+        <f t="shared" si="0"/>
+        <v>1208.88</v>
       </c>
       <c r="M6" s="8">
-        <f t="shared" si="1"/>
-        <v>1186.54192859811</v>
+        <f t="shared" si="0"/>
+        <v>1252.68</v>
       </c>
       <c r="N6" s="8">
-        <f t="shared" si="1"/>
-        <v>1230.34192859811</v>
+        <f t="shared" si="0"/>
+        <v>1296.48</v>
       </c>
       <c r="O6" s="8">
-        <f t="shared" si="1"/>
-        <v>1274.14192859811</v>
+        <f t="shared" si="0"/>
+        <v>1340.28</v>
       </c>
       <c r="P6" s="8">
-        <f t="shared" si="1"/>
-        <v>1317.94192859811</v>
+        <f t="shared" si="0"/>
+        <v>1384.08</v>
       </c>
       <c r="Q6" s="8">
-        <f t="shared" si="1"/>
-        <v>1361.74192859811</v>
+        <f t="shared" si="0"/>
+        <v>1427.88</v>
       </c>
       <c r="R6" s="8">
-        <f t="shared" si="1"/>
-        <v>1405.54192859811</v>
+        <f t="shared" si="0"/>
+        <v>1471.68</v>
       </c>
       <c r="S6" s="8">
-        <f t="shared" si="1"/>
-        <v>1449.34192859811</v>
+        <f t="shared" si="0"/>
+        <v>1515.48</v>
       </c>
       <c r="T6" s="8">
-        <f t="shared" si="1"/>
-        <v>1493.14192859811</v>
+        <f t="shared" si="0"/>
+        <v>1559.28</v>
       </c>
       <c r="U6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1603.08</v>
       </c>
       <c r="V6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1646.88</v>
       </c>
       <c r="W6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1690.68</v>
       </c>
       <c r="X6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1734.48</v>
       </c>
       <c r="Y6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1778.28</v>
       </c>
       <c r="Z6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AA6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AB6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AC6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AD6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AE6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AF6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AG6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AH6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AI6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AJ6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AK6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AL6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AM6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AN6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AO6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AP6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
       <c r="AQ6" s="8">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>1795.8</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="13:13">
       <c r="M11" s="8">
         <f>1500/8760</f>
         <v>0.171232876712329</v>
@@ -33739,25 +33685,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AP25"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.5309734513274" customWidth="1"/>
-    <col min="2" max="2" width="11.7964601769912" customWidth="1"/>
-    <col min="3" max="3" width="12.5309734513274" customWidth="1"/>
-    <col min="4" max="4" width="10.7964601769912" customWidth="1"/>
-    <col min="5" max="6" width="12.7964601769912" customWidth="1"/>
-    <col min="7" max="7" width="14.7964601769912" customWidth="1"/>
-    <col min="8" max="8" width="12.7964601769912" customWidth="1"/>
-    <col min="9" max="9" width="14.7964601769912" customWidth="1"/>
-    <col min="10" max="46" width="12.7964601769912" customWidth="1"/>
+    <col min="1" max="1" width="17.5277777777778" customWidth="1"/>
+    <col min="2" max="2" width="11.7962962962963" customWidth="1"/>
+    <col min="3" max="3" width="12.5277777777778" customWidth="1"/>
+    <col min="4" max="4" width="10.7962962962963" customWidth="1"/>
+    <col min="5" max="6" width="12.7962962962963" customWidth="1"/>
+    <col min="7" max="7" width="14.7962962962963" customWidth="1"/>
+    <col min="8" max="8" width="12.7962962962963" customWidth="1"/>
+    <col min="9" max="9" width="14.7962962962963" customWidth="1"/>
+    <col min="10" max="46" width="12.7962962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:2">
       <c r="A2" s="8" t="s">
         <v>95</v>
       </c>
@@ -33765,7 +33711,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -33773,7 +33719,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:2">
       <c r="A4" s="8" t="s">
         <v>97</v>
       </c>
@@ -33781,7 +33727,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="2:42">
       <c r="B6">
         <v>2020</v>
       </c>
@@ -34290,7 +34236,7 @@
         <v>1949469.00679781</v>
       </c>
     </row>
-    <row r="11" spans="1:42">
+    <row r="11" spans="2:42">
       <c r="B11">
         <v>2020</v>
       </c>
@@ -35736,19 +35682,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AQ24"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.7964601769912" customWidth="1"/>
-    <col min="2" max="2" width="6.53097345132743" customWidth="1"/>
-    <col min="3" max="3" width="8.53097345132743" customWidth="1"/>
-    <col min="4" max="4" width="9.53097345132743" customWidth="1"/>
-    <col min="5" max="5" width="9.46902654867257" customWidth="1"/>
-    <col min="6" max="6" width="7.53097345132743" customWidth="1"/>
-    <col min="7" max="7" width="9.53097345132743" customWidth="1"/>
-    <col min="8" max="43" width="10.5309734513274" customWidth="1"/>
+    <col min="1" max="1" width="11.7962962962963" customWidth="1"/>
+    <col min="2" max="2" width="6.52777777777778" customWidth="1"/>
+    <col min="3" max="3" width="8.52777777777778" customWidth="1"/>
+    <col min="4" max="4" width="9.52777777777778" customWidth="1"/>
+    <col min="5" max="5" width="9.47222222222222" customWidth="1"/>
+    <col min="6" max="6" width="7.52777777777778" customWidth="1"/>
+    <col min="7" max="7" width="9.52777777777778" customWidth="1"/>
+    <col min="8" max="43" width="10.5277777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="2:7">
       <c r="B1">
         <v>2019</v>
       </c>
@@ -35765,7 +35711,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>111</v>
       </c>
@@ -35790,7 +35736,7 @@
         <v>5487.97</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>112</v>
       </c>
@@ -35815,7 +35761,7 @@
         <v>2927.9</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -35840,7 +35786,7 @@
         <v>2560.07</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -35857,7 +35803,7 @@
         <v>19847.94</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -35874,7 +35820,7 @@
         <v>10750.8</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="2:7">
       <c r="B10">
         <v>2019</v>
       </c>
@@ -35891,7 +35837,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -35908,7 +35854,7 @@
         <v>10750.8</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>115</v>
       </c>
@@ -35916,7 +35862,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>116</v>
       </c>
@@ -36053,24 +35999,20 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B17">
-        <f>能源局光伏数据!D3*10</f>
         <v>141670</v>
       </c>
       <c r="C17">
-        <f>能源局光伏数据!E3*10</f>
         <v>172878.7</v>
       </c>
       <c r="D17">
-        <f>能源局光伏数据!F3*10</f>
         <v>198479.4</v>
       </c>
       <c r="E17">
-        <f>23442*10</f>
         <v>234420</v>
       </c>
       <c r="F17" s="6">
@@ -36078,6 +36020,9 @@
       </c>
       <c r="G17" s="6">
         <v>510890</v>
+      </c>
+      <c r="H17">
+        <v>670000</v>
       </c>
     </row>
     <row r="18" spans="1:43">
@@ -36085,172 +36030,130 @@
         <v>117</v>
       </c>
       <c r="B18">
-        <f t="shared" ref="B18:G18" si="4">B22-B19</f>
-        <v>57902.6193333</v>
+        <v>47272</v>
       </c>
       <c r="C18">
-        <f t="shared" si="4"/>
-        <v>69324.4902653</v>
+        <v>52751</v>
       </c>
       <c r="D18">
-        <f t="shared" si="4"/>
-        <v>86346.597329</v>
+        <v>60440</v>
       </c>
       <c r="E18">
-        <f t="shared" si="4"/>
-        <v>109547.778329</v>
+        <v>85306</v>
       </c>
       <c r="F18">
-        <f t="shared" si="4"/>
         <v>138641</v>
       </c>
       <c r="G18">
-        <f t="shared" si="4"/>
         <v>229630</v>
       </c>
       <c r="H18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,H$16),用户PV上限模拟!G$21)</f>
-        <v>224210.842229882</v>
+        <v>327168</v>
       </c>
       <c r="I18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,I$16),用户PV上限模拟!H$21)</f>
-        <v>244910.07892934</v>
+        <v>347201.636363636</v>
       </c>
       <c r="J18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,J$16),用户PV上限模拟!I$21)</f>
-        <v>247430.707609845</v>
+        <v>367235.272727273</v>
       </c>
       <c r="K18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,K$16),用户PV上限模拟!J$21)</f>
-        <v>249960.561025928</v>
+        <v>387268.909090909</v>
       </c>
       <c r="L18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,L$16),用户PV上限模拟!K$21)</f>
-        <v>252498.538961338</v>
+        <v>407302.545454545</v>
       </c>
       <c r="M18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,M$16),用户PV上限模拟!L$21)</f>
-        <v>254883.726485301</v>
+        <v>427336.181818182</v>
       </c>
       <c r="N18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,N$16),用户PV上限模拟!M$21)</f>
-        <v>257272.318984883</v>
+        <v>447369.818181818</v>
       </c>
       <c r="O18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,O$16),用户PV上限模拟!N$21)</f>
-        <v>259665.453926246</v>
+        <v>467403.454545454</v>
       </c>
       <c r="P18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,P$16),用户PV上限模拟!O$21)</f>
-        <v>262062.974482612</v>
+        <v>487437.090909091</v>
       </c>
       <c r="Q18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,Q$16),用户PV上限模拟!P$21)</f>
-        <v>264463.879226501</v>
+        <v>507470.727272727</v>
       </c>
       <c r="R18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,R$16),用户PV上限模拟!Q$21)</f>
-        <v>265631.411603458</v>
+        <v>450000</v>
       </c>
       <c r="S18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,S$16),用户PV上限模拟!R$21)</f>
-        <v>266794.659190862</v>
+        <v>456666.666666667</v>
       </c>
       <c r="T18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,T$16),用户PV上限模拟!S$21)</f>
-        <v>267954.855680568</v>
+        <v>463333.333333333</v>
       </c>
       <c r="U18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,U$16),用户PV上限模拟!T$21)</f>
-        <v>269111.286531409</v>
+        <v>470000</v>
       </c>
       <c r="V18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,V$16),用户PV上限模拟!U$21)</f>
-        <v>270264.469609319</v>
+        <v>476666.666666667</v>
       </c>
       <c r="W18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,W$16),用户PV上限模拟!V$21)</f>
-        <v>270857.05313173</v>
+        <v>483333.333333333</v>
       </c>
       <c r="X18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,X$16),用户PV上限模拟!W$21)</f>
-        <v>271443.089542668</v>
+        <v>490000</v>
       </c>
       <c r="Y18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,Y$16),用户PV上限模拟!X$21)</f>
-        <v>272023.607404707</v>
+        <v>496666.666666667</v>
       </c>
       <c r="Z18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,Z$16),用户PV上限模拟!Y$21)</f>
-        <v>272598.160578447</v>
+        <v>503333.333333333</v>
       </c>
       <c r="AA18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AA$16),用户PV上限模拟!Z$21)</f>
-        <v>273165.534507682</v>
+        <v>510000</v>
       </c>
       <c r="AB18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AB$16),用户PV上限模拟!AA$21)</f>
-        <v>273311.612917102</v>
+        <v>516666.666666667</v>
       </c>
       <c r="AC18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AC$16),用户PV上限模拟!AB$21)</f>
-        <v>273446.40812347</v>
+        <v>523333.333333334</v>
       </c>
       <c r="AD18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AD$16),用户PV上限模拟!AC$21)</f>
-        <v>273570.247923253</v>
+        <v>530000</v>
       </c>
       <c r="AE18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AE$16),用户PV上限模拟!AD$21)</f>
-        <v>273682.724166801</v>
+        <v>536666.666666667</v>
       </c>
       <c r="AF18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AF$16),用户PV上限模拟!AE$21)</f>
-        <v>273784.562403588</v>
+        <v>543333.333333333</v>
       </c>
       <c r="AG18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AG$16),用户PV上限模拟!AF$21)</f>
-        <v>273368.72012959</v>
+        <v>550000</v>
       </c>
       <c r="AH18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AH$16),用户PV上限模拟!AG$21)</f>
-        <v>272934.812255703</v>
+        <v>555000</v>
       </c>
       <c r="AI18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AI$16),用户PV上限模拟!AH$21)</f>
-        <v>272485.719528671</v>
+        <v>560000</v>
       </c>
       <c r="AJ18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AJ$16),用户PV上限模拟!AI$21)</f>
-        <v>272019.356726679</v>
+        <v>565000</v>
       </c>
       <c r="AK18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AK$16),用户PV上限模拟!AJ$21)</f>
-        <v>271534.938828024</v>
+        <v>570000</v>
       </c>
       <c r="AL18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AL$16),用户PV上限模拟!AK$21)</f>
-        <v>270645.21366965</v>
+        <v>575000</v>
       </c>
       <c r="AM18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AM$16),用户PV上限模拟!AL$21)</f>
-        <v>269733.199793622</v>
+        <v>580000</v>
       </c>
       <c r="AN18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AN$16),用户PV上限模拟!AM$21)</f>
-        <v>268799.735648496</v>
+        <v>585000</v>
       </c>
       <c r="AO18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AO$16),用户PV上限模拟!AN$21)</f>
-        <v>267844.200839324</v>
+        <v>590000</v>
       </c>
       <c r="AP18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AP$16),用户PV上限模拟!AO$21)</f>
-        <v>266865.906863427</v>
+        <v>595000</v>
       </c>
       <c r="AQ18">
-        <f>MIN(TREND($B18:$G18,$B$16:$G$16,AQ$16),用户PV上限模拟!AP$21)</f>
-        <v>329487.719458785</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="19" spans="1:43">
@@ -36258,20 +36161,16 @@
         <v>108</v>
       </c>
       <c r="B19">
-        <f>0.07548109*B22</f>
-        <v>4727.3806667</v>
+        <v>15358</v>
       </c>
       <c r="C19">
-        <f>B19+SUM(用户光伏装机数据!G36:K36)*10</f>
-        <v>8904.5097347</v>
+        <v>25478</v>
       </c>
       <c r="D19">
-        <f>C19+SUM(用户光伏装机数据!N36:X36)*10</f>
-        <v>21161.402671</v>
+        <v>47068</v>
       </c>
       <c r="E19">
-        <f>D19+SUM(用户光伏装机数据!Z36:AK36)*10</f>
-        <v>48072.221671</v>
+        <v>72314</v>
       </c>
       <c r="F19">
         <v>115797</v>
@@ -36280,148 +36179,112 @@
         <v>145150</v>
       </c>
       <c r="H19">
-        <f t="shared" ref="H19:AQ19" si="5">H20+H21</f>
-        <v>162272.224436784</v>
+        <v>205832</v>
       </c>
       <c r="I19">
-        <f t="shared" si="5"/>
-        <v>192263.692621417</v>
+        <v>247182</v>
       </c>
       <c r="J19">
-        <f t="shared" si="5"/>
-        <v>222255.16080605</v>
+        <v>288532</v>
       </c>
       <c r="K19">
-        <f t="shared" si="5"/>
-        <v>252246.628990683</v>
+        <v>329882</v>
       </c>
       <c r="L19">
-        <f t="shared" si="5"/>
-        <v>282238.097175316</v>
+        <v>371232</v>
       </c>
       <c r="M19">
-        <f t="shared" si="5"/>
-        <v>312229.565359949</v>
+        <v>412582</v>
       </c>
       <c r="N19">
-        <f t="shared" si="5"/>
-        <v>342221.033544581</v>
+        <v>453932</v>
       </c>
       <c r="O19">
-        <f t="shared" si="5"/>
-        <v>372212.501729214</v>
+        <v>495282</v>
       </c>
       <c r="P19">
-        <f t="shared" si="5"/>
-        <v>402203.969913847</v>
+        <v>536632</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="5"/>
-        <v>432195.43809848</v>
+        <v>577982</v>
       </c>
       <c r="R19">
-        <f t="shared" si="5"/>
-        <v>462186.906283113</v>
+        <v>600000</v>
       </c>
       <c r="S19">
-        <f t="shared" si="5"/>
-        <v>486000.575818998</v>
+        <v>610666.666666667</v>
       </c>
       <c r="T19">
-        <f t="shared" si="5"/>
-        <v>486370.928404351</v>
+        <v>621333.333333333</v>
       </c>
       <c r="U19">
-        <f t="shared" si="5"/>
-        <v>486744.979246426</v>
+        <v>632000</v>
       </c>
       <c r="V19">
-        <f t="shared" si="5"/>
-        <v>487125.702016588</v>
+        <v>642666.666666667</v>
       </c>
       <c r="W19">
-        <f t="shared" si="5"/>
-        <v>487510.914263203</v>
+        <v>653333.333333333</v>
       </c>
       <c r="X19">
-        <f t="shared" si="5"/>
-        <v>488828.684306797</v>
+        <v>664000</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="5"/>
-        <v>490159.047293144</v>
+        <v>674666.666666667</v>
       </c>
       <c r="Z19">
-        <f t="shared" si="5"/>
-        <v>491497.61784297</v>
+        <v>685333.333333333</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="5"/>
-        <v>492846.260311682</v>
+        <v>696000</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="5"/>
-        <v>494209.967972527</v>
+        <v>706666.666666667</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="5"/>
-        <v>495003.400968679</v>
+        <v>717333.333333333</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="5"/>
-        <v>495819.730909112</v>
+        <v>728000</v>
       </c>
       <c r="AE19">
-        <f t="shared" si="5"/>
-        <v>496657.422666866</v>
+        <v>738666.666666666</v>
       </c>
       <c r="AF19">
-        <f t="shared" si="5"/>
-        <v>497518.21228305</v>
+        <v>749333.333333333</v>
       </c>
       <c r="AG19">
-        <f t="shared" si="5"/>
-        <v>498398.900892715</v>
+        <v>760000</v>
       </c>
       <c r="AH19">
-        <f t="shared" si="5"/>
-        <v>498755.386873907</v>
+        <v>774000</v>
       </c>
       <c r="AI19">
-        <f t="shared" si="5"/>
-        <v>499151.983825863</v>
+        <v>788000</v>
       </c>
       <c r="AJ19">
-        <f t="shared" si="5"/>
-        <v>499576.672702356</v>
+        <v>802000</v>
       </c>
       <c r="AK19">
-        <f t="shared" si="5"/>
-        <v>500037.904329015</v>
+        <v>816000</v>
       </c>
       <c r="AL19">
-        <f t="shared" si="5"/>
-        <v>500538.98689642</v>
+        <v>830000</v>
       </c>
       <c r="AM19">
-        <f t="shared" si="5"/>
-        <v>500631.707448133</v>
+        <v>844000</v>
       </c>
       <c r="AN19">
-        <f t="shared" si="5"/>
-        <v>500773.416499975</v>
+        <v>858000</v>
       </c>
       <c r="AO19">
-        <f t="shared" si="5"/>
-        <v>500960.495471817</v>
+        <v>872000</v>
       </c>
       <c r="AP19">
-        <f t="shared" si="5"/>
-        <v>501195.36648689</v>
+        <v>886000</v>
       </c>
       <c r="AQ19">
-        <f t="shared" si="5"/>
-        <v>501480.794793643</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="20" spans="1:43">
@@ -36429,172 +36292,130 @@
         <v>118</v>
       </c>
       <c r="B20">
-        <f t="shared" ref="B20:G20" si="6">0.2*B19</f>
-        <v>945.47613334</v>
+        <v>2303.7</v>
       </c>
       <c r="C20">
-        <f t="shared" si="6"/>
-        <v>1780.90194694</v>
+        <v>3821.7</v>
       </c>
       <c r="D20">
-        <f t="shared" si="6"/>
-        <v>4232.2805342</v>
+        <v>7060.2</v>
       </c>
       <c r="E20">
-        <f t="shared" si="6"/>
-        <v>9614.4443342</v>
+        <v>10847.1</v>
       </c>
       <c r="F20">
-        <f t="shared" si="6"/>
-        <v>23159.4</v>
+        <v>17369.55</v>
       </c>
       <c r="G20">
-        <f t="shared" si="6"/>
-        <v>29030</v>
+        <v>21772.5</v>
       </c>
       <c r="H20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,H$16),用户PV上限模拟!G$22)</f>
-        <v>32454.4448873569</v>
+        <v>30874.8</v>
       </c>
       <c r="I20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,I$16),用户PV上限模拟!H$22)</f>
-        <v>38452.7385242834</v>
+        <v>37986.3909090909</v>
       </c>
       <c r="J20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,J$16),用户PV上限模拟!I$22)</f>
-        <v>44451.03216121</v>
+        <v>45097.9818181818</v>
       </c>
       <c r="K20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,K$16),用户PV上限模拟!J$22)</f>
-        <v>50449.3257981366</v>
+        <v>52209.5727272727</v>
       </c>
       <c r="L20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,L$16),用户PV上限模拟!K$22)</f>
-        <v>56447.6194350631</v>
+        <v>59321.1636363636</v>
       </c>
       <c r="M20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,M$16),用户PV上限模拟!L$22)</f>
-        <v>62445.9130719897</v>
+        <v>66432.7545454545</v>
       </c>
       <c r="N20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,N$16),用户PV上限模拟!M$22)</f>
-        <v>68444.2067089163</v>
+        <v>73544.3454545455</v>
       </c>
       <c r="O20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,O$16),用户PV上限模拟!N$22)</f>
-        <v>74442.5003458429</v>
+        <v>80655.9363636364</v>
       </c>
       <c r="P20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,P$16),用户PV上限模拟!O$22)</f>
-        <v>80440.7939827694</v>
+        <v>87767.5272727273</v>
       </c>
       <c r="Q20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,Q$16),用户PV上限模拟!P$22)</f>
-        <v>86439.087619696</v>
+        <v>94879.1181818182</v>
       </c>
       <c r="R20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,R$16),用户PV上限模拟!Q$22)</f>
-        <v>92437.3812566226</v>
+        <v>100000</v>
       </c>
       <c r="S20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,S$16),用户PV上限模拟!R$22)</f>
-        <v>98435.6748935491</v>
+        <v>104000</v>
       </c>
       <c r="T20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,T$16),用户PV上限模拟!S$22)</f>
-        <v>104433.968530476</v>
+        <v>108000</v>
       </c>
       <c r="U20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,U$16),用户PV上限模拟!T$22)</f>
-        <v>110432.262167402</v>
+        <v>112000</v>
       </c>
       <c r="V20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,V$16),用户PV上限模拟!U$22)</f>
-        <v>116430.555804329</v>
+        <v>116000</v>
       </c>
       <c r="W20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,W$16),用户PV上限模拟!V$22)</f>
-        <v>122428.849441255</v>
+        <v>120000</v>
       </c>
       <c r="X20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,X$16),用户PV上限模拟!W$22)</f>
-        <v>128427.143078182</v>
+        <v>124000</v>
       </c>
       <c r="Y20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,Y$16),用户PV上限模拟!X$22)</f>
-        <v>134425.436715109</v>
+        <v>128000</v>
       </c>
       <c r="Z20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,Z$16),用户PV上限模拟!Y$22)</f>
-        <v>140423.730352035</v>
+        <v>132000</v>
       </c>
       <c r="AA20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AA$16),用户PV上限模拟!Z$22)</f>
-        <v>146422.023988962</v>
+        <v>136000</v>
       </c>
       <c r="AB20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AB$16),用户PV上限模拟!AA$22)</f>
-        <v>152420.317625888</v>
+        <v>140000</v>
       </c>
       <c r="AC20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AC$16),用户PV上限模拟!AB$22)</f>
-        <v>158418.611262815</v>
+        <v>144000</v>
       </c>
       <c r="AD20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AD$16),用户PV上限模拟!AC$22)</f>
-        <v>164416.904899741</v>
+        <v>148000</v>
       </c>
       <c r="AE20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AE$16),用户PV上限模拟!AD$22)</f>
-        <v>170415.198536668</v>
+        <v>152000</v>
       </c>
       <c r="AF20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AF$16),用户PV上限模拟!AE$22)</f>
-        <v>176413.492173595</v>
+        <v>156000</v>
       </c>
       <c r="AG20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AG$16),用户PV上限模拟!AF$22)</f>
-        <v>182411.785810521</v>
+        <v>160000</v>
       </c>
       <c r="AH20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AH$16),用户PV上限模拟!AG$22)</f>
-        <v>188410.079447448</v>
+        <v>164000</v>
       </c>
       <c r="AI20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AI$16),用户PV上限模拟!AH$22)</f>
-        <v>194408.373084374</v>
+        <v>168000</v>
       </c>
       <c r="AJ20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AJ$16),用户PV上限模拟!AI$22)</f>
-        <v>200406.666721301</v>
+        <v>172000</v>
       </c>
       <c r="AK20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AK$16),用户PV上限模拟!AJ$22)</f>
-        <v>206404.960358227</v>
+        <v>176000</v>
       </c>
       <c r="AL20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AL$16),用户PV上限模拟!AK$22)</f>
-        <v>212403.253995154</v>
+        <v>180000</v>
       </c>
       <c r="AM20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AM$16),用户PV上限模拟!AL$22)</f>
-        <v>218401.547632081</v>
+        <v>184000</v>
       </c>
       <c r="AN20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AN$16),用户PV上限模拟!AM$22)</f>
-        <v>224399.841269007</v>
+        <v>188000</v>
       </c>
       <c r="AO20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AO$16),用户PV上限模拟!AN$22)</f>
-        <v>230398.134905934</v>
+        <v>192000</v>
       </c>
       <c r="AP20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AP$16),用户PV上限模拟!AO$22)</f>
-        <v>236396.42854286</v>
+        <v>196000</v>
       </c>
       <c r="AQ20">
-        <f>MIN(TREND($B20:$G20,$B$16:$G$16,AQ$16),用户PV上限模拟!AP$22)</f>
-        <v>242394.722179787</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="21" spans="1:43">
@@ -36602,172 +36423,130 @@
         <v>119</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:G21" si="7">0.8*B19</f>
-        <v>3781.90453336</v>
+        <v>13054.3</v>
       </c>
       <c r="C21">
-        <f t="shared" si="7"/>
-        <v>7123.60778776</v>
+        <v>21656.3</v>
       </c>
       <c r="D21">
-        <f t="shared" si="7"/>
-        <v>16929.1221368</v>
+        <v>40007.8</v>
       </c>
       <c r="E21">
-        <f t="shared" si="7"/>
-        <v>38457.7773368</v>
+        <v>61466.9</v>
       </c>
       <c r="F21">
-        <f t="shared" si="7"/>
-        <v>92637.6</v>
+        <v>98427.45</v>
       </c>
       <c r="G21">
-        <f t="shared" si="7"/>
-        <v>116120</v>
+        <v>123377.5</v>
       </c>
       <c r="H21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,H$16),用户PV上限模拟!G$23)</f>
-        <v>129817.779549427</v>
+        <v>174957.2</v>
       </c>
       <c r="I21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,I$16),用户PV上限模拟!H$23)</f>
-        <v>153810.954097134</v>
+        <v>209195.609090909</v>
       </c>
       <c r="J21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,J$16),用户PV上限模拟!I$23)</f>
-        <v>177804.12864484</v>
+        <v>243434.018181818</v>
       </c>
       <c r="K21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,K$16),用户PV上限模拟!J$23)</f>
-        <v>201797.303192546</v>
+        <v>277672.427272727</v>
       </c>
       <c r="L21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,L$16),用户PV上限模拟!K$23)</f>
-        <v>225790.477740253</v>
+        <v>311910.836363636</v>
       </c>
       <c r="M21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,M$16),用户PV上限模拟!L$23)</f>
-        <v>249783.652287959</v>
+        <v>346149.245454545</v>
       </c>
       <c r="N21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,N$16),用户PV上限模拟!M$23)</f>
-        <v>273776.826835665</v>
+        <v>380387.654545454</v>
       </c>
       <c r="O21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,O$16),用户PV上限模拟!N$23)</f>
-        <v>297770.001383371</v>
+        <v>414626.063636363</v>
       </c>
       <c r="P21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,P$16),用户PV上限模拟!O$23)</f>
-        <v>321763.175931078</v>
+        <v>448864.472727273</v>
       </c>
       <c r="Q21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,Q$16),用户PV上限模拟!P$23)</f>
-        <v>345756.350478784</v>
+        <v>483102.881818182</v>
       </c>
       <c r="R21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,R$16),用户PV上限模拟!Q$23)</f>
-        <v>369749.52502649</v>
+        <v>500000</v>
       </c>
       <c r="S21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,S$16),用户PV上限模拟!R$23)</f>
-        <v>387564.900925449</v>
+        <v>506666.666666667</v>
       </c>
       <c r="T21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,T$16),用户PV上限模拟!S$23)</f>
-        <v>381936.959873876</v>
+        <v>513333.333333333</v>
       </c>
       <c r="U21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,U$16),用户PV上限模拟!T$23)</f>
-        <v>376312.717079023</v>
+        <v>520000</v>
       </c>
       <c r="V21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,V$16),用户PV上限模拟!U$23)</f>
-        <v>370695.146212259</v>
+        <v>526666.666666667</v>
       </c>
       <c r="W21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,W$16),用户PV上限模拟!V$23)</f>
-        <v>365082.064821948</v>
+        <v>533333.333333333</v>
       </c>
       <c r="X21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,X$16),用户PV上限模拟!W$23)</f>
-        <v>360401.541228615</v>
+        <v>540000</v>
       </c>
       <c r="Y21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,Y$16),用户PV上限模拟!X$23)</f>
-        <v>355733.610578035</v>
+        <v>546666.666666667</v>
       </c>
       <c r="Z21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,Z$16),用户PV上限模拟!Y$23)</f>
-        <v>351073.887490935</v>
+        <v>553333.333333333</v>
       </c>
       <c r="AA21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AA$16),用户PV上限模拟!Z$23)</f>
-        <v>346424.23632272</v>
+        <v>560000</v>
       </c>
       <c r="AB21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AB$16),用户PV上限模拟!AA$23)</f>
-        <v>341789.650346639</v>
+        <v>566666.666666667</v>
       </c>
       <c r="AC21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AC$16),用户PV上限模拟!AB$23)</f>
-        <v>336584.789705864</v>
+        <v>573333.333333333</v>
       </c>
       <c r="AD21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AD$16),用户PV上限模拟!AC$23)</f>
-        <v>331402.82600937</v>
+        <v>580000</v>
       </c>
       <c r="AE21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AE$16),用户PV上限模拟!AD$23)</f>
-        <v>326242.224130198</v>
+        <v>586666.666666666</v>
       </c>
       <c r="AF21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AF$16),用户PV上限模拟!AE$23)</f>
-        <v>321104.720109455</v>
+        <v>593333.333333333</v>
       </c>
       <c r="AG21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AG$16),用户PV上限模拟!AF$23)</f>
-        <v>315987.115082194</v>
+        <v>600000</v>
       </c>
       <c r="AH21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AH$16),用户PV上限模拟!AG$23)</f>
-        <v>310345.307426459</v>
+        <v>610000</v>
       </c>
       <c r="AI21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AI$16),用户PV上限模拟!AH$23)</f>
-        <v>304743.610741489</v>
+        <v>620000</v>
       </c>
       <c r="AJ21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AJ$16),用户PV上限模拟!AI$23)</f>
-        <v>299170.005981055</v>
+        <v>630000</v>
       </c>
       <c r="AK21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AK$16),用户PV上限模拟!AJ$23)</f>
-        <v>293632.943970788</v>
+        <v>640000</v>
       </c>
       <c r="AL21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AL$16),用户PV上限模拟!AK$23)</f>
-        <v>288135.732901266</v>
+        <v>650000</v>
       </c>
       <c r="AM21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AM$16),用户PV上限模拟!AL$23)</f>
-        <v>282230.159816052</v>
+        <v>660000</v>
       </c>
       <c r="AN21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AN$16),用户PV上限模拟!AM$23)</f>
-        <v>276373.575230968</v>
+        <v>670000</v>
       </c>
       <c r="AO21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AO$16),用户PV上限模拟!AN$23)</f>
-        <v>270562.360565884</v>
+        <v>680000</v>
       </c>
       <c r="AP21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AP$16),用户PV上限模拟!AO$23)</f>
-        <v>264798.937944029</v>
+        <v>690000</v>
       </c>
       <c r="AQ21">
-        <f>MIN(TREND($B21:$G21,$B$16:$G$16,AQ$16),用户PV上限模拟!AP$23)</f>
-        <v>259086.072613856</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="22" spans="1:43">
@@ -36775,19 +36554,15 @@
         <v>120</v>
       </c>
       <c r="B22">
-        <f>能源局光伏数据!J3*10</f>
         <v>62630</v>
       </c>
       <c r="C22">
-        <f>能源局光伏数据!K3*10</f>
         <v>78229</v>
       </c>
       <c r="D22">
-        <f>能源局光伏数据!L3*10</f>
         <v>107508</v>
       </c>
       <c r="E22">
-        <f>15762*10</f>
         <v>157620</v>
       </c>
       <c r="F22" s="6">
@@ -36797,180 +36572,144 @@
         <v>374780</v>
       </c>
       <c r="H22">
-        <f t="shared" ref="H22:AQ22" si="8">H19+H18</f>
-        <v>386483.066666666</v>
+        <v>533000</v>
       </c>
       <c r="I22">
-        <f t="shared" si="8"/>
-        <v>437173.771550758</v>
+        <v>594383.636363636</v>
       </c>
       <c r="J22">
-        <f t="shared" si="8"/>
-        <v>469685.868415895</v>
+        <v>655767.272727273</v>
       </c>
       <c r="K22">
-        <f t="shared" si="8"/>
-        <v>502207.190016611</v>
+        <v>717150.909090909</v>
       </c>
       <c r="L22">
-        <f t="shared" si="8"/>
-        <v>534736.636136654</v>
+        <v>778534.545454545</v>
       </c>
       <c r="M22">
-        <f t="shared" si="8"/>
-        <v>567113.291845249</v>
+        <v>839918.181818182</v>
       </c>
       <c r="N22">
-        <f t="shared" si="8"/>
-        <v>599493.352529464</v>
+        <v>901301.818181818</v>
       </c>
       <c r="O22">
-        <f t="shared" si="8"/>
-        <v>631877.955655461</v>
+        <v>962685.454545454</v>
       </c>
       <c r="P22">
-        <f t="shared" si="8"/>
-        <v>664266.944396459</v>
+        <v>1024069.09090909</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="8"/>
-        <v>696659.317324981</v>
+        <v>1085452.72727273</v>
       </c>
       <c r="R22">
-        <f t="shared" si="8"/>
-        <v>727818.317886571</v>
+        <v>1050000</v>
       </c>
       <c r="S22">
-        <f t="shared" si="8"/>
-        <v>752795.23500986</v>
+        <v>1067333.33333333</v>
       </c>
       <c r="T22">
-        <f t="shared" si="8"/>
-        <v>754325.78408492</v>
+        <v>1084666.66666667</v>
       </c>
       <c r="U22">
-        <f t="shared" si="8"/>
-        <v>755856.265777834</v>
+        <v>1102000</v>
       </c>
       <c r="V22">
-        <f t="shared" si="8"/>
-        <v>757390.171625907</v>
+        <v>1119333.33333333</v>
       </c>
       <c r="W22">
-        <f t="shared" si="8"/>
-        <v>758367.967394933</v>
+        <v>1136666.66666667</v>
       </c>
       <c r="X22">
-        <f t="shared" si="8"/>
-        <v>760271.773849465</v>
+        <v>1154000</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="8"/>
-        <v>762182.654697851</v>
+        <v>1171333.33333333</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="8"/>
-        <v>764095.778421417</v>
+        <v>1188666.66666667</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="8"/>
-        <v>766011.794819364</v>
+        <v>1206000</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="8"/>
-        <v>767521.580889629</v>
+        <v>1223333.33333333</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="8"/>
-        <v>768449.809092149</v>
+        <v>1240666.66666667</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="8"/>
-        <v>769389.978832365</v>
+        <v>1258000</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="8"/>
-        <v>770340.146833667</v>
+        <v>1275333.33333333</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="8"/>
-        <v>771302.774686638</v>
+        <v>1292666.66666667</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="8"/>
-        <v>771767.621022305</v>
+        <v>1310000</v>
       </c>
       <c r="AH22">
-        <f t="shared" si="8"/>
-        <v>771690.199129609</v>
+        <v>1329000</v>
       </c>
       <c r="AI22">
-        <f t="shared" si="8"/>
-        <v>771637.703354534</v>
+        <v>1348000</v>
       </c>
       <c r="AJ22">
-        <f t="shared" si="8"/>
-        <v>771596.029429035</v>
+        <v>1367000</v>
       </c>
       <c r="AK22">
-        <f t="shared" si="8"/>
-        <v>771572.843157039</v>
+        <v>1386000</v>
       </c>
       <c r="AL22">
-        <f t="shared" si="8"/>
-        <v>771184.20056607</v>
+        <v>1405000</v>
       </c>
       <c r="AM22">
-        <f t="shared" si="8"/>
-        <v>770364.907241754</v>
+        <v>1424000</v>
       </c>
       <c r="AN22">
-        <f t="shared" si="8"/>
-        <v>769573.152148472</v>
+        <v>1443000</v>
       </c>
       <c r="AO22">
-        <f t="shared" si="8"/>
-        <v>768804.696311141</v>
+        <v>1462000</v>
       </c>
       <c r="AP22">
-        <f t="shared" si="8"/>
-        <v>768061.273350316</v>
+        <v>1481000</v>
       </c>
       <c r="AQ22">
-        <f t="shared" si="8"/>
-        <v>830968.514252428</v>
+        <v>1500000</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
         <v>121</v>
       </c>
       <c r="B23">
-        <f t="shared" ref="B23:G23" si="9">B17+B22</f>
+        <f t="shared" ref="B23:G23" si="4">B17+B22</f>
         <v>204300</v>
       </c>
       <c r="C23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>251107.7</v>
       </c>
       <c r="D23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>305987.4</v>
       </c>
       <c r="E23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>392040</v>
       </c>
       <c r="F23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>608919</v>
       </c>
       <c r="G23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>885670</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:1">
       <c r="A24" s="7"/>
     </row>
   </sheetData>
@@ -36985,11 +36724,11 @@
     <tabColor theme="4" tint="0.399975585192419"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="33.1327433628319" customWidth="1"/>
-    <col min="2" max="3" width="21.7964601769912" customWidth="1"/>
-    <col min="4" max="4" width="13.1327433628319" customWidth="1"/>
+    <col min="1" max="1" width="33.1296296296296" customWidth="1"/>
+    <col min="2" max="3" width="21.7962962962963" customWidth="1"/>
+    <col min="4" max="4" width="13.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -37082,15 +36821,15 @@
       </c>
       <c r="B7">
         <f>中国光伏数据!B20</f>
-        <v>945.47613334</v>
+        <v>2303.7</v>
       </c>
       <c r="C7">
         <f>中国光伏数据!B21</f>
-        <v>3781.90453336</v>
+        <v>13054.3</v>
       </c>
       <c r="D7">
         <f>中国光伏数据!B18</f>
-        <v>57902.6193333</v>
+        <v>47272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -37245,18 +36984,18 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ17"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="29.7964601769912" customWidth="1"/>
-    <col min="2" max="4" width="7.53097345132743" customWidth="1"/>
-    <col min="5" max="8" width="8.53097345132743" customWidth="1"/>
-    <col min="9" max="13" width="12.7964601769912" customWidth="1"/>
-    <col min="14" max="14" width="11.7964601769912" customWidth="1"/>
-    <col min="15" max="15" width="9.53097345132743" customWidth="1"/>
-    <col min="16" max="16" width="11.7964601769912" customWidth="1"/>
-    <col min="17" max="34" width="12.7964601769912" customWidth="1"/>
-    <col min="35" max="37" width="11.7964601769912" customWidth="1"/>
-    <col min="38" max="43" width="12.7964601769912" customWidth="1"/>
+    <col min="1" max="1" width="29.7962962962963" customWidth="1"/>
+    <col min="2" max="4" width="7.52777777777778" customWidth="1"/>
+    <col min="5" max="8" width="8.52777777777778" customWidth="1"/>
+    <col min="9" max="13" width="12.7962962962963" customWidth="1"/>
+    <col min="14" max="14" width="11.7962962962963" customWidth="1"/>
+    <col min="15" max="15" width="9.52777777777778" customWidth="1"/>
+    <col min="16" max="16" width="11.7962962962963" customWidth="1"/>
+    <col min="17" max="34" width="12.7962962962963" customWidth="1"/>
+    <col min="35" max="37" width="11.7962962962963" customWidth="1"/>
+    <col min="38" max="43" width="12.7962962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
@@ -38051,171 +37790,171 @@
       </c>
       <c r="B7" s="1">
         <f>中国光伏数据!B$20</f>
-        <v>945.47613334</v>
+        <v>2303.7</v>
       </c>
       <c r="C7" s="1">
         <f>中国光伏数据!C$20</f>
-        <v>1780.90194694</v>
+        <v>3821.7</v>
       </c>
       <c r="D7" s="1">
         <f>中国光伏数据!D$20</f>
-        <v>4232.2805342</v>
+        <v>7060.2</v>
       </c>
       <c r="E7" s="1">
         <f>中国光伏数据!E$20</f>
-        <v>9614.4443342</v>
+        <v>10847.1</v>
       </c>
       <c r="F7" s="1">
         <f>中国光伏数据!F$20</f>
-        <v>23159.4</v>
+        <v>17369.55</v>
       </c>
       <c r="G7" s="1">
         <f>中国光伏数据!G$20</f>
-        <v>29030</v>
+        <v>21772.5</v>
       </c>
       <c r="H7" s="1">
         <f>中国光伏数据!H$20</f>
-        <v>32454.4448873569</v>
+        <v>30874.8</v>
       </c>
       <c r="I7" s="1">
         <f>中国光伏数据!I$20</f>
-        <v>38452.7385242834</v>
+        <v>37986.3909090909</v>
       </c>
       <c r="J7" s="1">
         <f>中国光伏数据!J$20</f>
-        <v>44451.03216121</v>
+        <v>45097.9818181818</v>
       </c>
       <c r="K7" s="1">
         <f>中国光伏数据!K$20</f>
-        <v>50449.3257981366</v>
+        <v>52209.5727272727</v>
       </c>
       <c r="L7" s="1">
         <f>中国光伏数据!L$20</f>
-        <v>56447.6194350631</v>
+        <v>59321.1636363636</v>
       </c>
       <c r="M7" s="1">
         <f>中国光伏数据!M$20</f>
-        <v>62445.9130719897</v>
+        <v>66432.7545454545</v>
       </c>
       <c r="N7" s="1">
         <f>中国光伏数据!N$20</f>
-        <v>68444.2067089163</v>
+        <v>73544.3454545455</v>
       </c>
       <c r="O7" s="1">
         <f>中国光伏数据!O$20</f>
-        <v>74442.5003458429</v>
+        <v>80655.9363636364</v>
       </c>
       <c r="P7" s="1">
         <f>中国光伏数据!P$20</f>
-        <v>80440.7939827694</v>
+        <v>87767.5272727273</v>
       </c>
       <c r="Q7" s="1">
         <f>中国光伏数据!Q$20</f>
-        <v>86439.087619696</v>
+        <v>94879.1181818182</v>
       </c>
       <c r="R7" s="1">
         <f>中国光伏数据!R$20</f>
-        <v>92437.3812566226</v>
+        <v>100000</v>
       </c>
       <c r="S7" s="1">
         <f>中国光伏数据!S$20</f>
-        <v>98435.6748935491</v>
+        <v>104000</v>
       </c>
       <c r="T7" s="1">
         <f>中国光伏数据!T$20</f>
-        <v>104433.968530476</v>
+        <v>108000</v>
       </c>
       <c r="U7" s="1">
         <f>中国光伏数据!U$20</f>
-        <v>110432.262167402</v>
+        <v>112000</v>
       </c>
       <c r="V7" s="1">
         <f>中国光伏数据!V$20</f>
-        <v>116430.555804329</v>
+        <v>116000</v>
       </c>
       <c r="W7" s="1">
         <f>中国光伏数据!W$20</f>
-        <v>122428.849441255</v>
+        <v>120000</v>
       </c>
       <c r="X7" s="1">
         <f>中国光伏数据!X$20</f>
-        <v>128427.143078182</v>
+        <v>124000</v>
       </c>
       <c r="Y7" s="1">
         <f>中国光伏数据!Y$20</f>
-        <v>134425.436715109</v>
+        <v>128000</v>
       </c>
       <c r="Z7" s="1">
         <f>中国光伏数据!Z$20</f>
-        <v>140423.730352035</v>
+        <v>132000</v>
       </c>
       <c r="AA7" s="1">
         <f>中国光伏数据!AA$20</f>
-        <v>146422.023988962</v>
+        <v>136000</v>
       </c>
       <c r="AB7" s="1">
         <f>中国光伏数据!AB$20</f>
-        <v>152420.317625888</v>
+        <v>140000</v>
       </c>
       <c r="AC7" s="1">
         <f>中国光伏数据!AC$20</f>
-        <v>158418.611262815</v>
+        <v>144000</v>
       </c>
       <c r="AD7" s="1">
         <f>中国光伏数据!AD$20</f>
-        <v>164416.904899741</v>
+        <v>148000</v>
       </c>
       <c r="AE7" s="1">
         <f>中国光伏数据!AE$20</f>
-        <v>170415.198536668</v>
+        <v>152000</v>
       </c>
       <c r="AF7" s="1">
         <f>中国光伏数据!AF$20</f>
-        <v>176413.492173595</v>
+        <v>156000</v>
       </c>
       <c r="AG7" s="1">
         <f>中国光伏数据!AG$20</f>
-        <v>182411.785810521</v>
+        <v>160000</v>
       </c>
       <c r="AH7" s="1">
         <f>中国光伏数据!AH$20</f>
-        <v>188410.079447448</v>
+        <v>164000</v>
       </c>
       <c r="AI7" s="1">
         <f>中国光伏数据!AI$20</f>
-        <v>194408.373084374</v>
+        <v>168000</v>
       </c>
       <c r="AJ7" s="1">
         <f>中国光伏数据!AJ$20</f>
-        <v>200406.666721301</v>
+        <v>172000</v>
       </c>
       <c r="AK7" s="1">
         <f>中国光伏数据!AK$20</f>
-        <v>206404.960358227</v>
+        <v>176000</v>
       </c>
       <c r="AL7" s="1">
         <f>中国光伏数据!AL$20</f>
-        <v>212403.253995154</v>
+        <v>180000</v>
       </c>
       <c r="AM7" s="1">
         <f>中国光伏数据!AM$20</f>
-        <v>218401.547632081</v>
+        <v>184000</v>
       </c>
       <c r="AN7" s="1">
         <f>中国光伏数据!AN$20</f>
-        <v>224399.841269007</v>
+        <v>188000</v>
       </c>
       <c r="AO7" s="1">
         <f>中国光伏数据!AO$20</f>
-        <v>230398.134905934</v>
+        <v>192000</v>
       </c>
       <c r="AP7" s="1">
         <f>中国光伏数据!AP$20</f>
-        <v>236396.42854286</v>
+        <v>196000</v>
       </c>
       <c r="AQ7" s="1">
         <f>中国光伏数据!AQ$20</f>
-        <v>242394.722179787</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="8" spans="1:43">
